--- a/database/event/2325/event_2325_evp_summary.xlsx
+++ b/database/event/2325/event_2325_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5687</v>
+        <v>6.2259</v>
       </c>
       <c r="C2" t="n">
-        <v>2.533</v>
+        <v>2.8319</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8283</v>
+        <v>2.0365</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5687</v>
+        <v>6.2259</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3381</v>
+        <v>2.1458</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2306</v>
+        <v>4.0801</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3381</v>
+        <v>2.1458</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3381</v>
+        <v>2.1458</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2306</v>
+        <v>4.0801</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>183</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5687</v>
+        <v>6.225899999999999</v>
       </c>
       <c r="N2" t="n">
         <v>230</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4334</v>
+        <v>5.6838</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4715</v>
+        <v>2.5854</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7736</v>
+        <v>1.8205</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4334</v>
+        <v>5.6838</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3533</v>
+        <v>1.4532</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0801</v>
+        <v>4.2306</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3533</v>
+        <v>1.4532</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3533</v>
+        <v>1.4532</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0801</v>
+        <v>4.2306</v>
       </c>
       <c r="K3" t="n">
         <v>47</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4334</v>
+        <v>5.6838</v>
       </c>
       <c r="N3" t="n">
         <v>230</v>
@@ -584,127 +584,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0296</v>
+        <v>4.8685</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8329</v>
+        <v>2.2145</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2065</v>
+        <v>1.4957</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0296</v>
+        <v>4.8685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.773</v>
+        <v>1.9744</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2566</v>
+        <v>2.8941</v>
       </c>
       <c r="H4" t="n">
-        <v>0.773</v>
+        <v>1.9744</v>
       </c>
       <c r="I4" t="n">
-        <v>0.773</v>
+        <v>1.9744</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2566</v>
+        <v>2.8941</v>
       </c>
       <c r="K4" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0296</v>
+        <v>4.8685</v>
       </c>
       <c r="N4" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0053</v>
+        <v>4.2615</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8219</v>
+        <v>1.9384</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1967</v>
+        <v>1.2539</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0053</v>
+        <v>4.2615</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2165</v>
+        <v>2.7349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7888</v>
+        <v>1.5266</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2165</v>
+        <v>2.7349</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2165</v>
+        <v>2.7349</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7888</v>
+        <v>1.5266</v>
       </c>
       <c r="K5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0053</v>
+        <v>4.2615</v>
       </c>
       <c r="N5" t="n">
-        <v>230</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9378</v>
+        <v>4.203</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7912</v>
+        <v>1.9118</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1694</v>
+        <v>1.2306</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9378</v>
+        <v>4.203</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0437</v>
+        <v>2.9979</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8941</v>
+        <v>1.2051</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0437</v>
+        <v>2.9979</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0437</v>
+        <v>2.9979</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8941</v>
+        <v>1.2051</v>
       </c>
       <c r="K6" t="n">
         <v>45</v>
@@ -713,7 +713,7 @@
         <v>179</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9378</v>
+        <v>4.203</v>
       </c>
       <c r="N6" t="n">
         <v>224</v>
@@ -722,127 +722,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1733</v>
+        <v>4.0296</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4434</v>
+        <v>1.8329</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8606</v>
+        <v>1.1615</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1733</v>
+        <v>4.0296</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6467</v>
+        <v>0.773</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5266</v>
+        <v>3.2566</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6467</v>
+        <v>0.773</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6467</v>
+        <v>0.773</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5266</v>
+        <v>3.2566</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L7" t="n">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1733</v>
+        <v>4.0296</v>
       </c>
       <c r="N7" t="n">
-        <v>161</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1664</v>
+        <v>4.0057</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4403</v>
+        <v>1.8221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8578</v>
+        <v>1.152</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1664</v>
+        <v>4.0057</v>
       </c>
       <c r="F8" t="n">
-        <v>1.382</v>
+        <v>0.2169</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7844</v>
+        <v>3.7888</v>
       </c>
       <c r="H8" t="n">
-        <v>1.382</v>
+        <v>0.2169</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3884</v>
+        <v>0.2169</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7844</v>
+        <v>3.7888</v>
       </c>
       <c r="K8" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1728</v>
+        <v>4.0057</v>
       </c>
       <c r="N8" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1306</v>
+        <v>3.6013</v>
       </c>
       <c r="C9" t="n">
-        <v>1.424</v>
+        <v>1.6381</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8433</v>
+        <v>0.9908</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1306</v>
+        <v>3.6013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6446</v>
+        <v>1.8169</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4861</v>
+        <v>1.7844</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6446</v>
+        <v>1.8169</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6476</v>
+        <v>1.8322</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4861</v>
+        <v>1.7844</v>
       </c>
       <c r="K9" t="n">
         <v>95</v>
@@ -851,7 +851,7 @@
         <v>140</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1337</v>
+        <v>3.6166</v>
       </c>
       <c r="N9" t="n">
         <v>235</v>
@@ -860,127 +860,127 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0103</v>
+        <v>3.289</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3693</v>
+        <v>1.496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7947</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0103</v>
+        <v>3.289</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1569</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8534</v>
+        <v>2.4861</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1569</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2.167</v>
+        <v>0.8097</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8534</v>
+        <v>2.4861</v>
       </c>
       <c r="K10" t="n">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="L10" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0204</v>
+        <v>3.2958</v>
       </c>
       <c r="N10" t="n">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8931</v>
+        <v>3.2374</v>
       </c>
       <c r="C11" t="n">
-        <v>1.316</v>
+        <v>1.4726</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7474</v>
+        <v>0.8459</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8931</v>
+        <v>3.2374</v>
       </c>
       <c r="F11" t="n">
-        <v>1.688</v>
+        <v>2.1857</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2051</v>
+        <v>1.0517</v>
       </c>
       <c r="H11" t="n">
-        <v>1.688</v>
+        <v>2.1857</v>
       </c>
       <c r="I11" t="n">
-        <v>1.688</v>
+        <v>2.1857</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2051</v>
+        <v>1.0517</v>
       </c>
       <c r="K11" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="L11" t="n">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8931</v>
+        <v>3.2374</v>
       </c>
       <c r="N11" t="n">
-        <v>224</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6261</v>
+        <v>3.1999</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1945</v>
+        <v>1.4555</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6395</v>
+        <v>0.8309</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6261</v>
+        <v>3.1999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5744</v>
+        <v>3.1852</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0517</v>
+        <v>0.0147</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5744</v>
+        <v>3.1852</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5744</v>
+        <v>3.1852</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0517</v>
+        <v>0.0147</v>
       </c>
       <c r="K12" t="n">
         <v>58</v>
@@ -989,7 +989,7 @@
         <v>83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6261</v>
+        <v>3.1999</v>
       </c>
       <c r="N12" t="n">
         <v>141</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4701</v>
+        <v>3.0814</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1236</v>
+        <v>1.4016</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5765</v>
+        <v>0.7837</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4701</v>
+        <v>3.0814</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7492</v>
+        <v>2.228</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7209</v>
+        <v>0.8534</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7492</v>
+        <v>2.228</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7574</v>
+        <v>2.2468</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7209</v>
+        <v>0.8534</v>
       </c>
       <c r="K13" t="n">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4783</v>
+        <v>3.1002</v>
       </c>
       <c r="N13" t="n">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4661</v>
+        <v>2.5802</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1217</v>
+        <v>1.1736</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5749</v>
+        <v>0.584</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4661</v>
+        <v>2.5802</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1196</v>
+        <v>1.8593</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3465</v>
+        <v>0.7209</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1196</v>
+        <v>1.8593</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1248</v>
+        <v>1.8749</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3465</v>
+        <v>0.7209</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4713</v>
+        <v>2.5958</v>
       </c>
       <c r="N14" t="n">
-        <v>156</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2236</v>
+        <v>2.4619</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0114</v>
+        <v>1.1198</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4769</v>
+        <v>0.5369</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2236</v>
+        <v>2.4619</v>
       </c>
       <c r="F15" t="n">
-        <v>2.602</v>
+        <v>1.1154</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3784</v>
+        <v>1.3465</v>
       </c>
       <c r="H15" t="n">
-        <v>2.602</v>
+        <v>1.1154</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6141</v>
+        <v>1.1248</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3784</v>
+        <v>1.3465</v>
       </c>
       <c r="K15" t="n">
         <v>97</v>
@@ -1127,7 +1127,7 @@
         <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2357</v>
+        <v>2.4713</v>
       </c>
       <c r="N15" t="n">
         <v>156</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9833</v>
+        <v>2.3081</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9021</v>
+        <v>1.0499</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3798</v>
+        <v>0.4756</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9833</v>
+        <v>2.3081</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9567</v>
+        <v>1.2815</v>
       </c>
       <c r="G16" t="n">
         <v>1.0266</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9567</v>
+        <v>1.2815</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9567</v>
+        <v>1.2815</v>
       </c>
       <c r="J16" t="n">
         <v>1.0266</v>
@@ -1173,7 +1173,7 @@
         <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9833</v>
+        <v>2.3081</v>
       </c>
       <c r="N16" t="n">
         <v>161</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9388</v>
+        <v>2.3005</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8819</v>
+        <v>1.0464</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3619</v>
+        <v>0.4726</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9388</v>
+        <v>2.3005</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6183</v>
+        <v>2.6789</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3205</v>
+        <v>-0.3784</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6183</v>
+        <v>2.6789</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6258</v>
+        <v>2.7014</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3205</v>
+        <v>-0.3784</v>
       </c>
       <c r="K17" t="n">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9463</v>
+        <v>2.323</v>
       </c>
       <c r="N17" t="n">
-        <v>213</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7179</v>
+        <v>2.1162</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7814</v>
+        <v>0.9626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2726</v>
+        <v>0.3992</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7179</v>
+        <v>2.1162</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7032</v>
+        <v>2.6572</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0147</v>
+        <v>-0.541</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7032</v>
+        <v>2.6572</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7032</v>
+        <v>2.6796</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0147</v>
+        <v>-0.541</v>
       </c>
       <c r="K18" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="L18" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7179</v>
+        <v>2.1386</v>
       </c>
       <c r="N18" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5312</v>
+        <v>1.939</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6965</v>
+        <v>0.882</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1972</v>
+        <v>0.3286</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5312</v>
+        <v>1.939</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5312</v>
+        <v>1.939</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5312</v>
+        <v>1.939</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5312</v>
+        <v>1.939</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5312</v>
+        <v>1.939</v>
       </c>
       <c r="N19" t="n">
         <v>122</v>
@@ -1320,127 +1320,127 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4559</v>
+        <v>1.9328</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6622</v>
+        <v>0.8792</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1668</v>
+        <v>0.3261</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4559</v>
+        <v>1.9328</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4559</v>
+        <v>1.6123</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.3205</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4559</v>
+        <v>1.6123</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4559</v>
+        <v>1.6258</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.3205</v>
       </c>
       <c r="K20" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4559</v>
+        <v>1.9463</v>
       </c>
       <c r="N20" t="n">
-        <v>132</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4524</v>
+        <v>1.7355</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6606</v>
+        <v>0.7894</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1654</v>
+        <v>0.2475</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4524</v>
+        <v>1.7355</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4936</v>
+        <v>1.7355</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0412</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4936</v>
+        <v>1.7355</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5005</v>
+        <v>1.7355</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0412</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4593</v>
+        <v>1.7355</v>
       </c>
       <c r="N21" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4385</v>
+        <v>1.6235</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6543</v>
+        <v>0.7385</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1598</v>
+        <v>0.2029</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4385</v>
+        <v>1.6235</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9795</v>
+        <v>1.6647</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.541</v>
+        <v>-0.0412</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9795</v>
+        <v>1.6647</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9887</v>
+        <v>1.6787</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.541</v>
+        <v>-0.0412</v>
       </c>
       <c r="K22" t="n">
         <v>97</v>
@@ -1449,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4477</v>
+        <v>1.6375</v>
       </c>
       <c r="N22" t="n">
         <v>156</v>
@@ -1458,127 +1458,127 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4234</v>
+        <v>1.5424</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6475</v>
+        <v>0.7016</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1537</v>
+        <v>0.1706</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4234</v>
+        <v>1.5424</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2136</v>
+        <v>1.8333</v>
       </c>
       <c r="G23" t="n">
-        <v>1.637</v>
+        <v>-0.2909</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2136</v>
+        <v>1.8333</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2136</v>
+        <v>1.8487</v>
       </c>
       <c r="J23" t="n">
-        <v>1.637</v>
+        <v>-0.2909</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4234</v>
+        <v>1.5578</v>
       </c>
       <c r="N23" t="n">
-        <v>161</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3719</v>
+        <v>1.5059</v>
       </c>
       <c r="C24" t="n">
-        <v>0.624</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1329</v>
+        <v>0.156</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3719</v>
+        <v>1.5059</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3719</v>
+        <v>1.8655</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.3596</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3719</v>
+        <v>1.8655</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3719</v>
+        <v>1.8655</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.3596</v>
       </c>
       <c r="K24" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3719</v>
+        <v>1.5059</v>
       </c>
       <c r="N24" t="n">
-        <v>122</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3067</v>
+        <v>1.4234</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5944</v>
+        <v>0.6475</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1065</v>
+        <v>0.1232</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3067</v>
+        <v>1.4234</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0746</v>
+        <v>-0.2136</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2321</v>
+        <v>1.637</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0746</v>
+        <v>-0.2136</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0746</v>
+        <v>-0.2136</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2321</v>
+        <v>1.637</v>
       </c>
       <c r="K25" t="n">
         <v>44</v>
@@ -1587,7 +1587,7 @@
         <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3067</v>
+        <v>1.4234</v>
       </c>
       <c r="N25" t="n">
         <v>161</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2902</v>
+        <v>1.4105</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5869</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0998</v>
+        <v>0.118</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2902</v>
+        <v>1.4105</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4137</v>
+        <v>1.534</v>
       </c>
       <c r="G26" t="n">
         <v>-0.1235</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4137</v>
+        <v>1.534</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4203</v>
+        <v>1.5469</v>
       </c>
       <c r="J26" t="n">
         <v>-0.1235</v>
@@ -1633,7 +1633,7 @@
         <v>69</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2968</v>
+        <v>1.4234</v>
       </c>
       <c r="N26" t="n">
         <v>190</v>
@@ -1642,829 +1642,829 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2855</v>
+        <v>1.3862</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5847</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.098</v>
+        <v>0.1084</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2855</v>
+        <v>1.3862</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5764</v>
+        <v>1.3862</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2909</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5764</v>
+        <v>1.3862</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5837</v>
+        <v>1.3862</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2909</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L27" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2928</v>
+        <v>1.3862</v>
       </c>
       <c r="N27" t="n">
-        <v>213</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2755</v>
+        <v>1.3852</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5802</v>
+        <v>0.6301</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0939</v>
+        <v>0.108</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2755</v>
+        <v>1.3852</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2029</v>
+        <v>1.3852</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0726</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2029</v>
+        <v>1.3852</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2085</v>
+        <v>1.3852</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0726</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L28" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2811</v>
+        <v>1.3852</v>
       </c>
       <c r="N28" t="n">
-        <v>213</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1605</v>
+        <v>1.3734</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5279</v>
+        <v>0.6247</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0475</v>
+        <v>0.1033</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1605</v>
+        <v>1.3734</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5201</v>
+        <v>1.3734</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3596</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5201</v>
+        <v>1.3734</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5201</v>
+        <v>1.3734</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3596</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="L29" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1605</v>
+        <v>1.3734</v>
       </c>
       <c r="N29" t="n">
-        <v>161</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1165</v>
+        <v>1.361</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5079</v>
+        <v>0.6191</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0297</v>
+        <v>0.0983</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1165</v>
+        <v>1.361</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8466</v>
+        <v>1.361</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2699</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8466</v>
+        <v>1.361</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8466</v>
+        <v>1.361</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2699</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="L30" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1165</v>
+        <v>1.361</v>
       </c>
       <c r="N30" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0561</v>
+        <v>1.3564</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4804</v>
+        <v>0.617</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0053</v>
+        <v>0.0965</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0561</v>
+        <v>1.3564</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0561</v>
+        <v>1.0865</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.2699</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0561</v>
+        <v>1.0865</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0561</v>
+        <v>1.0865</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2699</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0561</v>
+        <v>1.3564</v>
       </c>
       <c r="N31" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0345</v>
+        <v>1.3557</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4706</v>
+        <v>0.6167</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0034</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0345</v>
+        <v>1.3557</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0345</v>
+        <v>1.3557</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0345</v>
+        <v>1.3557</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0345</v>
+        <v>1.3557</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0345</v>
+        <v>1.3557</v>
       </c>
       <c r="N32" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9709</v>
+        <v>1.3067</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4416</v>
+        <v>0.5944</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0291</v>
+        <v>0.0767</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9709</v>
+        <v>1.3067</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9709</v>
+        <v>1.0746</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.2321</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9709</v>
+        <v>1.0746</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9709</v>
+        <v>1.0746</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.2321</v>
       </c>
       <c r="K33" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9709</v>
+        <v>1.3067</v>
       </c>
       <c r="N33" t="n">
-        <v>122</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9102</v>
+        <v>1.271</v>
       </c>
       <c r="C34" t="n">
-        <v>0.414</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0537</v>
+        <v>0.0625</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9102</v>
+        <v>1.271</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1335</v>
+        <v>1.1984</v>
       </c>
       <c r="G34" t="n">
-        <v>1.0437</v>
+        <v>0.0726</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1335</v>
+        <v>1.1984</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1335</v>
+        <v>1.2085</v>
       </c>
       <c r="J34" t="n">
-        <v>1.0437</v>
+        <v>0.0726</v>
       </c>
       <c r="K34" t="n">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="L34" t="n">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9102000000000001</v>
+        <v>1.2811</v>
       </c>
       <c r="N34" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8556</v>
+        <v>1.2677</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3892</v>
+        <v>0.5766</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0757</v>
+        <v>0.0611</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8556</v>
+        <v>1.2677</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1885</v>
+        <v>1.2677</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6671</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1885</v>
+        <v>1.2677</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1885</v>
+        <v>1.2677</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6671</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="L35" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8556</v>
+        <v>1.2677</v>
       </c>
       <c r="N35" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2717</v>
+        <v>0.4708</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1801</v>
+        <v>-0.0316</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="N36" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4997</v>
+        <v>0.9709</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2273</v>
+        <v>0.4416</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2195</v>
+        <v>-0.0571</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4997</v>
+        <v>0.9709</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4997</v>
+        <v>0.9709</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4997</v>
+        <v>0.9709</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4997</v>
+        <v>0.9709</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4997</v>
+        <v>0.9709</v>
       </c>
       <c r="N37" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4847</v>
+        <v>0.9102</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2205</v>
+        <v>0.414</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2256</v>
+        <v>-0.0813</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4847</v>
+        <v>0.9102</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4847</v>
+        <v>-0.1335</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4847</v>
+        <v>-0.1335</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4847</v>
+        <v>-0.1335</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="K38" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4847</v>
+        <v>0.9102000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>52</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.476</v>
+        <v>0.8556</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2165</v>
+        <v>0.3892</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2291</v>
+        <v>-0.103</v>
       </c>
       <c r="E39" t="n">
-        <v>0.476</v>
+        <v>0.8556</v>
       </c>
       <c r="F39" t="n">
-        <v>0.476</v>
+        <v>0.1885</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.6671</v>
       </c>
       <c r="H39" t="n">
-        <v>0.476</v>
+        <v>0.1885</v>
       </c>
       <c r="I39" t="n">
-        <v>0.476</v>
+        <v>0.1885</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.6671</v>
       </c>
       <c r="K39" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M39" t="n">
-        <v>0.476</v>
+        <v>0.8556</v>
       </c>
       <c r="N39" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4401</v>
+        <v>0.6712</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2002</v>
+        <v>0.3053</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2436</v>
+        <v>-0.1765</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4401</v>
+        <v>0.6712</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4401</v>
+        <v>0.6712</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4401</v>
+        <v>0.6712</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4401</v>
+        <v>0.6712</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4401</v>
+        <v>0.6712</v>
       </c>
       <c r="N40" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4303</v>
+        <v>0.5184</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1957</v>
+        <v>0.2358</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2475</v>
+        <v>-0.2374</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4303</v>
+        <v>0.5184</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4303</v>
+        <v>0.5184</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4303</v>
+        <v>0.5184</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4303</v>
+        <v>0.5184</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4303</v>
+        <v>0.5184</v>
       </c>
       <c r="N41" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3599</v>
+        <v>0.476</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1637</v>
+        <v>0.2165</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.276</v>
+        <v>-0.2543</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3599</v>
+        <v>0.476</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3599</v>
+        <v>0.476</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3599</v>
+        <v>0.476</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3599</v>
+        <v>0.476</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3599</v>
+        <v>0.476</v>
       </c>
       <c r="N42" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.321</v>
+        <v>0.4133</v>
       </c>
       <c r="C43" t="n">
-        <v>0.146</v>
+        <v>0.188</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2917</v>
+        <v>-0.2793</v>
       </c>
       <c r="E43" t="n">
-        <v>0.321</v>
+        <v>0.4133</v>
       </c>
       <c r="F43" t="n">
-        <v>0.321</v>
+        <v>0.4133</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.321</v>
+        <v>0.4133</v>
       </c>
       <c r="I43" t="n">
-        <v>0.321</v>
+        <v>0.4133</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.321</v>
+        <v>0.4133</v>
       </c>
       <c r="N43" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2912</v>
+        <v>0.321</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1325</v>
+        <v>0.146</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3037</v>
+        <v>-0.316</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2912</v>
+        <v>0.321</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2912</v>
+        <v>0.321</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2912</v>
+        <v>0.321</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2912</v>
+        <v>0.321</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2912</v>
+        <v>0.321</v>
       </c>
       <c r="N44" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
@@ -2480,7 +2480,7 @@
         <v>0.1291</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3067</v>
+        <v>-0.3308</v>
       </c>
       <c r="E45" t="n">
         <v>0.2838</v>
@@ -2516,35 +2516,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2309</v>
+        <v>0.2366</v>
       </c>
       <c r="C46" t="n">
-        <v>0.105</v>
+        <v>0.1076</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3281</v>
+        <v>-0.3496</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2309</v>
+        <v>0.2366</v>
       </c>
       <c r="F46" t="n">
-        <v>0.125</v>
+        <v>0.8794</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1059</v>
+        <v>-0.6428</v>
       </c>
       <c r="H46" t="n">
-        <v>0.125</v>
+        <v>0.8794</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1256</v>
+        <v>0.8868</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1059</v>
+        <v>-0.6428</v>
       </c>
       <c r="K46" t="n">
         <v>121</v>
@@ -2553,7 +2553,7 @@
         <v>69</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2315</v>
+        <v>0.244</v>
       </c>
       <c r="N46" t="n">
         <v>190</v>
@@ -2562,630 +2562,630 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LOVEYY</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1293</v>
+        <v>0.2305</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0588</v>
+        <v>0.1048</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3691</v>
+        <v>-0.3521</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1293</v>
+        <v>0.2305</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1293</v>
+        <v>0.1246</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1293</v>
+        <v>0.1246</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1293</v>
+        <v>0.1256</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="K47" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1293</v>
+        <v>0.2315</v>
       </c>
       <c r="N47" t="n">
-        <v>92</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>LOVEYY</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0297</v>
+        <v>0.16</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0135</v>
+        <v>0.0728</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4094</v>
+        <v>-0.3802</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0297</v>
+        <v>0.16</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4992</v>
+        <v>0.16</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.4695</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4992</v>
+        <v>0.16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4992</v>
+        <v>0.16</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.4695</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L48" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0297</v>
+        <v>0.16</v>
       </c>
       <c r="N48" t="n">
-        <v>224</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0272</v>
+        <v>0.0297</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0124</v>
+        <v>0.0135</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4324</v>
+        <v>-0.4321</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0272</v>
+        <v>0.0297</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0272</v>
+        <v>0.4992</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.4695</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0272</v>
+        <v>0.4992</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0272</v>
+        <v>0.4992</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.4695</v>
       </c>
       <c r="K49" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0272</v>
+        <v>0.0297</v>
       </c>
       <c r="N49" t="n">
-        <v>47</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1521</v>
+        <v>-0.0272</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0692</v>
+        <v>-0.0124</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4828</v>
+        <v>-0.4547</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1521</v>
+        <v>-0.0272</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1521</v>
+        <v>-0.0272</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1521</v>
+        <v>-0.0272</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1521</v>
+        <v>-0.0272</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1521</v>
+        <v>-0.0272</v>
       </c>
       <c r="N50" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1688</v>
+        <v>-0.1093</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0497</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4896</v>
+        <v>-0.4875</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1688</v>
+        <v>-0.1093</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1688</v>
+        <v>-0.1093</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1688</v>
+        <v>-0.1093</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1688</v>
+        <v>-0.1093</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1688</v>
+        <v>-0.1093</v>
       </c>
       <c r="N51" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1521</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0924</v>
+        <v>-0.0692</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5034</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1521</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1521</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1521</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1521</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1521</v>
       </c>
       <c r="N52" t="n">
-        <v>132</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HSK</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1688</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0934</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5043</v>
+        <v>-0.5112</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1688</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1688</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1688</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1688</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1688</v>
       </c>
       <c r="N53" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>HSK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2411</v>
+        <v>-0.2054</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1097</v>
+        <v>-0.0934</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5188</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2411</v>
+        <v>-0.2054</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3484</v>
+        <v>-0.2054</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.5895</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3484</v>
+        <v>-0.2054</v>
       </c>
       <c r="I54" t="n">
-        <v>0.35</v>
+        <v>-0.2054</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.5895</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="L54" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2395</v>
+        <v>-0.2054</v>
       </c>
       <c r="N54" t="n">
-        <v>235</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2673</v>
+        <v>-0.2424</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1216</v>
+        <v>-0.1103</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5293</v>
+        <v>-0.5405</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2673</v>
+        <v>-0.2424</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2673</v>
+        <v>0.3471</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.5895</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2673</v>
+        <v>0.3471</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2673</v>
+        <v>0.35</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.5895</v>
       </c>
       <c r="K55" t="n">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2673</v>
+        <v>-0.2395</v>
       </c>
       <c r="N55" t="n">
-        <v>52</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.335</v>
+        <v>-0.2673</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1524</v>
+        <v>-0.1216</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5567</v>
+        <v>-0.5504</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.335</v>
+        <v>-0.2673</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3078</v>
+        <v>-0.2673</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.6428</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3078</v>
+        <v>-0.2673</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3093</v>
+        <v>-0.2673</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.6428</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="L56" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3335</v>
+        <v>-0.2673</v>
       </c>
       <c r="N56" t="n">
-        <v>190</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Argency</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3674</v>
+        <v>-0.3052</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1671</v>
+        <v>-0.1388</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5698</v>
+        <v>-0.5655</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3674</v>
+        <v>-0.3052</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3674</v>
+        <v>-0.3052</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3674</v>
+        <v>-0.3052</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3674</v>
+        <v>-0.3052</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3674</v>
+        <v>-0.3052</v>
       </c>
       <c r="N57" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>smike</t>
+          <t>Argency</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4306</v>
+        <v>-0.3674</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1959</v>
+        <v>-0.1671</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5903</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4306</v>
+        <v>-0.3674</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4306</v>
+        <v>-0.3674</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4306</v>
+        <v>-0.3674</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4306</v>
+        <v>-0.3674</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4306</v>
+        <v>-0.3674</v>
       </c>
       <c r="N58" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>smike</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5678</v>
+        <v>-0.4306</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2583</v>
+        <v>-0.1959</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.6155</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5678</v>
+        <v>-0.4306</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5678</v>
+        <v>-0.4306</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5678</v>
+        <v>-0.4306</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5678</v>
+        <v>-0.4306</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5678</v>
+        <v>-0.4306</v>
       </c>
       <c r="N59" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5979</v>
+        <v>-0.4419</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.272</v>
+        <v>-0.201</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6629</v>
+        <v>-0.62</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5979</v>
+        <v>-0.4419</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5979</v>
+        <v>-0.4419</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5979</v>
+        <v>-0.4419</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5979</v>
+        <v>-0.4419</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5979</v>
+        <v>-0.4419</v>
       </c>
       <c r="N60" t="n">
         <v>90</v>
@@ -3206,277 +3206,277 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7015</v>
+        <v>-0.5678</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3191</v>
+        <v>-0.2583</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7048</v>
+        <v>-0.6701</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7015</v>
+        <v>-0.5678</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7015</v>
+        <v>-0.5678</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7015</v>
+        <v>-0.5678</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7015</v>
+        <v>-0.5678</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7015</v>
+        <v>-0.5678</v>
       </c>
       <c r="N61" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7369</v>
+        <v>-0.7015</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3352</v>
+        <v>-0.3191</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7191</v>
+        <v>-0.7234</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7369</v>
+        <v>-0.7015</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7369</v>
+        <v>-0.7015</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7369</v>
+        <v>-0.7015</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7369</v>
+        <v>-0.7015</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7369</v>
+        <v>-0.7015</v>
       </c>
       <c r="N62" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7621</v>
+        <v>-0.7088</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3467</v>
+        <v>-0.3224</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7292</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7621</v>
+        <v>-0.7088</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7621</v>
+        <v>0.8462</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-1.555</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7621</v>
+        <v>0.8462</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7621</v>
+        <v>0.8462</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-1.555</v>
       </c>
       <c r="K63" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7621</v>
+        <v>-0.7088</v>
       </c>
       <c r="N63" t="n">
-        <v>61</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7744</v>
+        <v>-0.7369</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3522</v>
+        <v>-0.3352</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7342</v>
+        <v>-0.7375</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7744</v>
+        <v>-0.7369</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7744</v>
+        <v>-0.7369</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7744</v>
+        <v>-0.7369</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7744</v>
+        <v>-0.7369</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7744</v>
+        <v>-0.7369</v>
       </c>
       <c r="N64" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7872</v>
+        <v>-0.7621</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3581</v>
+        <v>-0.3467</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7872</v>
+        <v>-0.7621</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7678</v>
+        <v>-0.7621</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.555</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7678</v>
+        <v>-0.7621</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7678</v>
+        <v>-0.7621</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.555</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="L65" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7871999999999999</v>
+        <v>-0.7621</v>
       </c>
       <c r="N65" t="n">
-        <v>224</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7926</v>
+        <v>-0.7744</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3605</v>
+        <v>-0.3522</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7416</v>
+        <v>-0.7524</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7926</v>
+        <v>-0.7744</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7926</v>
+        <v>-0.7744</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7926</v>
+        <v>-0.7744</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7926</v>
+        <v>-0.7744</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7926</v>
+        <v>-0.7744</v>
       </c>
       <c r="N66" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67">
@@ -3492,7 +3492,7 @@
         <v>-0.3821</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7607</v>
+        <v>-0.7786</v>
       </c>
       <c r="E67" t="n">
         <v>-0.84</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4167</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7915</v>
+        <v>-0.8089</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9162</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4175</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7921</v>
+        <v>-0.8096</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9177999999999999</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4273</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8182</v>
       </c>
       <c r="E70" t="n">
         <v>-0.9395</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4486</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8198</v>
+        <v>-0.8368</v>
       </c>
       <c r="E71" t="n">
         <v>-0.9862</v>
@@ -3722,7 +3722,7 @@
         <v>-0.52</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8832</v>
+        <v>-0.8994</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1432</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1595</v>
+        <v>-1.157</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5274</v>
+        <v>-0.5263</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8898</v>
+        <v>-0.9049</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1595</v>
+        <v>-1.157</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6526</v>
+        <v>-0.6501</v>
       </c>
       <c r="G73" t="n">
         <v>-0.5069</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6526</v>
+        <v>-0.6501</v>
       </c>
       <c r="I73" t="n">
         <v>-0.6556</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.264</v>
+        <v>-1.2624</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5749</v>
+        <v>-0.5742</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9469</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.264</v>
+        <v>-1.2624</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.4134</v>
+        <v>-0.4118</v>
       </c>
       <c r="G74" t="n">
         <v>-0.8506</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.4134</v>
+        <v>-0.4118</v>
       </c>
       <c r="I74" t="n">
         <v>-0.4153</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.429</v>
+        <v>-1.4244</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.65</v>
+        <v>-0.6479</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9986</v>
+        <v>-1.0114</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.429</v>
+        <v>-1.4244</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.238</v>
+        <v>-1.2334</v>
       </c>
       <c r="G75" t="n">
         <v>-0.191</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.238</v>
+        <v>-1.2334</v>
       </c>
       <c r="I75" t="n">
         <v>-1.2438</v>
@@ -3906,7 +3906,7 @@
         <v>-0.6525</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0008</v>
+        <v>-1.0154</v>
       </c>
       <c r="E76" t="n">
         <v>-1.4344</v>
@@ -3952,7 +3952,7 @@
         <v>-0.6938</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0375</v>
+        <v>-1.0516</v>
       </c>
       <c r="E77" t="n">
         <v>-1.5253</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.8198</v>
+        <v>-1.8159</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8278</v>
+        <v>-0.826</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1565</v>
+        <v>-1.1674</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8198</v>
+        <v>-1.8159</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.0408</v>
+        <v>-1.0369</v>
       </c>
       <c r="G78" t="n">
         <v>-0.779</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.0408</v>
+        <v>-1.0369</v>
       </c>
       <c r="I78" t="n">
         <v>-1.0456</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8334</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1615</v>
+        <v>-1.1738</v>
       </c>
       <c r="E79" t="n">
         <v>-1.8321</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3392</v>
+        <v>-2.3322</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.064</v>
+        <v>-1.0608</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3663</v>
+        <v>-1.3731</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3392</v>
+        <v>-2.3322</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.8899</v>
+        <v>-1.8829</v>
       </c>
       <c r="G80" t="n">
         <v>-0.4493</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.8899</v>
+        <v>-1.8829</v>
       </c>
       <c r="I80" t="n">
         <v>-1.8987</v>
@@ -4136,7 +4136,7 @@
         <v>-1.1164</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4128</v>
+        <v>-1.4217</v>
       </c>
       <c r="E81" t="n">
         <v>-2.4543</v>

--- a/database/event/2325/event_2325_evp_summary.xlsx
+++ b/database/event/2325/event_2325_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.574</v>
+        <v>5.7349</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5354</v>
+        <v>2.6086</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8784</v>
+        <v>1.9864</v>
       </c>
       <c r="E2" t="n">
-        <v>5.574</v>
+        <v>5.7349</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8975</v>
+        <v>1.8741</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6765</v>
+        <v>3.8608</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8975</v>
+        <v>1.8741</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8975</v>
+        <v>1.8741</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6765</v>
+        <v>3.8608</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>183</v>
       </c>
       <c r="M2" t="n">
-        <v>5.574</v>
+        <v>5.7349</v>
       </c>
       <c r="N2" t="n">
         <v>230</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0207</v>
+        <v>5.3208</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2837</v>
+        <v>2.4202</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6286</v>
+        <v>1.7979</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0207</v>
+        <v>5.3208</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4838</v>
+        <v>1.4124</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5369</v>
+        <v>3.9084</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4838</v>
+        <v>1.4124</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4838</v>
+        <v>1.4124</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5369</v>
+        <v>3.9084</v>
       </c>
       <c r="K3" t="n">
         <v>47</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0207</v>
+        <v>5.3208</v>
       </c>
       <c r="N3" t="n">
         <v>230</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0588</v>
+        <v>4.4803</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8462</v>
+        <v>2.0379</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1943</v>
+        <v>1.4153</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0588</v>
+        <v>4.4803</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9599</v>
+        <v>2.1136</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0989</v>
+        <v>2.3667</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9599</v>
+        <v>2.1136</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9599</v>
+        <v>2.1136</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0989</v>
+        <v>2.3667</v>
       </c>
       <c r="K4" t="n">
         <v>45</v>
@@ -621,7 +621,7 @@
         <v>179</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0588</v>
+        <v>4.4803</v>
       </c>
       <c r="N4" t="n">
         <v>224</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8456</v>
+        <v>4.0371</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7492</v>
+        <v>1.8363</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0981</v>
+        <v>1.2136</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8456</v>
+        <v>4.0371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8396</v>
+        <v>0.837</v>
       </c>
       <c r="G5" t="n">
-        <v>3.006</v>
+        <v>3.2001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8396</v>
+        <v>0.837</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8396</v>
+        <v>0.837</v>
       </c>
       <c r="J5" t="n">
-        <v>3.006</v>
+        <v>3.2001</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>183</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8456</v>
+        <v>4.0371</v>
       </c>
       <c r="N5" t="n">
         <v>230</v>
@@ -676,277 +676,277 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.832</v>
+        <v>3.901</v>
       </c>
       <c r="C6" t="n">
-        <v>1.743</v>
+        <v>1.7744</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0919</v>
+        <v>1.1516</v>
       </c>
       <c r="E6" t="n">
-        <v>3.832</v>
+        <v>3.901</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7106</v>
+        <v>0.358</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1214</v>
+        <v>3.543</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7106</v>
+        <v>0.358</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7106</v>
+        <v>0.358</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1214</v>
+        <v>3.543</v>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L6" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>3.832</v>
+        <v>3.901</v>
       </c>
       <c r="N6" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7559</v>
+        <v>3.7155</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7084</v>
+        <v>1.69</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0576</v>
+        <v>1.0672</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7559</v>
+        <v>3.7155</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5051</v>
+        <v>2.4696</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2508</v>
+        <v>1.2459</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5051</v>
+        <v>2.6803</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5051</v>
+        <v>2.6803</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2508</v>
+        <v>1.2459</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7559</v>
+        <v>3.9262</v>
       </c>
       <c r="N7" t="n">
-        <v>161</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6902</v>
+        <v>3.6966</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6785</v>
+        <v>1.6815</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0279</v>
+        <v>1.0586</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6902</v>
+        <v>3.6966</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3739</v>
+        <v>2.3642</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3163</v>
+        <v>1.3324</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3739</v>
+        <v>2.4496</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3739</v>
+        <v>2.4496</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3163</v>
+        <v>1.3324</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L8" t="n">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6902</v>
+        <v>3.782</v>
       </c>
       <c r="N8" t="n">
-        <v>230</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3281</v>
+        <v>3.277</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5138</v>
+        <v>1.4906</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8645</v>
+        <v>0.8676</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3281</v>
+        <v>3.277</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4949</v>
+        <v>1.7035</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.5735</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4949</v>
+        <v>1.7035</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5975</v>
+        <v>1.7474</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.5735</v>
       </c>
       <c r="K9" t="n">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4307</v>
+        <v>3.3209</v>
       </c>
       <c r="N9" t="n">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.21</v>
+        <v>3.2535</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4601</v>
+        <v>1.4799</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8111</v>
+        <v>0.8569</v>
       </c>
       <c r="E10" t="n">
-        <v>3.21</v>
+        <v>3.2535</v>
       </c>
       <c r="F10" t="n">
-        <v>1.771</v>
+        <v>2.333</v>
       </c>
       <c r="G10" t="n">
-        <v>1.439</v>
+        <v>0.9205</v>
       </c>
       <c r="H10" t="n">
-        <v>1.771</v>
+        <v>2.3812</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8438</v>
+        <v>2.4426</v>
       </c>
       <c r="J10" t="n">
-        <v>1.439</v>
+        <v>0.9205</v>
       </c>
       <c r="K10" t="n">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="L10" t="n">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2828</v>
+        <v>3.3631</v>
       </c>
       <c r="N10" t="n">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1164</v>
+        <v>3.155</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4175</v>
+        <v>1.4351</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7689</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1164</v>
+        <v>3.155</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0674</v>
+        <v>0.9658</v>
       </c>
       <c r="G11" t="n">
-        <v>1.049</v>
+        <v>2.1892</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0674</v>
+        <v>0.9658</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0674</v>
+        <v>0.9907</v>
       </c>
       <c r="J11" t="n">
-        <v>1.049</v>
+        <v>2.1892</v>
       </c>
       <c r="K11" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="L11" t="n">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1164</v>
+        <v>3.1799</v>
       </c>
       <c r="N11" t="n">
-        <v>141</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0759</v>
+        <v>3.1539</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3991</v>
+        <v>1.4346</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7506</v>
+        <v>0.8115</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0759</v>
+        <v>3.1539</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3753</v>
+        <v>2.3065</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7006</v>
+        <v>0.8474</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3753</v>
+        <v>2.3233</v>
       </c>
       <c r="I12" t="n">
-        <v>2.473</v>
+        <v>2.3832</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7006</v>
+        <v>0.8474</v>
       </c>
       <c r="K12" t="n">
         <v>95</v>
@@ -989,7 +989,7 @@
         <v>140</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1736</v>
+        <v>3.2306</v>
       </c>
       <c r="N12" t="n">
         <v>235</v>
@@ -998,323 +998,323 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9811</v>
+        <v>3.1097</v>
       </c>
       <c r="C13" t="n">
-        <v>1.356</v>
+        <v>1.4145</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7078</v>
+        <v>0.7914</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9811</v>
+        <v>3.1097</v>
       </c>
       <c r="F13" t="n">
-        <v>1.003</v>
+        <v>1.982</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9781</v>
+        <v>1.1277</v>
       </c>
       <c r="H13" t="n">
-        <v>1.003</v>
+        <v>1.982</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0442</v>
+        <v>1.982</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9781</v>
+        <v>1.1277</v>
       </c>
       <c r="K13" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="L13" t="n">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0223</v>
+        <v>3.1097</v>
       </c>
       <c r="N13" t="n">
-        <v>235</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.93</v>
+        <v>2.7063</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3328</v>
+        <v>1.231</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6847</v>
+        <v>0.6078</v>
       </c>
       <c r="E14" t="n">
-        <v>2.93</v>
+        <v>2.7063</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7835</v>
+        <v>1.3065</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1465</v>
+        <v>1.3998</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7835</v>
+        <v>1.3065</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7835</v>
+        <v>1.3402</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1465</v>
+        <v>1.3998</v>
       </c>
       <c r="K14" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="N14" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.608</v>
+        <v>2.6455</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1863</v>
+        <v>1.2033</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5394</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.608</v>
+        <v>2.6455</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3449</v>
+        <v>2.4974</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2631</v>
+        <v>0.1481</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3449</v>
+        <v>2.7411</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4002</v>
+        <v>2.7411</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2631</v>
+        <v>0.1481</v>
       </c>
       <c r="K15" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6633</v>
+        <v>2.8892</v>
       </c>
       <c r="N15" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.579</v>
+        <v>2.2855</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1731</v>
+        <v>1.0396</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5263</v>
+        <v>0.4162</v>
       </c>
       <c r="E16" t="n">
-        <v>2.579</v>
+        <v>2.2855</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8066</v>
+        <v>1.3109</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2276</v>
+        <v>0.9746</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8066</v>
+        <v>1.3109</v>
       </c>
       <c r="I16" t="n">
-        <v>2.922</v>
+        <v>1.3109</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2276</v>
+        <v>0.9746</v>
       </c>
       <c r="K16" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="L16" t="n">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6944</v>
+        <v>2.2855</v>
       </c>
       <c r="N16" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2986</v>
+        <v>2.2535</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0456</v>
+        <v>1.025</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3997</v>
+        <v>0.4016</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2986</v>
+        <v>2.2535</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2986</v>
+        <v>2.4996</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.2461</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2986</v>
+        <v>2.7459</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2986</v>
+        <v>2.8167</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.2461</v>
       </c>
       <c r="K17" t="n">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2986</v>
+        <v>2.5706</v>
       </c>
       <c r="N17" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2633</v>
+        <v>2.2456</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0295</v>
+        <v>1.0214</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3838</v>
+        <v>0.398</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2633</v>
+        <v>2.2456</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5909</v>
+        <v>2.2456</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3276</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5909</v>
+        <v>2.2456</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6975</v>
+        <v>2.2456</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3276</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="L18" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3699</v>
+        <v>2.2456</v>
       </c>
       <c r="N18" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2008</v>
+        <v>2.0455</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0011</v>
+        <v>0.9304</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3555</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2008</v>
+        <v>2.0455</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3284</v>
+        <v>2.3983</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8724</v>
+        <v>-0.3528</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3284</v>
+        <v>2.5242</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3284</v>
+        <v>2.5892</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8724</v>
+        <v>-0.3528</v>
       </c>
       <c r="K19" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="L19" t="n">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2008</v>
+        <v>2.2364</v>
       </c>
       <c r="N19" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9647</v>
+        <v>2.0131</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8937</v>
+        <v>0.9157</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2489</v>
+        <v>0.2922</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9647</v>
+        <v>2.0131</v>
       </c>
       <c r="F20" t="n">
-        <v>1.798</v>
+        <v>1.7431</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1667</v>
+        <v>0.27</v>
       </c>
       <c r="H20" t="n">
-        <v>1.798</v>
+        <v>1.7431</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8719</v>
+        <v>1.788</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1667</v>
+        <v>0.27</v>
       </c>
       <c r="K20" t="n">
         <v>141</v>
@@ -1357,7 +1357,7 @@
         <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0386</v>
+        <v>2.058</v>
       </c>
       <c r="N20" t="n">
         <v>213</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9532</v>
+        <v>1.9221</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8884</v>
+        <v>0.8743</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2438</v>
+        <v>0.2508</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9532</v>
+        <v>1.9221</v>
       </c>
       <c r="F21" t="n">
-        <v>1.952</v>
+        <v>1.8453</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0012</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.952</v>
+        <v>1.8453</v>
       </c>
       <c r="I21" t="n">
-        <v>1.952</v>
+        <v>1.8453</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0012</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>44</v>
@@ -1403,7 +1403,7 @@
         <v>117</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9532</v>
+        <v>1.9221</v>
       </c>
       <c r="N21" t="n">
         <v>161</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9081</v>
+        <v>1.8385</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8679</v>
+        <v>0.8363</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2234</v>
+        <v>0.2127</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9081</v>
+        <v>1.8385</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0128</v>
+        <v>1.9544</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1047</v>
+        <v>-0.1159</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0128</v>
+        <v>1.9544</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0956</v>
+        <v>2.0048</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1047</v>
+        <v>-0.1159</v>
       </c>
       <c r="K22" t="n">
         <v>141</v>
@@ -1449,7 +1449,7 @@
         <v>72</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9909</v>
+        <v>1.8889</v>
       </c>
       <c r="N22" t="n">
         <v>213</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8789</v>
+        <v>1.796</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8546</v>
+        <v>0.8169</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2102</v>
+        <v>0.1934</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8789</v>
+        <v>1.796</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8789</v>
+        <v>1.796</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8789</v>
+        <v>1.796</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8789</v>
+        <v>1.796</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8789</v>
+        <v>1.796</v>
       </c>
       <c r="N23" t="n">
         <v>132</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6782</v>
+        <v>1.7053</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7634</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1196</v>
+        <v>0.1521</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6782</v>
+        <v>1.7053</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6782</v>
+        <v>1.7053</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6782</v>
+        <v>1.7053</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6782</v>
+        <v>1.7053</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6782</v>
+        <v>1.7053</v>
       </c>
       <c r="N24" t="n">
         <v>122</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6389</v>
+        <v>1.687</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7674</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1019</v>
+        <v>0.1438</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6389</v>
+        <v>1.687</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6353</v>
+        <v>1.687</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6353</v>
+        <v>1.687</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7026</v>
+        <v>1.687</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="L25" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7062</v>
+        <v>1.687</v>
       </c>
       <c r="N25" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6131</v>
+        <v>1.6486</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7337</v>
+        <v>0.7499</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0902</v>
+        <v>0.1263</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6131</v>
+        <v>1.6486</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6131</v>
+        <v>1.167</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.4816</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6131</v>
+        <v>1.167</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6131</v>
+        <v>1.167</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.4816</v>
       </c>
       <c r="K26" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6131</v>
+        <v>1.6486</v>
       </c>
       <c r="N26" t="n">
-        <v>122</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6121</v>
+        <v>1.5865</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7333</v>
+        <v>0.7216</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0898</v>
+        <v>0.098</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6121</v>
+        <v>1.5865</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1953</v>
+        <v>1.5849</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4168</v>
+        <v>0.0016</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1953</v>
+        <v>1.5849</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1953</v>
+        <v>1.6257</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4168</v>
+        <v>0.0016</v>
       </c>
       <c r="K27" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="L27" t="n">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6121</v>
+        <v>1.6273</v>
       </c>
       <c r="N27" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6118</v>
+        <v>1.5116</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7332</v>
+        <v>0.6876</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0896</v>
+        <v>0.0639</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6118</v>
+        <v>1.5116</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6118</v>
+        <v>1.5116</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6118</v>
+        <v>1.5116</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6118</v>
+        <v>1.5116</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6118</v>
+        <v>1.5116</v>
       </c>
       <c r="N28" t="n">
         <v>90</v>
@@ -1734,139 +1734,139 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5053</v>
+        <v>1.4992</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6847</v>
+        <v>0.6819</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0416</v>
+        <v>0.0583</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5053</v>
+        <v>1.4992</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5748</v>
+        <v>-0.0042</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.06950000000000001</v>
+        <v>1.5034</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5748</v>
+        <v>-0.0042</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6396</v>
+        <v>-0.0042</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.06950000000000001</v>
+        <v>1.5034</v>
       </c>
       <c r="K29" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="L29" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5701</v>
+        <v>1.4992</v>
       </c>
       <c r="N29" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3792</v>
+        <v>1.4254</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6273</v>
+        <v>0.6484</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0154</v>
+        <v>0.0247</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3792</v>
+        <v>1.4254</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2337</v>
+        <v>1.4419</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1455</v>
+        <v>-0.0165</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2337</v>
+        <v>1.4419</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2844</v>
+        <v>1.4791</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1455</v>
+        <v>-0.0165</v>
       </c>
       <c r="K30" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="L30" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4299</v>
+        <v>1.4626</v>
       </c>
       <c r="N30" t="n">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3673</v>
+        <v>1.389</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6219</v>
+        <v>0.6318</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0207</v>
+        <v>0.0081</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3673</v>
+        <v>1.389</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3673</v>
+        <v>1.2667</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1223</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3673</v>
+        <v>1.2667</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3673</v>
+        <v>1.2993</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1223</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3673</v>
+        <v>1.4216</v>
       </c>
       <c r="N31" t="n">
-        <v>132</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3604</v>
+        <v>1.3477</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6188</v>
+        <v>0.613</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0239</v>
+        <v>-0.0107</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3604</v>
+        <v>1.3477</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1359</v>
+        <v>1.0959</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2245</v>
+        <v>0.2518</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1359</v>
+        <v>1.0959</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1359</v>
+        <v>1.0959</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2245</v>
+        <v>0.2518</v>
       </c>
       <c r="K32" t="n">
         <v>58</v>
@@ -1909,7 +1909,7 @@
         <v>83</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3604</v>
+        <v>1.3477</v>
       </c>
       <c r="N32" t="n">
         <v>141</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3127</v>
+        <v>1.3106</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5971</v>
+        <v>0.5961</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0454</v>
+        <v>-0.0276</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3127</v>
+        <v>1.3106</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3475</v>
+        <v>0.3381</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9725</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3475</v>
+        <v>0.3381</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3475</v>
+        <v>0.3381</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9725</v>
       </c>
       <c r="K33" t="n">
         <v>47</v>
@@ -1955,7 +1955,7 @@
         <v>183</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3127</v>
+        <v>1.3106</v>
       </c>
       <c r="N33" t="n">
         <v>230</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3125</v>
+        <v>1.2975</v>
       </c>
       <c r="C34" t="n">
-        <v>0.597</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0455</v>
+        <v>-0.0336</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3125</v>
+        <v>1.2975</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0414</v>
+        <v>1.2975</v>
       </c>
       <c r="G34" t="n">
-        <v>1.3539</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0414</v>
+        <v>1.2975</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0414</v>
+        <v>1.2975</v>
       </c>
       <c r="J34" t="n">
-        <v>1.3539</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="L34" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3125</v>
+        <v>1.2975</v>
       </c>
       <c r="N34" t="n">
-        <v>161</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.284</v>
+        <v>1.2791</v>
       </c>
       <c r="C35" t="n">
-        <v>0.584</v>
+        <v>0.5818</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0584</v>
+        <v>-0.0419</v>
       </c>
       <c r="E35" t="n">
-        <v>1.284</v>
+        <v>1.2791</v>
       </c>
       <c r="F35" t="n">
-        <v>1.284</v>
+        <v>1.2791</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.284</v>
+        <v>1.2791</v>
       </c>
       <c r="I35" t="n">
-        <v>1.284</v>
+        <v>1.2791</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.284</v>
+        <v>1.2791</v>
       </c>
       <c r="N35" t="n">
         <v>92</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.2574</v>
+        <v>1.2197</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5719</v>
+        <v>0.5548</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0704</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2574</v>
+        <v>1.2197</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2574</v>
+        <v>1.2197</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.2574</v>
+        <v>1.2197</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2574</v>
+        <v>1.2197</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.2574</v>
+        <v>1.2197</v>
       </c>
       <c r="N36" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.2216</v>
+        <v>1.2141</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5557</v>
+        <v>0.5523</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2216</v>
+        <v>1.2141</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2216</v>
+        <v>1.2141</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2216</v>
+        <v>1.2141</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2216</v>
+        <v>1.2141</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2216</v>
+        <v>1.2141</v>
       </c>
       <c r="N37" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.2206</v>
+        <v>1.212</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5552</v>
+        <v>0.5513</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0725</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2206</v>
+        <v>1.212</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2206</v>
+        <v>1.212</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2206</v>
+        <v>1.212</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2206</v>
+        <v>1.212</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.2206</v>
+        <v>1.212</v>
       </c>
       <c r="N38" t="n">
         <v>122</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.06</v>
+        <v>1.2061</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4822</v>
+        <v>0.5486</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1595</v>
+        <v>-0.0752</v>
       </c>
       <c r="E39" t="n">
-        <v>1.06</v>
+        <v>1.2061</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0479</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>1.0121</v>
+        <v>1.1278</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0479</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0479</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>1.0121</v>
+        <v>1.1278</v>
       </c>
       <c r="K39" t="n">
         <v>45</v>
@@ -2231,7 +2231,7 @@
         <v>179</v>
       </c>
       <c r="M39" t="n">
-        <v>1.06</v>
+        <v>1.2061</v>
       </c>
       <c r="N39" t="n">
         <v>224</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9769</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4444</v>
+        <v>0.4234</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.197</v>
+        <v>-0.2004</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9769</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9769</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9769</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9769</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9769</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>52</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7643</v>
+        <v>0.7119</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3477</v>
+        <v>0.3238</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.293</v>
+        <v>-0.3001</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7643</v>
+        <v>0.7119</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7643</v>
+        <v>0.7119</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7643</v>
+        <v>0.7119</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7643</v>
+        <v>0.7119</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7643</v>
+        <v>0.7119</v>
       </c>
       <c r="N41" t="n">
         <v>52</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7237</v>
+        <v>0.6582</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3292</v>
+        <v>0.2994</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3113</v>
+        <v>-0.3246</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7237</v>
+        <v>0.6582</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7237</v>
+        <v>0.6582</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7237</v>
+        <v>0.6582</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7237</v>
+        <v>0.6582</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7237</v>
+        <v>0.6582</v>
       </c>
       <c r="N42" t="n">
         <v>61</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6957</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3164</v>
+        <v>0.2854</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3239</v>
+        <v>-0.3386</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6957</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0515</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.3558</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.0515</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0947</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.3558</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="L43" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7389</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6637</v>
+        <v>0.597</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3019</v>
+        <v>0.2716</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3384</v>
+        <v>-0.3524</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6637</v>
+        <v>0.597</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6637</v>
+        <v>0.9674</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6637</v>
+        <v>0.9674</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6637</v>
+        <v>0.9923</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="K44" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6637</v>
+        <v>0.6218999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5425</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2468</v>
+        <v>0.2598</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3931</v>
+        <v>-0.3642</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5425</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6496</v>
+        <v>0.6744</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1071</v>
+        <v>-0.1033</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6496</v>
+        <v>0.6744</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6496</v>
+        <v>0.6744</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.1071</v>
+        <v>-0.1033</v>
       </c>
       <c r="K45" t="n">
         <v>45</v>
@@ -2507,7 +2507,7 @@
         <v>179</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5425</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="N45" t="n">
         <v>224</v>
@@ -2516,323 +2516,323 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LOVEYY</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5232</v>
+        <v>0.4864</v>
       </c>
       <c r="C46" t="n">
-        <v>0.238</v>
+        <v>0.2212</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4018</v>
+        <v>-0.4028</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5232</v>
+        <v>0.4864</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5232</v>
+        <v>0.2714</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5232</v>
+        <v>0.2714</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5232</v>
+        <v>0.2784</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="K46" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5232</v>
+        <v>0.4933999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>92</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.493</v>
+        <v>0.4575</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2242</v>
+        <v>0.2081</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4154</v>
+        <v>-0.4159</v>
       </c>
       <c r="E47" t="n">
-        <v>0.493</v>
+        <v>0.4575</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3052</v>
+        <v>0.4575</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1878</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3052</v>
+        <v>0.4575</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3178</v>
+        <v>0.4575</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1878</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="L47" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5056</v>
+        <v>0.4575</v>
       </c>
       <c r="N47" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>LOVEYY</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4162</v>
+        <v>0.4464</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1893</v>
+        <v>0.2031</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4501</v>
+        <v>-0.421</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4162</v>
+        <v>0.4464</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4162</v>
+        <v>0.4464</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4162</v>
+        <v>0.4464</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4162</v>
+        <v>0.4464</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4162</v>
+        <v>0.4464</v>
       </c>
       <c r="N48" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3583</v>
+        <v>0.4065</v>
       </c>
       <c r="C49" t="n">
-        <v>0.163</v>
+        <v>0.1849</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4763</v>
+        <v>-0.4392</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3583</v>
+        <v>0.4065</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3583</v>
+        <v>0.6001</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.1936</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3583</v>
+        <v>0.6001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3583</v>
+        <v>0.6156</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.1936</v>
       </c>
       <c r="K49" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M49" t="n">
-        <v>0.3583</v>
+        <v>0.422</v>
       </c>
       <c r="N49" t="n">
-        <v>47</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3522</v>
+        <v>0.3339</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1602</v>
+        <v>0.1519</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.479</v>
+        <v>-0.4722</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3522</v>
+        <v>0.3339</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.3339</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.236</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.3339</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.3339</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.236</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="L50" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3764000000000001</v>
+        <v>0.3339</v>
       </c>
       <c r="N50" t="n">
-        <v>235</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.2416</v>
+        <v>0.1736</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1099</v>
+        <v>0.079</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5289</v>
+        <v>-0.5452</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2416</v>
+        <v>0.1736</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2416</v>
+        <v>0.1736</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2416</v>
+        <v>0.1736</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2416</v>
+        <v>0.1736</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2416</v>
+        <v>0.1736</v>
       </c>
       <c r="N51" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2061</v>
+        <v>0.1545</v>
       </c>
       <c r="C52" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.545</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2061</v>
+        <v>0.1545</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2061</v>
+        <v>0.1545</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2061</v>
+        <v>0.1545</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2061</v>
+        <v>0.1545</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2061</v>
+        <v>0.1545</v>
       </c>
       <c r="N52" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1155</v>
+        <v>0.0658</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0525</v>
+        <v>0.0299</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5859</v>
+        <v>-0.5942</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1155</v>
+        <v>0.0658</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1155</v>
+        <v>0.0658</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1155</v>
+        <v>0.0658</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1155</v>
+        <v>0.0658</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1155</v>
+        <v>0.0658</v>
       </c>
       <c r="N53" t="n">
         <v>90</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0863</v>
+        <v>0.0181</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0393</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5991</v>
+        <v>-0.616</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0863</v>
+        <v>0.0181</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0863</v>
+        <v>0.0181</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0863</v>
+        <v>0.0181</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0863</v>
+        <v>0.0181</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0863</v>
+        <v>0.0181</v>
       </c>
       <c r="N54" t="n">
         <v>90</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0048</v>
+        <v>-0.0271</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0022</v>
+        <v>-0.0123</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6358</v>
+        <v>-0.6365</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0048</v>
+        <v>-0.0271</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0048</v>
+        <v>-0.0271</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0048</v>
+        <v>-0.0271</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0048</v>
+        <v>-0.0271</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0048</v>
+        <v>-0.0271</v>
       </c>
       <c r="N55" t="n">
         <v>44</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0384</v>
+        <v>-0.0437</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0175</v>
+        <v>-0.0199</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6553</v>
+        <v>-0.6441</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0384</v>
+        <v>-0.0437</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0384</v>
+        <v>-0.0437</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0384</v>
+        <v>-0.0437</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0384</v>
+        <v>-0.0437</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0384</v>
+        <v>-0.0437</v>
       </c>
       <c r="N56" t="n">
         <v>52</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1024</v>
+        <v>-0.127</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0466</v>
+        <v>-0.0578</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6842</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1024</v>
+        <v>-0.127</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1024</v>
+        <v>-0.127</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1024</v>
+        <v>-0.127</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1024</v>
+        <v>-0.127</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1024</v>
+        <v>-0.127</v>
       </c>
       <c r="N57" t="n">
         <v>61</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1308</v>
+        <v>-0.1588</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0595</v>
+        <v>-0.0722</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.6965</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1308</v>
+        <v>-0.1588</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1308</v>
+        <v>-0.1588</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1308</v>
+        <v>-0.1588</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1308</v>
+        <v>-0.1588</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1308</v>
+        <v>-0.1588</v>
       </c>
       <c r="N58" t="n">
         <v>47</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1927</v>
+        <v>-0.1933</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0877</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.725</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1927</v>
+        <v>-0.1933</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1927</v>
+        <v>-0.1933</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1927</v>
+        <v>-0.1933</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1927</v>
+        <v>-0.1933</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1927</v>
+        <v>-0.1933</v>
       </c>
       <c r="N59" t="n">
         <v>52</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2492</v>
+        <v>-0.3115</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1134</v>
+        <v>-0.1417</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.766</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2492</v>
+        <v>-0.3115</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2492</v>
+        <v>-0.3115</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2492</v>
+        <v>-0.3115</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2492</v>
+        <v>-0.3115</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2492</v>
+        <v>-0.3115</v>
       </c>
       <c r="N60" t="n">
         <v>44</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3387</v>
+        <v>-0.3344</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1541</v>
+        <v>-0.1521</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7909</v>
+        <v>-0.7764</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3387</v>
+        <v>-0.3344</v>
       </c>
       <c r="F61" t="n">
-        <v>1.0371</v>
+        <v>1.0103</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.3758</v>
+        <v>-1.3447</v>
       </c>
       <c r="H61" t="n">
-        <v>1.0371</v>
+        <v>1.0103</v>
       </c>
       <c r="I61" t="n">
-        <v>1.0371</v>
+        <v>1.0103</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.3758</v>
+        <v>-1.3447</v>
       </c>
       <c r="K61" t="n">
         <v>45</v>
@@ -3243,7 +3243,7 @@
         <v>179</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3387</v>
+        <v>-0.3344</v>
       </c>
       <c r="N61" t="n">
         <v>224</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3737</v>
+        <v>-0.406</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.17</v>
+        <v>-0.1847</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8067</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3737</v>
+        <v>-0.406</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3737</v>
+        <v>-0.406</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3737</v>
+        <v>-0.406</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3737</v>
+        <v>-0.406</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3737</v>
+        <v>-0.406</v>
       </c>
       <c r="N62" t="n">
         <v>61</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.399</v>
+        <v>-0.4096</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1815</v>
+        <v>-0.1863</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8181</v>
+        <v>-0.8107</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.399</v>
+        <v>-0.4096</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.399</v>
+        <v>-0.4096</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.399</v>
+        <v>-0.4096</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.399</v>
+        <v>-0.4096</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.399</v>
+        <v>-0.4096</v>
       </c>
       <c r="N63" t="n">
         <v>92</v>
@@ -3344,93 +3344,93 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4115</v>
+        <v>-0.4449</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1872</v>
+        <v>-0.2024</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8238</v>
+        <v>-0.8267</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4115</v>
+        <v>-0.4449</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.101</v>
+        <v>-0.4449</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.3105</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.101</v>
+        <v>-0.4449</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1052</v>
+        <v>-0.4449</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.3105</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="L64" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4157</v>
+        <v>-0.4449</v>
       </c>
       <c r="N64" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4389</v>
+        <v>-0.4463</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1996</v>
+        <v>-0.203</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.8274</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.4389</v>
+        <v>-0.4463</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4389</v>
+        <v>-0.1153</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-0.331</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.4389</v>
+        <v>-0.1153</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4389</v>
+        <v>-0.1183</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>-0.331</v>
       </c>
       <c r="K65" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.4389</v>
+        <v>-0.4493</v>
       </c>
       <c r="N65" t="n">
-        <v>44</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66">
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4933</v>
+        <v>-0.521</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2244</v>
+        <v>-0.237</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8607</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4933</v>
+        <v>-0.521</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4933</v>
+        <v>-0.521</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4933</v>
+        <v>-0.521</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4933</v>
+        <v>-0.521</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4933</v>
+        <v>-0.521</v>
       </c>
       <c r="N66" t="n">
         <v>61</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5004</v>
+        <v>-0.5295</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2276</v>
+        <v>-0.2409</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8639</v>
+        <v>-0.8652</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5004</v>
+        <v>-0.5295</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5004</v>
+        <v>-0.5295</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5004</v>
+        <v>-0.5295</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5004</v>
+        <v>-0.5295</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5004</v>
+        <v>-0.5295</v>
       </c>
       <c r="N67" t="n">
         <v>61</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5129</v>
+        <v>-0.5389</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2333</v>
+        <v>-0.2451</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8696</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5129</v>
+        <v>-0.5389</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5129</v>
+        <v>-0.5389</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5129</v>
+        <v>-0.5389</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5129</v>
+        <v>-0.5389</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5129</v>
+        <v>-0.5389</v>
       </c>
       <c r="N68" t="n">
         <v>47</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5349</v>
+        <v>-0.5612</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2433</v>
+        <v>-0.2553</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.8797</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5349</v>
+        <v>-0.5612</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5349</v>
+        <v>-0.5612</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5349</v>
+        <v>-0.5612</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5349</v>
+        <v>-0.5612</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5349</v>
+        <v>-0.5612</v>
       </c>
       <c r="N69" t="n">
         <v>52</v>
@@ -3624,31 +3624,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6159</v>
+        <v>-0.6514</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2802</v>
+        <v>-0.2963</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9161</v>
+        <v>-0.9207</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6159</v>
+        <v>-0.6514</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.5406</v>
+        <v>-0.5649</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0784</v>
+        <v>-0.0887</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5406</v>
+        <v>-0.5649</v>
       </c>
       <c r="K70" t="n">
         <v>97</v>
@@ -3657,7 +3657,7 @@
         <v>59</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.619</v>
+        <v>-0.6536</v>
       </c>
       <c r="N70" t="n">
         <v>156</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6407</v>
+        <v>-0.6728</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2914</v>
+        <v>-0.306</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9273</v>
+        <v>-0.9305</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6407</v>
+        <v>-0.6728</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6407</v>
+        <v>-0.6728</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6407</v>
+        <v>-0.6728</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6407</v>
+        <v>-0.6728</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6407</v>
+        <v>-0.6728</v>
       </c>
       <c r="N71" t="n">
         <v>92</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6506</v>
+        <v>-0.6872</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2959</v>
+        <v>-0.3126</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9317</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6506</v>
+        <v>-0.6872</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6506</v>
+        <v>-0.6872</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6506</v>
+        <v>-0.6872</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6506</v>
+        <v>-0.6872</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6506</v>
+        <v>-0.6872</v>
       </c>
       <c r="N72" t="n">
         <v>44</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7018</v>
+        <v>-0.7204</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3192</v>
+        <v>-0.3277</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9548</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7018</v>
+        <v>-0.7204</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7018</v>
+        <v>-0.7204</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7018</v>
+        <v>-0.7204</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7018</v>
+        <v>-0.7204</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7018</v>
+        <v>-0.7204</v>
       </c>
       <c r="N73" t="n">
         <v>47</v>
@@ -3804,139 +3804,139 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rindA</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7963</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.3497</v>
+        <v>-0.3622</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9851</v>
+        <v>-0.9867</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7963</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7688</v>
+        <v>-0.9443</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7688</v>
+        <v>-0.9443</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7688</v>
+        <v>-0.9686</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="K74" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7688</v>
+        <v>-0.8206</v>
       </c>
       <c r="N74" t="n">
-        <v>44</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tb</t>
+          <t>rindA</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.8539</v>
+        <v>-0.8002</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.3884</v>
+        <v>-0.364</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0235</v>
+        <v>-0.9885</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.8539</v>
+        <v>-0.8002</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.8539</v>
+        <v>-0.8002</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.8539</v>
+        <v>-0.8002</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8539</v>
+        <v>-0.8002</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.8539</v>
+        <v>-0.8002</v>
       </c>
       <c r="N75" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>tb</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8964</v>
+        <v>-0.8813</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4077</v>
+        <v>-0.4009</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0427</v>
+        <v>-1.0254</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.8964</v>
+        <v>-0.8813</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9938</v>
+        <v>-0.8813</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0974</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9938</v>
+        <v>-0.8813</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0347</v>
+        <v>-0.8813</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0974</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L76" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9372999999999999</v>
+        <v>-0.8813</v>
       </c>
       <c r="N76" t="n">
-        <v>235</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77">
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.4663</v>
+        <v>-0.4682</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1008</v>
+        <v>-1.0928</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="N77" t="n">
         <v>132</v>
@@ -3992,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.1141</v>
+        <v>-1.038</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5068</v>
+        <v>-0.4721</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.141</v>
+        <v>-1.0967</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.1141</v>
+        <v>-1.038</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.6342</v>
+        <v>-0.615</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.4799</v>
+        <v>-0.423</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.6342</v>
+        <v>-0.615</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.6603</v>
+        <v>-0.6308</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.4799</v>
+        <v>-0.423</v>
       </c>
       <c r="K78" t="n">
         <v>141</v>
@@ -4025,7 +4025,7 @@
         <v>72</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.1402</v>
+        <v>-1.0538</v>
       </c>
       <c r="N78" t="n">
         <v>213</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.4252</v>
+        <v>-1.4282</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6483</v>
+        <v>-0.6496</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2814</v>
+        <v>-1.2743</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.4252</v>
+        <v>-1.4282</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.1977</v>
+        <v>-1.1847</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.2275</v>
+        <v>-0.2435</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.1977</v>
+        <v>-1.1847</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.247</v>
+        <v>-1.2152</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.2275</v>
+        <v>-0.2435</v>
       </c>
       <c r="K79" t="n">
         <v>121</v>
@@ -4071,7 +4071,7 @@
         <v>69</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.4745</v>
+        <v>-1.4587</v>
       </c>
       <c r="N79" t="n">
         <v>190</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.5817</v>
+        <v>-1.4518</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7195</v>
+        <v>-0.6604</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3521</v>
+        <v>-1.2851</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.5817</v>
+        <v>-1.4518</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.5147</v>
+        <v>-1.3974</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.067</v>
+        <v>-0.0544</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.5147</v>
+        <v>-1.3974</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.5147</v>
+        <v>-1.3974</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.067</v>
+        <v>-0.0544</v>
       </c>
       <c r="K80" t="n">
         <v>58</v>
@@ -4117,7 +4117,7 @@
         <v>83</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.5817</v>
+        <v>-1.4518</v>
       </c>
       <c r="N80" t="n">
         <v>141</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1054</v>
+        <v>-2.0015</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9577</v>
+        <v>-0.9104</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5885</v>
+        <v>-1.5353</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1054</v>
+        <v>-2.0015</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.3799</v>
+        <v>-1.2545</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.7255</v>
+        <v>-0.747</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.3799</v>
+        <v>-1.2545</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3799</v>
+        <v>-1.2545</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.7255</v>
+        <v>-0.747</v>
       </c>
       <c r="K81" t="n">
         <v>58</v>
@@ -4163,7 +4163,7 @@
         <v>83</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.1054</v>
+        <v>-2.0015</v>
       </c>
       <c r="N81" t="n">
         <v>141</v>
@@ -4269,10 +4269,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1266</v>
+        <v>1.1253</v>
       </c>
       <c r="J2" t="n">
-        <v>25.9118</v>
+        <v>25.8819</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1266</v>
+        <v>1.1253</v>
       </c>
       <c r="J3" t="n">
-        <v>25.9118</v>
+        <v>25.8819</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0242</v>
+        <v>0.9798</v>
       </c>
       <c r="J4" t="n">
-        <v>23.5566</v>
+        <v>22.5354</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4848</v>
+        <v>0.483</v>
       </c>
       <c r="J5" t="n">
-        <v>11.1504</v>
+        <v>11.109</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>1.03</v>
       </c>
       <c r="I6" t="n">
-        <v>0.053</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.219</v>
+        <v>1.8883</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1999</v>
+        <v>0.1921</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5977</v>
+        <v>4.4183</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1679</v>
+        <v>-0.1861</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.8617</v>
+        <v>-4.2803</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1881</v>
+        <v>-0.2064</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.3263</v>
+        <v>-4.7472</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1979</v>
+        <v>-0.2162</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.5517</v>
+        <v>-4.9726</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.52</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4809</v>
+        <v>-0.4897</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.0607</v>
+        <v>-11.2631</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.41</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0317</v>
+        <v>0.9802</v>
       </c>
       <c r="J12" t="n">
-        <v>41.268</v>
+        <v>39.208</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6397</v>
+        <v>0.6148</v>
       </c>
       <c r="J13" t="n">
-        <v>25.588</v>
+        <v>24.592</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.18</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5181</v>
+        <v>0.5058</v>
       </c>
       <c r="J14" t="n">
-        <v>20.724</v>
+        <v>20.232</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0945</v>
+        <v>0.1111</v>
       </c>
       <c r="J15" t="n">
-        <v>3.78</v>
+        <v>4.444</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.95</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2402</v>
+        <v>-0.2301</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.608000000000001</v>
+        <v>-9.204000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.41</v>
+        <v>0.4054</v>
       </c>
       <c r="J17" t="n">
-        <v>16.4</v>
+        <v>16.216</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.145</v>
+        <v>0.152</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.98</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0343</v>
+        <v>-0.0415</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.372</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2056</v>
+        <v>-0.2198</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.224</v>
+        <v>-8.792</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2056</v>
+        <v>-0.2198</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.224</v>
+        <v>-8.792</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9472</v>
+        <v>1.0391</v>
       </c>
       <c r="J22" t="n">
-        <v>27.4688</v>
+        <v>30.1339</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.23</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5167</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>14.9843</v>
+        <v>16.5619</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1332</v>
+        <v>0.1475</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8628</v>
+        <v>4.2775</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0985</v>
+        <v>0.1139</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8565</v>
+        <v>3.3031</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4741</v>
+        <v>-0.4477</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.7489</v>
+        <v>-12.9833</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3568</v>
+        <v>0.3704</v>
       </c>
       <c r="J27" t="n">
-        <v>10.3472</v>
+        <v>10.7416</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1455</v>
+        <v>0.1523</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2195</v>
+        <v>4.4167</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0608</v>
+        <v>-0.0707</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.7632</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.12</v>
+        <v>-0.1331</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.48</v>
+        <v>-3.8599</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2556</v>
+        <v>-0.2695</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.4124</v>
+        <v>-7.8155</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2872</v>
+        <v>18.9252</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.2</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4985</v>
+        <v>0.5445</v>
       </c>
       <c r="J33" t="n">
-        <v>13.958</v>
+        <v>15.246</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.01</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0508</v>
+        <v>0.057</v>
       </c>
       <c r="J34" t="n">
-        <v>1.4224</v>
+        <v>1.596</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5446</v>
       </c>
       <c r="J35" t="n">
-        <v>-16.0748</v>
+        <v>-15.2488</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.78</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6782</v>
+        <v>-0.6369</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.9896</v>
+        <v>-17.8332</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5823</v>
+        <v>0.6521</v>
       </c>
       <c r="J37" t="n">
-        <v>16.3044</v>
+        <v>18.2588</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6303</v>
       </c>
       <c r="J38" t="n">
-        <v>15.764</v>
+        <v>17.6484</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0716</v>
+        <v>-0.0789</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.0048</v>
+        <v>-2.2092</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1652</v>
+        <v>-0.1764</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.6256</v>
+        <v>-4.9392</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2581</v>
+        <v>-0.2694</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.2268</v>
+        <v>-7.5432</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.04</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1558</v>
+        <v>0.1535</v>
       </c>
       <c r="J42" t="n">
-        <v>3.895</v>
+        <v>3.8375</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0333</v>
+        <v>0.0241</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8325</v>
+        <v>0.6025</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0333</v>
+        <v>0.0241</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8325</v>
+        <v>0.6025</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3284</v>
+        <v>-0.3433</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.5825</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.57</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4407</v>
+        <v>-0.4508</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.0175</v>
+        <v>-11.27</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0958</v>
+        <v>1.2014</v>
       </c>
       <c r="J47" t="n">
-        <v>27.395</v>
+        <v>30.035</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6919</v>
+        <v>0.7682</v>
       </c>
       <c r="J48" t="n">
-        <v>17.2975</v>
+        <v>19.205</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5591</v>
+        <v>0.6217</v>
       </c>
       <c r="J49" t="n">
-        <v>13.9775</v>
+        <v>15.5425</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1104</v>
+        <v>0.1316</v>
       </c>
       <c r="J50" t="n">
-        <v>2.76</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6576</v>
+        <v>-0.6082</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.44</v>
+        <v>-15.205</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3196</v>
+        <v>0.3116</v>
       </c>
       <c r="J52" t="n">
-        <v>7.3508</v>
+        <v>7.1668</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1115</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.2011</v>
+        <v>-2.5645</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1907</v>
+        <v>-0.2084</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.3861</v>
+        <v>-4.7932</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2786</v>
+        <v>-0.2953</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.4078</v>
+        <v>-6.7919</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3831</v>
+        <v>-0.3962</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.811299999999999</v>
+        <v>-9.1126</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.69</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0685</v>
+        <v>1.1773</v>
       </c>
       <c r="J57" t="n">
-        <v>24.5755</v>
+        <v>27.0779</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.55</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8998</v>
+        <v>0.9973</v>
       </c>
       <c r="J58" t="n">
-        <v>20.6954</v>
+        <v>22.9379</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.3</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5888</v>
+        <v>0.6574</v>
       </c>
       <c r="J59" t="n">
-        <v>13.5424</v>
+        <v>15.1202</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1.3</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5888</v>
+        <v>0.6574</v>
       </c>
       <c r="J60" t="n">
-        <v>13.5424</v>
+        <v>15.1202</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4934</v>
+        <v>-0.4555</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.3482</v>
+        <v>-10.4765</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.14</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3376</v>
+        <v>0.3408</v>
       </c>
       <c r="J62" t="n">
-        <v>9.1152</v>
+        <v>9.201599999999999</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2412</v>
+        <v>0.2438</v>
       </c>
       <c r="J63" t="n">
-        <v>6.5124</v>
+        <v>6.5826</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.5542</v>
+        <v>-2.8971</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1282</v>
+        <v>-0.1423</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.4614</v>
+        <v>-3.8421</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3675</v>
+        <v>-0.379</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.922499999999999</v>
+        <v>-10.233</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7904</v>
       </c>
       <c r="J67" t="n">
-        <v>19.3644</v>
+        <v>21.3408</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.32</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7156</v>
       </c>
       <c r="J68" t="n">
-        <v>17.5149</v>
+        <v>19.3212</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5071</v>
+        <v>0.5593</v>
       </c>
       <c r="J69" t="n">
-        <v>13.6917</v>
+        <v>15.1011</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4943</v>
+        <v>-0.4674</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.3461</v>
+        <v>-12.6198</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.628</v>
+        <v>-0.5874</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.956</v>
+        <v>-15.8598</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4104</v>
+        <v>0.464</v>
       </c>
       <c r="J72" t="n">
-        <v>11.4912</v>
+        <v>12.992</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3761</v>
+        <v>0.4171</v>
       </c>
       <c r="J73" t="n">
-        <v>10.5308</v>
+        <v>11.6788</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1427</v>
+        <v>0.1594</v>
       </c>
       <c r="J74" t="n">
-        <v>3.9956</v>
+        <v>4.4632</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0818</v>
+        <v>0.0969</v>
       </c>
       <c r="J75" t="n">
-        <v>2.2904</v>
+        <v>2.7132</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0146</v>
+        <v>-0.0112</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.4088</v>
+        <v>-0.3136</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1955</v>
+        <v>0.203</v>
       </c>
       <c r="J77" t="n">
-        <v>5.474</v>
+        <v>5.684</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.09</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1796</v>
+        <v>0.1873</v>
       </c>
       <c r="J78" t="n">
-        <v>5.0288</v>
+        <v>5.2444</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1299</v>
+        <v>0.1378</v>
       </c>
       <c r="J79" t="n">
-        <v>3.6372</v>
+        <v>3.8584</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.962</v>
+        <v>-4.3484</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3418</v>
+        <v>-0.3538</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.570399999999999</v>
+        <v>-9.9064</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.34</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5687</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>15.9236</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1049</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.5564</v>
+        <v>-2.9372</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1765</v>
+        <v>-0.1926</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.942</v>
+        <v>-5.3928</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3149</v>
+        <v>-0.3292</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.8172</v>
+        <v>-9.217599999999999</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.68</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3434</v>
+        <v>-0.3568</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.6152</v>
+        <v>-9.990399999999999</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7565</v>
+        <v>0.8386</v>
       </c>
       <c r="J87" t="n">
-        <v>21.182</v>
+        <v>23.4808</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6784</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>18.9952</v>
+        <v>21.098</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.21</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4779</v>
+        <v>0.5304</v>
       </c>
       <c r="J89" t="n">
-        <v>13.3812</v>
+        <v>14.8512</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>1.12</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3419</v>
+        <v>0.3551</v>
       </c>
       <c r="J90" t="n">
-        <v>9.5732</v>
+        <v>9.9428</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2357</v>
+        <v>0.2503</v>
       </c>
       <c r="J91" t="n">
-        <v>6.5996</v>
+        <v>7.0084</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4623</v>
+        <v>0.5092</v>
       </c>
       <c r="J92" t="n">
-        <v>13.869</v>
+        <v>15.276</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4326</v>
+        <v>0.4757</v>
       </c>
       <c r="J93" t="n">
-        <v>12.978</v>
+        <v>14.271</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4326</v>
+        <v>0.4757</v>
       </c>
       <c r="J94" t="n">
-        <v>12.978</v>
+        <v>14.271</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2917</v>
+        <v>0.296</v>
       </c>
       <c r="J95" t="n">
-        <v>8.750999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0835</v>
+        <v>-0.0794</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.505</v>
+        <v>-2.382</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4165</v>
+        <v>0.4588</v>
       </c>
       <c r="J97" t="n">
-        <v>12.495</v>
+        <v>13.764</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0654</v>
+        <v>0.073</v>
       </c>
       <c r="J98" t="n">
-        <v>1.962</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0208</v>
+        <v>-0.0254</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.624</v>
+        <v>-0.762</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1005</v>
+        <v>-0.1118</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.015</v>
+        <v>-3.354</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.86</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1779</v>
+        <v>-0.1913</v>
       </c>
       <c r="J101" t="n">
-        <v>-5.337</v>
+        <v>-5.739</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.84</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3164</v>
+        <v>1.4272</v>
       </c>
       <c r="J102" t="n">
-        <v>38.1756</v>
+        <v>41.3888</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2006</v>
+        <v>0.2111</v>
       </c>
       <c r="J103" t="n">
-        <v>5.8174</v>
+        <v>6.1219</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1015</v>
+        <v>0.116</v>
       </c>
       <c r="J104" t="n">
-        <v>2.9435</v>
+        <v>3.364</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4147</v>
+        <v>-0.3942</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.0263</v>
+        <v>-11.4318</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5528</v>
+        <v>-0.5193</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.0312</v>
+        <v>-15.0597</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.65</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8466</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>24.5514</v>
+        <v>27.289</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.96</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0618</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.7922</v>
+        <v>-2.0706</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2068</v>
+        <v>-0.2207</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.9972</v>
+        <v>-6.4003</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2271</v>
+        <v>-0.241</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.5859</v>
+        <v>-6.989</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3627</v>
+        <v>-0.3736</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.5183</v>
+        <v>-10.8344</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3784</v>
+        <v>0.3898</v>
       </c>
       <c r="J112" t="n">
-        <v>8.3248</v>
+        <v>8.5756</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.86</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.143</v>
+        <v>-0.1644</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.146</v>
+        <v>-3.6168</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2559</v>
+        <v>-0.2758</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.6298</v>
+        <v>-6.0676</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.47</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.516</v>
+        <v>-0.5243</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.352</v>
+        <v>-11.5346</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.41</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5716</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.5752</v>
+        <v>-12.6742</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>2.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8394</v>
+        <v>0.9656</v>
       </c>
       <c r="J117" t="n">
-        <v>18.4668</v>
+        <v>21.2432</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.47</v>
       </c>
       <c r="I118" t="n">
-        <v>0.469</v>
+        <v>0.5383</v>
       </c>
       <c r="J118" t="n">
-        <v>10.318</v>
+        <v>11.8426</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.23</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3006</v>
+        <v>0.3216</v>
       </c>
       <c r="J119" t="n">
-        <v>6.6132</v>
+        <v>7.0752</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>1.15</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2</v>
+        <v>0.2229</v>
       </c>
       <c r="J120" t="n">
-        <v>4.4</v>
+        <v>4.9038</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1246</v>
+        <v>-0.1275</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.7412</v>
+        <v>-2.805</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6268</v>
       </c>
       <c r="J122" t="n">
-        <v>15.82</v>
+        <v>17.5504</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5097</v>
+        <v>0.5651</v>
       </c>
       <c r="J123" t="n">
-        <v>14.2716</v>
+        <v>15.8228</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5097</v>
+        <v>0.5651</v>
       </c>
       <c r="J124" t="n">
-        <v>14.2716</v>
+        <v>15.8228</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.13</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3649</v>
+        <v>0.387</v>
       </c>
       <c r="J125" t="n">
-        <v>10.2172</v>
+        <v>10.836</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>1.1</v>
       </c>
       <c r="I126" t="n">
-        <v>0.3042</v>
+        <v>0.3115</v>
       </c>
       <c r="J126" t="n">
-        <v>8.5176</v>
+        <v>8.722</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7769</v>
+        <v>0.86</v>
       </c>
       <c r="J127" t="n">
-        <v>21.7532</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2509</v>
+        <v>0.251</v>
       </c>
       <c r="J128" t="n">
-        <v>7.0252</v>
+        <v>7.028</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.73</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2972</v>
+        <v>-0.3117</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.3216</v>
+        <v>-8.727600000000001</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3068</v>
+        <v>-0.321</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.590400000000001</v>
+        <v>-8.988</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.48</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.529</v>
+        <v>-0.5332</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.812</v>
+        <v>-14.9296</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.5</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8459</v>
+        <v>0.9378</v>
       </c>
       <c r="J132" t="n">
-        <v>18.6098</v>
+        <v>20.6316</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8837</v>
       </c>
       <c r="J133" t="n">
-        <v>17.5098</v>
+        <v>19.4414</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.24</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5713</v>
       </c>
       <c r="J134" t="n">
-        <v>11.2772</v>
+        <v>12.5686</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>1.18</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4268</v>
+        <v>0.4747</v>
       </c>
       <c r="J135" t="n">
-        <v>9.3896</v>
+        <v>10.4434</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I136" t="n">
-        <v>0.35</v>
+        <v>0.3697</v>
       </c>
       <c r="J136" t="n">
-        <v>7.7</v>
+        <v>8.1334</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I137" t="n">
-        <v>0.0192</v>
+        <v>-0.0012</v>
       </c>
       <c r="J137" t="n">
-        <v>0.4224</v>
+        <v>-0.0264</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>0.91</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0985</v>
+        <v>-0.1165</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.167</v>
+        <v>-2.563</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1437</v>
+        <v>-0.1624</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.1614</v>
+        <v>-3.5728</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1437</v>
+        <v>-0.1624</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.1614</v>
+        <v>-3.5728</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.33</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6496</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.3374</v>
+        <v>-14.2912</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8892</v>
+        <v>0.9832</v>
       </c>
       <c r="J142" t="n">
-        <v>21.3408</v>
+        <v>23.5968</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7376</v>
+        <v>0.8193</v>
       </c>
       <c r="J143" t="n">
-        <v>17.7024</v>
+        <v>19.6632</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4598</v>
+        <v>0.511</v>
       </c>
       <c r="J144" t="n">
-        <v>11.0352</v>
+        <v>12.264</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.13</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3542</v>
+        <v>0.3745</v>
       </c>
       <c r="J145" t="n">
-        <v>8.5008</v>
+        <v>8.988</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>1.09</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2569</v>
+        <v>0.2719</v>
       </c>
       <c r="J146" t="n">
-        <v>6.1656</v>
+        <v>6.5256</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1892</v>
+        <v>0.1843</v>
       </c>
       <c r="J147" t="n">
-        <v>4.5408</v>
+        <v>4.4232</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1805</v>
+        <v>-0.1981</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.332</v>
+        <v>-4.7544</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.82</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1997</v>
+        <v>-0.2176</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.7928</v>
+        <v>-5.2224</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2193</v>
+        <v>-0.2371</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.2632</v>
+        <v>-5.6904</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.68</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3349</v>
+        <v>-0.3501</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.037599999999999</v>
+        <v>-8.4024</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0698</v>
+        <v>0.0521</v>
       </c>
       <c r="J152" t="n">
-        <v>1.6752</v>
+        <v>1.2504</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.68</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3196</v>
+        <v>-0.3382</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.6704</v>
+        <v>-8.1168</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3196</v>
+        <v>-0.3382</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.6704</v>
+        <v>-8.1168</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3289</v>
+        <v>-0.3472</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.8936</v>
+        <v>-8.332800000000001</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.63</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3663</v>
+        <v>-0.3831</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.7912</v>
+        <v>-9.1944</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.64</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5779</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>13.8696</v>
+        <v>15.9552</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3909</v>
+        <v>0.4422</v>
       </c>
       <c r="J158" t="n">
-        <v>9.381600000000001</v>
+        <v>10.6128</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3276</v>
+        <v>0.3491</v>
       </c>
       <c r="J159" t="n">
-        <v>7.8624</v>
+        <v>8.378399999999999</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.25</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3276</v>
+        <v>0.3491</v>
       </c>
       <c r="J160" t="n">
-        <v>7.8624</v>
+        <v>8.378399999999999</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.13</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1795</v>
+        <v>0.2011</v>
       </c>
       <c r="J161" t="n">
-        <v>4.308</v>
+        <v>4.8264</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>0.959</v>
+        <v>1.0633</v>
       </c>
       <c r="J162" t="n">
-        <v>20.139</v>
+        <v>22.3293</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8398</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>17.6358</v>
+        <v>19.635</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>0.732</v>
+        <v>0.8174</v>
       </c>
       <c r="J164" t="n">
-        <v>15.372</v>
+        <v>17.1654</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.3</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5803</v>
+        <v>0.6501</v>
       </c>
       <c r="J165" t="n">
-        <v>12.1863</v>
+        <v>13.6521</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>1.26</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5261</v>
+        <v>0.5899</v>
       </c>
       <c r="J166" t="n">
-        <v>11.0481</v>
+        <v>12.3879</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.71</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.2707</v>
+        <v>-0.295</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.6847</v>
+        <v>-6.195</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.63</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3485</v>
+        <v>-0.3694</v>
       </c>
       <c r="J168" t="n">
-        <v>-7.3185</v>
+        <v>-7.7574</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.6</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3746</v>
+        <v>-0.3945</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.8666</v>
+        <v>-8.2845</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.58</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3923</v>
+        <v>-0.4115</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.238300000000001</v>
+        <v>-8.641500000000001</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.52</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4477</v>
+        <v>-0.4637</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.4017</v>
+        <v>-9.7377</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.31</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8378</v>
+        <v>0.788</v>
       </c>
       <c r="J172" t="n">
-        <v>25.134</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7432</v>
+        <v>0.705</v>
       </c>
       <c r="J173" t="n">
-        <v>22.296</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7432</v>
+        <v>0.705</v>
       </c>
       <c r="J174" t="n">
-        <v>22.296</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.91</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3572</v>
+        <v>-0.3412</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.716</v>
+        <v>-10.236</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3572</v>
+        <v>-0.3412</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.716</v>
+        <v>-10.236</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.2</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4426</v>
+        <v>0.4366</v>
       </c>
       <c r="J177" t="n">
-        <v>13.278</v>
+        <v>13.098</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4426</v>
+        <v>0.4366</v>
       </c>
       <c r="J178" t="n">
-        <v>13.278</v>
+        <v>13.098</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>0.96</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0621</v>
+        <v>-0.0717</v>
       </c>
       <c r="J179" t="n">
-        <v>-1.863</v>
+        <v>-2.151</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.89</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1439</v>
+        <v>-0.1572</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.317</v>
+        <v>-4.716</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3443</v>
+        <v>-0.3558</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.329</v>
+        <v>-10.674</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2063</v>
+        <v>1.1828</v>
       </c>
       <c r="J182" t="n">
-        <v>22.9197</v>
+        <v>22.4732</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.57</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1826</v>
+        <v>1.1574</v>
       </c>
       <c r="J183" t="n">
-        <v>22.4694</v>
+        <v>21.9906</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.44</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0253</v>
+        <v>0.9806</v>
       </c>
       <c r="J184" t="n">
-        <v>19.4807</v>
+        <v>18.6314</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.31</v>
       </c>
       <c r="I185" t="n">
-        <v>0.771</v>
+        <v>0.742</v>
       </c>
       <c r="J185" t="n">
-        <v>14.649</v>
+        <v>14.098</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>1.28</v>
       </c>
       <c r="I186" t="n">
-        <v>0.7028</v>
+        <v>0.6818</v>
       </c>
       <c r="J186" t="n">
-        <v>13.3532</v>
+        <v>12.9542</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>0.76</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2427</v>
+        <v>-0.2637</v>
       </c>
       <c r="J187" t="n">
-        <v>-4.6113</v>
+        <v>-5.0103</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2525</v>
+        <v>-0.2733</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.7975</v>
+        <v>-5.1927</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.75</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2525</v>
+        <v>-0.2733</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.7975</v>
+        <v>-5.1927</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.67</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3257</v>
+        <v>-0.3447</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.1883</v>
+        <v>-6.5493</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.62</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3722</v>
+        <v>-0.3893</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.0718</v>
+        <v>-7.3967</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3256</v>
+        <v>0.3151</v>
       </c>
       <c r="J192" t="n">
-        <v>7.4888</v>
+        <v>7.2473</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.96</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0439</v>
+        <v>-0.0577</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.0097</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2869</v>
+        <v>-0.3036</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.5987</v>
+        <v>-6.9828</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2965</v>
+        <v>-0.313</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.8195</v>
+        <v>-7.199</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.66</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3535</v>
+        <v>-0.3681</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.1305</v>
+        <v>-8.4663</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.4</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0058</v>
+        <v>0.9493</v>
       </c>
       <c r="J197" t="n">
-        <v>23.1334</v>
+        <v>21.8339</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.36</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9296</v>
+        <v>0.8729</v>
       </c>
       <c r="J198" t="n">
-        <v>21.3808</v>
+        <v>20.0767</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4375</v>
+        <v>0.4339</v>
       </c>
       <c r="J199" t="n">
-        <v>10.0625</v>
+        <v>9.979699999999999</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.303</v>
+        <v>0.3106</v>
       </c>
       <c r="J200" t="n">
-        <v>6.969</v>
+        <v>7.1438</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.98</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1442</v>
+        <v>-0.1345</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.3166</v>
+        <v>-3.0935</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5193</v>
+        <v>0.5262</v>
       </c>
       <c r="J202" t="n">
-        <v>13.5018</v>
+        <v>13.6812</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4965</v>
+        <v>0.5047</v>
       </c>
       <c r="J203" t="n">
-        <v>12.909</v>
+        <v>13.1222</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1971</v>
+        <v>0.2144</v>
       </c>
       <c r="J204" t="n">
-        <v>5.1246</v>
+        <v>5.5744</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.02</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0281</v>
+        <v>0.0404</v>
       </c>
       <c r="J205" t="n">
-        <v>0.7306</v>
+        <v>1.0504</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1519</v>
+        <v>-0.1607</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.9494</v>
+        <v>-4.1782</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4007</v>
+        <v>0.4019</v>
       </c>
       <c r="J207" t="n">
-        <v>10.4182</v>
+        <v>10.4494</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1213</v>
+        <v>0.1314</v>
       </c>
       <c r="J208" t="n">
-        <v>3.1538</v>
+        <v>3.4164</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.001</v>
+        <v>-0.0007</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.026</v>
+        <v>-0.0182</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1017</v>
+        <v>-0.1128</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.6442</v>
+        <v>-2.9328</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.84</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2002</v>
+        <v>-0.2133</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.2052</v>
+        <v>-5.5458</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.32</v>
+        <v>0.3196</v>
       </c>
       <c r="J212" t="n">
-        <v>8.960000000000001</v>
+        <v>8.9488</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.017</v>
+        <v>-0.0226</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.476</v>
+        <v>-0.6328</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0327</v>
+        <v>-0.0402</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.9156</v>
+        <v>-1.1256</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0838</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.3464</v>
+        <v>-2.6796</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.73</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3022</v>
+        <v>-0.3156</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.461600000000001</v>
+        <v>-8.8368</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.6</v>
       </c>
       <c r="I217" t="n">
-        <v>1.254</v>
+        <v>1.2271</v>
       </c>
       <c r="J217" t="n">
-        <v>35.112</v>
+        <v>34.3588</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.23</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6226</v>
+        <v>0.6032</v>
       </c>
       <c r="J218" t="n">
-        <v>17.4328</v>
+        <v>16.8896</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5991</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>16.7748</v>
+        <v>16.3016</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>1.14</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3991</v>
+        <v>0.4016</v>
       </c>
       <c r="J220" t="n">
-        <v>11.1748</v>
+        <v>11.2448</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>1.08</v>
       </c>
       <c r="I221" t="n">
-        <v>0.2319</v>
+        <v>0.2477</v>
       </c>
       <c r="J221" t="n">
-        <v>6.4932</v>
+        <v>6.9356</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1657</v>
+        <v>-0.1934</v>
       </c>
       <c r="J222" t="n">
-        <v>-3.314</v>
+        <v>-3.868</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.72</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2626</v>
+        <v>-0.2869</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.252</v>
+        <v>-5.738</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.64</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3407</v>
+        <v>-0.3617</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.814</v>
+        <v>-7.234</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4028</v>
+        <v>-0.4211</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.055999999999999</v>
+        <v>-8.422000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.34</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6201</v>
+        <v>-0.6233</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.402</v>
+        <v>-12.466</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.71</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7975</v>
+        <v>0.7937</v>
       </c>
       <c r="J227" t="n">
-        <v>15.95</v>
+        <v>15.874</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.51</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5969</v>
+        <v>0.6067</v>
       </c>
       <c r="J228" t="n">
-        <v>11.938</v>
+        <v>12.134</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.51</v>
       </c>
       <c r="I229" t="n">
-        <v>0.5969</v>
+        <v>0.6067</v>
       </c>
       <c r="J229" t="n">
-        <v>11.938</v>
+        <v>12.134</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.38</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4639</v>
+        <v>0.4802</v>
       </c>
       <c r="J230" t="n">
-        <v>9.278</v>
+        <v>9.603999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1657</v>
+        <v>0.1905</v>
       </c>
       <c r="J231" t="n">
-        <v>3.314</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.4</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0347</v>
+        <v>0.9761</v>
       </c>
       <c r="J232" t="n">
-        <v>28.9716</v>
+        <v>27.3308</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.11</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3501</v>
+        <v>0.3494</v>
       </c>
       <c r="J233" t="n">
-        <v>9.8028</v>
+        <v>9.783200000000001</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2387</v>
+        <v>0.245</v>
       </c>
       <c r="J234" t="n">
-        <v>6.6836</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>1.03</v>
       </c>
       <c r="I235" t="n">
-        <v>0.11</v>
+        <v>0.1218</v>
       </c>
       <c r="J235" t="n">
-        <v>3.08</v>
+        <v>3.4104</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4338</v>
+        <v>-0.4136</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.1464</v>
+        <v>-11.5808</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.06</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1682</v>
+        <v>0.1748</v>
       </c>
       <c r="J237" t="n">
-        <v>4.7096</v>
+        <v>4.8944</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.03</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0973</v>
+        <v>0.1039</v>
       </c>
       <c r="J238" t="n">
-        <v>2.7244</v>
+        <v>2.9092</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J239" t="n">
-        <v>1.1844</v>
+        <v>1.3048</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="J240" t="n">
-        <v>0.1092</v>
+        <v>0.0756</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.76</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2753</v>
+        <v>-0.2888</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.7084</v>
+        <v>-8.086399999999999</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.32</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8737</v>
+        <v>0.8171</v>
       </c>
       <c r="J242" t="n">
-        <v>26.211</v>
+        <v>24.513</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.19</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5573</v>
+        <v>0.538</v>
       </c>
       <c r="J243" t="n">
-        <v>16.719</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.05</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1762</v>
+        <v>0.186</v>
       </c>
       <c r="J244" t="n">
-        <v>5.286</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1434</v>
+        <v>0.1546</v>
       </c>
       <c r="J245" t="n">
-        <v>4.302</v>
+        <v>4.638</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.91</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3485</v>
+        <v>-0.3351</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.455</v>
+        <v>-10.053</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.58</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0422</v>
+        <v>0.9992</v>
       </c>
       <c r="J247" t="n">
-        <v>31.266</v>
+        <v>29.976</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1798</v>
+        <v>0.1889</v>
       </c>
       <c r="J248" t="n">
-        <v>5.394</v>
+        <v>5.667</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1362</v>
+        <v>-0.1485</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.086</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.82</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2209</v>
+        <v>-0.234</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.627</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.72</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3192</v>
+        <v>-0.3308</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.576000000000001</v>
+        <v>-9.923999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.66</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3073</v>
+        <v>1.2874</v>
       </c>
       <c r="J252" t="n">
-        <v>27.4533</v>
+        <v>27.0354</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.47</v>
       </c>
       <c r="I253" t="n">
-        <v>1.076</v>
+        <v>1.0374</v>
       </c>
       <c r="J253" t="n">
-        <v>22.596</v>
+        <v>21.7854</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.24</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6128</v>
       </c>
       <c r="J254" t="n">
-        <v>13.2195</v>
+        <v>12.8688</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5575</v>
+        <v>0.5485</v>
       </c>
       <c r="J255" t="n">
-        <v>11.7075</v>
+        <v>11.5185</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>1.12</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3257</v>
+        <v>0.3388</v>
       </c>
       <c r="J256" t="n">
-        <v>6.8397</v>
+        <v>7.1148</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>0.78</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2231</v>
+        <v>-0.2445</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.6851</v>
+        <v>-5.1345</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>0.76</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2431</v>
+        <v>-0.264</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.1051</v>
+        <v>-5.544</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.71</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2897</v>
+        <v>-0.3096</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.0837</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.67</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.326</v>
+        <v>-0.3449</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.846</v>
+        <v>-7.2429</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3538</v>
+        <v>-0.3717</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.4298</v>
+        <v>-7.8057</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5541</v>
+        <v>1.5349</v>
       </c>
       <c r="J262" t="n">
-        <v>45.0689</v>
+        <v>44.5121</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1439</v>
+        <v>0.1549</v>
       </c>
       <c r="J263" t="n">
-        <v>4.1731</v>
+        <v>4.4921</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.2533</v>
+        <v>-2.1866</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.98</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1187</v>
+        <v>-0.1168</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.4423</v>
+        <v>-3.3872</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.9254</v>
+        <v>-0.8495</v>
       </c>
       <c r="J266" t="n">
-        <v>-26.8366</v>
+        <v>-24.6355</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.39</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>21.4136</v>
+        <v>20.6538</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.16</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3431</v>
+        <v>0.3489</v>
       </c>
       <c r="J268" t="n">
-        <v>9.9499</v>
+        <v>10.1181</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2873</v>
+        <v>0.2959</v>
       </c>
       <c r="J269" t="n">
-        <v>8.3317</v>
+        <v>8.581099999999999</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0584</v>
+        <v>-0.0646</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.6936</v>
+        <v>-1.8734</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.77</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.278</v>
+        <v>-0.289</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.061999999999999</v>
+        <v>-8.381</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.83</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4891</v>
+        <v>1.4828</v>
       </c>
       <c r="J272" t="n">
-        <v>29.782</v>
+        <v>29.656</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.51</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1135</v>
+        <v>1.0822</v>
       </c>
       <c r="J273" t="n">
-        <v>22.27</v>
+        <v>21.644</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.4</v>
       </c>
       <c r="I274" t="n">
-        <v>0.9641</v>
+        <v>0.915</v>
       </c>
       <c r="J274" t="n">
-        <v>19.282</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1.22</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5648</v>
+        <v>0.5584</v>
       </c>
       <c r="J275" t="n">
-        <v>11.296</v>
+        <v>11.168</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>1.14</v>
       </c>
       <c r="I276" t="n">
-        <v>0.3621</v>
+        <v>0.3759</v>
       </c>
       <c r="J276" t="n">
-        <v>7.242</v>
+        <v>7.518</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>0.93</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.0374</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>-0.748</v>
+        <v>-1.254</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.76</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.233</v>
+        <v>-0.2562</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.66</v>
+        <v>-5.124</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3019</v>
+        <v>-0.3228</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.038</v>
+        <v>-6.456</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.47</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5046</v>
+        <v>-0.5154</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.092</v>
+        <v>-10.308</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.514</v>
+        <v>-0.5241</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.28</v>
+        <v>-10.482</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.68</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3517</v>
+        <v>1.3309</v>
       </c>
       <c r="J282" t="n">
-        <v>32.4408</v>
+        <v>31.9416</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.38</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9544</v>
+        <v>0.8995</v>
       </c>
       <c r="J283" t="n">
-        <v>22.9056</v>
+        <v>21.588</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8248</v>
+        <v>0.7831</v>
       </c>
       <c r="J284" t="n">
-        <v>19.7952</v>
+        <v>18.7944</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.03</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0707</v>
+        <v>0.0946</v>
       </c>
       <c r="J285" t="n">
-        <v>1.6968</v>
+        <v>2.2704</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5018</v>
+        <v>-0.4671</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.0432</v>
+        <v>-11.2104</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.23</v>
       </c>
       <c r="I287" t="n">
-        <v>0.52</v>
+        <v>0.5038</v>
       </c>
       <c r="J287" t="n">
-        <v>12.48</v>
+        <v>12.0912</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.18</v>
       </c>
       <c r="I288" t="n">
-        <v>0.426</v>
+        <v>0.4172</v>
       </c>
       <c r="J288" t="n">
-        <v>10.224</v>
+        <v>10.0128</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>0.92</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1048</v>
+        <v>-0.1183</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.5152</v>
+        <v>-2.8392</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.89</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1376</v>
+        <v>-0.1523</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.3024</v>
+        <v>-3.6552</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.43</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5752</v>
+        <v>-0.5765</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.8048</v>
+        <v>-13.836</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>0.99</v>
       </c>
       <c r="I292" t="n">
-        <v>0.0068</v>
+        <v>-0.0065</v>
       </c>
       <c r="J292" t="n">
-        <v>0.1564</v>
+        <v>-0.1495</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0677</v>
+        <v>-0.0833</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.5571</v>
+        <v>-1.9159</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.89</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1266</v>
+        <v>-0.1439</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.9118</v>
+        <v>-3.3097</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.7</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3139</v>
+        <v>-0.3302</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.2197</v>
+        <v>-7.5946</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.6</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4081</v>
+        <v>-0.4206</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.3863</v>
+        <v>-9.6738</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.96</v>
       </c>
       <c r="I297" t="n">
-        <v>1.6811</v>
+        <v>1.6772</v>
       </c>
       <c r="J297" t="n">
-        <v>38.6653</v>
+        <v>38.5756</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.29</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7547</v>
+        <v>0.7219</v>
       </c>
       <c r="J298" t="n">
-        <v>17.3581</v>
+        <v>16.6037</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.09</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2569</v>
+        <v>0.2719</v>
       </c>
       <c r="J299" t="n">
-        <v>5.9087</v>
+        <v>6.2537</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0113</v>
+        <v>0.0139</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.2599</v>
+        <v>0.3197</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.0113</v>
+        <v>0.0139</v>
       </c>
       <c r="J301" t="n">
-        <v>-0.2599</v>
+        <v>0.3197</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.43</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8647</v>
+        <v>0.8159</v>
       </c>
       <c r="J302" t="n">
-        <v>30.2645</v>
+        <v>28.5565</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.9</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1284</v>
+        <v>-0.1424</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.494</v>
+        <v>-4.984</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1393</v>
+        <v>-0.1536</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.8755</v>
+        <v>-5.376</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2022</v>
+        <v>-0.2172</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.077</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3489</v>
+        <v>-0.3611</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.2115</v>
+        <v>-12.6385</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.4</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0298</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J307" t="n">
-        <v>36.043</v>
+        <v>33.9955</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.28</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7741</v>
+        <v>0.7308</v>
       </c>
       <c r="J308" t="n">
-        <v>27.0935</v>
+        <v>25.578</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.2</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5789</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J309" t="n">
-        <v>20.2615</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.89</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4098</v>
+        <v>-0.3908</v>
       </c>
       <c r="J310" t="n">
-        <v>-14.343</v>
+        <v>-13.678</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6535</v>
+        <v>-0.6102</v>
       </c>
       <c r="J311" t="n">
-        <v>-22.8725</v>
+        <v>-21.357</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.79</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5064</v>
+        <v>1.4904</v>
       </c>
       <c r="J312" t="n">
-        <v>39.1664</v>
+        <v>38.7504</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.15</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4391</v>
+        <v>0.435</v>
       </c>
       <c r="J313" t="n">
-        <v>11.4166</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.08</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2472</v>
+        <v>0.2583</v>
       </c>
       <c r="J314" t="n">
-        <v>6.4272</v>
+        <v>6.7158</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1217</v>
+        <v>0.1395</v>
       </c>
       <c r="J315" t="n">
-        <v>3.1642</v>
+        <v>3.627</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.89</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4297</v>
+        <v>-0.4047</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.1722</v>
+        <v>-10.5222</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.36</v>
       </c>
       <c r="I317" t="n">
-        <v>0.802</v>
+        <v>0.7512</v>
       </c>
       <c r="J317" t="n">
-        <v>20.852</v>
+        <v>19.5312</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4837</v>
+        <v>0.4633</v>
       </c>
       <c r="J318" t="n">
-        <v>12.5762</v>
+        <v>12.0458</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.83</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1907</v>
+        <v>-0.2084</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.9582</v>
+        <v>-5.4184</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.43</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5668</v>
+        <v>-0.5698</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.7368</v>
+        <v>-14.8148</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.42</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5758</v>
+        <v>-0.5782</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.9708</v>
+        <v>-15.0332</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.15</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3991</v>
+        <v>0.3859</v>
       </c>
       <c r="J322" t="n">
-        <v>9.977499999999999</v>
+        <v>9.647500000000001</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.05</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1819</v>
+        <v>0.1789</v>
       </c>
       <c r="J323" t="n">
-        <v>4.5475</v>
+        <v>4.4725</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.73</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2896</v>
+        <v>-0.3057</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.24</v>
+        <v>-7.6425</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.68</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3374</v>
+        <v>-0.352</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.435</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3468</v>
+        <v>-0.3611</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.67</v>
+        <v>-9.0275</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.61</v>
       </c>
       <c r="I327" t="n">
-        <v>1.2715</v>
+        <v>1.2447</v>
       </c>
       <c r="J327" t="n">
-        <v>31.7875</v>
+        <v>31.1175</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8751</v>
+        <v>0.8262</v>
       </c>
       <c r="J328" t="n">
-        <v>21.8775</v>
+        <v>20.655</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.13</v>
       </c>
       <c r="I329" t="n">
-        <v>0.377</v>
+        <v>0.3805</v>
       </c>
       <c r="J329" t="n">
-        <v>9.425000000000001</v>
+        <v>9.512499999999999</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>1.05</v>
       </c>
       <c r="I330" t="n">
-        <v>0.144</v>
+        <v>0.1637</v>
       </c>
       <c r="J330" t="n">
-        <v>3.6</v>
+        <v>4.0925</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>1.04</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1109</v>
+        <v>0.132</v>
       </c>
       <c r="J331" t="n">
-        <v>2.7725</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.77</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4318</v>
+        <v>1.4202</v>
       </c>
       <c r="J332" t="n">
-        <v>30.0678</v>
+        <v>29.8242</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.37</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8649</v>
       </c>
       <c r="J333" t="n">
-        <v>19.1688</v>
+        <v>18.1629</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.29</v>
       </c>
       <c r="I334" t="n">
-        <v>0.74</v>
+        <v>0.7119</v>
       </c>
       <c r="J334" t="n">
-        <v>15.54</v>
+        <v>14.9499</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>1.24</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6241</v>
+        <v>0.6091</v>
       </c>
       <c r="J335" t="n">
-        <v>13.1061</v>
+        <v>12.7911</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>1.16</v>
       </c>
       <c r="I336" t="n">
-        <v>0.4263</v>
+        <v>0.4317</v>
       </c>
       <c r="J336" t="n">
-        <v>8.952299999999999</v>
+        <v>9.0657</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>0.99</v>
       </c>
       <c r="I337" t="n">
-        <v>0.0492</v>
+        <v>0.02</v>
       </c>
       <c r="J337" t="n">
-        <v>1.0332</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>0.97</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0055</v>
+        <v>-0.0236</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.1155</v>
+        <v>-0.4956</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.9</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.097</v>
+        <v>-0.1182</v>
       </c>
       <c r="J339" t="n">
-        <v>-2.037</v>
+        <v>-2.4822</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4321</v>
+        <v>-0.4455</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.0741</v>
+        <v>-9.355499999999999</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.25</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7189</v>
+        <v>-0.7121</v>
       </c>
       <c r="J341" t="n">
-        <v>-15.0969</v>
+        <v>-14.9541</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.64</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1428</v>
+        <v>1.1078</v>
       </c>
       <c r="J342" t="n">
-        <v>29.7128</v>
+        <v>28.8028</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>0.8</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.2274</v>
+        <v>-0.2433</v>
       </c>
       <c r="J343" t="n">
-        <v>-5.9124</v>
+        <v>-6.3258</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.74</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2863</v>
+        <v>-0.3013</v>
       </c>
       <c r="J344" t="n">
-        <v>-7.4438</v>
+        <v>-7.8338</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.68</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3437</v>
+        <v>-0.357</v>
       </c>
       <c r="J345" t="n">
-        <v>-8.936199999999999</v>
+        <v>-9.282</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3626</v>
+        <v>-0.3752</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.4276</v>
+        <v>-9.7552</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.53</v>
       </c>
       <c r="I347" t="n">
-        <v>1.1753</v>
+        <v>1.1413</v>
       </c>
       <c r="J347" t="n">
-        <v>30.5578</v>
+        <v>29.6738</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.36</v>
       </c>
       <c r="I348" t="n">
-        <v>0.9236</v>
+        <v>0.8685</v>
       </c>
       <c r="J348" t="n">
-        <v>24.0136</v>
+        <v>22.581</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.33</v>
       </c>
       <c r="I349" t="n">
-        <v>0.857</v>
+        <v>0.8095</v>
       </c>
       <c r="J349" t="n">
-        <v>22.282</v>
+        <v>21.047</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>1.02</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0429</v>
+        <v>0.0645</v>
       </c>
       <c r="J350" t="n">
-        <v>1.1154</v>
+        <v>1.677</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5475</v>
+        <v>-0.5103</v>
       </c>
       <c r="J351" t="n">
-        <v>-14.235</v>
+        <v>-13.2678</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.05</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1714</v>
+        <v>0.1712</v>
       </c>
       <c r="J352" t="n">
-        <v>4.1136</v>
+        <v>4.1088</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>0.92</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.1009</v>
+        <v>-0.1154</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.4216</v>
+        <v>-2.7696</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>0.84</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1847</v>
+        <v>-0.2014</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.4328</v>
+        <v>-4.8336</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.83</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1948</v>
+        <v>-0.2115</v>
       </c>
       <c r="J355" t="n">
-        <v>-4.6752</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.78</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2447</v>
+        <v>-0.261</v>
       </c>
       <c r="J356" t="n">
-        <v>-5.8728</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.41</v>
       </c>
       <c r="I357" t="n">
-        <v>1.0214</v>
+        <v>0.9668</v>
       </c>
       <c r="J357" t="n">
-        <v>24.5136</v>
+        <v>23.2032</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.39</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9879</v>
+        <v>0.9303</v>
       </c>
       <c r="J358" t="n">
-        <v>23.7096</v>
+        <v>22.3272</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>1.23</v>
       </c>
       <c r="I359" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6086</v>
       </c>
       <c r="J359" t="n">
-        <v>15.132</v>
+        <v>14.6064</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>1.07</v>
       </c>
       <c r="I360" t="n">
-        <v>0.2149</v>
+        <v>0.2287</v>
       </c>
       <c r="J360" t="n">
-        <v>5.1576</v>
+        <v>5.4888</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.9</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4035</v>
+        <v>-0.3801</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.683999999999999</v>
+        <v>-9.122400000000001</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.31</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6226</v>
+        <v>0.6044</v>
       </c>
       <c r="J362" t="n">
-        <v>18.0554</v>
+        <v>17.5276</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.01</v>
       </c>
       <c r="I363" t="n">
-        <v>0.034</v>
+        <v>0.0407</v>
       </c>
       <c r="J363" t="n">
-        <v>0.986</v>
+        <v>1.1803</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>0.97</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.0531</v>
+        <v>-0.0605</v>
       </c>
       <c r="J364" t="n">
-        <v>-1.5399</v>
+        <v>-1.7545</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.0915</v>
+        <v>-0.1016</v>
       </c>
       <c r="J365" t="n">
-        <v>-2.6535</v>
+        <v>-2.9464</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.93</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.1034</v>
+        <v>-0.1141</v>
       </c>
       <c r="J366" t="n">
-        <v>-2.9986</v>
+        <v>-3.3089</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.64</v>
       </c>
       <c r="I367" t="n">
-        <v>1.3255</v>
+        <v>1.2991</v>
       </c>
       <c r="J367" t="n">
-        <v>38.4395</v>
+        <v>37.6739</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.54</v>
       </c>
       <c r="I368" t="n">
-        <v>1.1989</v>
+        <v>1.1645</v>
       </c>
       <c r="J368" t="n">
-        <v>34.7681</v>
+        <v>33.7705</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.4</v>
       </c>
       <c r="I369" t="n">
-        <v>1.0117</v>
+        <v>0.9546</v>
       </c>
       <c r="J369" t="n">
-        <v>29.3393</v>
+        <v>27.6834</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.72</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.8704</v>
+        <v>-0.7985</v>
       </c>
       <c r="J370" t="n">
-        <v>-25.2416</v>
+        <v>-23.1565</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.58</v>
       </c>
       <c r="I371" t="n">
-        <v>-1.203</v>
+        <v>-1.0865</v>
       </c>
       <c r="J371" t="n">
-        <v>-34.887</v>
+        <v>-31.5085</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.6778</v>
+        <v>0.648</v>
       </c>
       <c r="J372" t="n">
-        <v>19.6562</v>
+        <v>18.792</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.01</v>
       </c>
       <c r="I373" t="n">
-        <v>0.0493</v>
+        <v>0.0516</v>
       </c>
       <c r="J373" t="n">
-        <v>1.4297</v>
+        <v>1.4964</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.87</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J374" t="n">
-        <v>-4.64</v>
+        <v>-5.0721</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.87</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J375" t="n">
-        <v>-4.64</v>
+        <v>-5.0721</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.63</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.395</v>
+        <v>-0.4055</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.455</v>
+        <v>-11.7595</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.75</v>
       </c>
       <c r="I377" t="n">
-        <v>1.4608</v>
+        <v>1.442</v>
       </c>
       <c r="J377" t="n">
-        <v>42.3632</v>
+        <v>41.818</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.33</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8685</v>
+        <v>0.8175</v>
       </c>
       <c r="J378" t="n">
-        <v>25.1865</v>
+        <v>23.7075</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.04</v>
       </c>
       <c r="I379" t="n">
-        <v>0.1242</v>
+        <v>0.1413</v>
       </c>
       <c r="J379" t="n">
-        <v>3.6018</v>
+        <v>4.0977</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.97</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.1769</v>
+        <v>-0.168</v>
       </c>
       <c r="J380" t="n">
-        <v>-5.1301</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.6443</v>
+        <v>-0.5989</v>
       </c>
       <c r="J381" t="n">
-        <v>-18.6847</v>
+        <v>-17.3681</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1</v>
       </c>
       <c r="I382" t="n">
-        <v>0.0369</v>
+        <v>0.0266</v>
       </c>
       <c r="J382" t="n">
-        <v>0.9594</v>
+        <v>0.6916</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>0.88</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.141</v>
+        <v>-0.1577</v>
       </c>
       <c r="J383" t="n">
-        <v>-3.666</v>
+        <v>-4.1002</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.87</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1515</v>
+        <v>-0.1684</v>
       </c>
       <c r="J384" t="n">
-        <v>-3.939</v>
+        <v>-4.3784</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.85</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1715</v>
+        <v>-0.1888</v>
       </c>
       <c r="J385" t="n">
-        <v>-4.459</v>
+        <v>-4.9088</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.65</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3649</v>
+        <v>-0.3786</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.487399999999999</v>
+        <v>-9.8436</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.46</v>
       </c>
       <c r="I387" t="n">
-        <v>1.09</v>
+        <v>1.0478</v>
       </c>
       <c r="J387" t="n">
-        <v>28.34</v>
+        <v>27.2428</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.43</v>
       </c>
       <c r="I388" t="n">
-        <v>1.0505</v>
+        <v>1.001</v>
       </c>
       <c r="J388" t="n">
-        <v>27.313</v>
+        <v>26.026</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.31</v>
       </c>
       <c r="I389" t="n">
-        <v>0.8165</v>
+        <v>0.7731</v>
       </c>
       <c r="J389" t="n">
-        <v>21.229</v>
+        <v>20.1006</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.92</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3444</v>
+        <v>-0.3255</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.9544</v>
+        <v>-8.462999999999999</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.88</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4605</v>
+        <v>-0.4323</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.973</v>
+        <v>-11.2398</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>2.15</v>
       </c>
       <c r="I392" t="n">
-        <v>1.8164</v>
+        <v>1.8298</v>
       </c>
       <c r="J392" t="n">
-        <v>32.6952</v>
+        <v>32.9364</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.74</v>
       </c>
       <c r="I393" t="n">
-        <v>1.3634</v>
+        <v>1.3539</v>
       </c>
       <c r="J393" t="n">
-        <v>24.5412</v>
+        <v>24.3702</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.59</v>
       </c>
       <c r="I394" t="n">
-        <v>1.193</v>
+        <v>1.1713</v>
       </c>
       <c r="J394" t="n">
-        <v>21.474</v>
+        <v>21.0834</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>1.15</v>
       </c>
       <c r="I395" t="n">
-        <v>0.3625</v>
+        <v>0.3816</v>
       </c>
       <c r="J395" t="n">
-        <v>6.525</v>
+        <v>6.8688</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>1.11</v>
       </c>
       <c r="I396" t="n">
-        <v>0.2547</v>
+        <v>0.2831</v>
       </c>
       <c r="J396" t="n">
-        <v>4.5846</v>
+        <v>5.0958</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>0.83</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.1186</v>
+        <v>-0.1519</v>
       </c>
       <c r="J397" t="n">
-        <v>-2.1348</v>
+        <v>-2.7342</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>0.64</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.3278</v>
+        <v>-0.3517</v>
       </c>
       <c r="J398" t="n">
-        <v>-5.9004</v>
+        <v>-6.3306</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.51</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.4474</v>
+        <v>-0.4649</v>
       </c>
       <c r="J399" t="n">
-        <v>-8.0532</v>
+        <v>-8.3682</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.46</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4943</v>
+        <v>-0.5087</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.897399999999999</v>
+        <v>-9.156599999999999</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.35</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.6004</v>
+        <v>-0.6065</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.8072</v>
+        <v>-10.917</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>2.16</v>
       </c>
       <c r="I402" t="n">
-        <v>1.8338</v>
+        <v>1.8553</v>
       </c>
       <c r="J402" t="n">
-        <v>34.8422</v>
+        <v>35.2507</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.6</v>
       </c>
       <c r="I403" t="n">
-        <v>1.2117</v>
+        <v>1.1899</v>
       </c>
       <c r="J403" t="n">
-        <v>23.0223</v>
+        <v>22.6081</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.38</v>
       </c>
       <c r="I404" t="n">
-        <v>0.9154</v>
+        <v>0.8708</v>
       </c>
       <c r="J404" t="n">
-        <v>17.3926</v>
+        <v>16.5452</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>1.19</v>
       </c>
       <c r="I405" t="n">
-        <v>0.4776</v>
+        <v>0.483</v>
       </c>
       <c r="J405" t="n">
-        <v>9.074400000000001</v>
+        <v>9.177</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>1.09</v>
       </c>
       <c r="I406" t="n">
-        <v>0.2105</v>
+        <v>0.2394</v>
       </c>
       <c r="J406" t="n">
-        <v>3.9995</v>
+        <v>4.5486</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>0.96</v>
       </c>
       <c r="I407" t="n">
-        <v>0.0404</v>
+        <v>-0.0058</v>
       </c>
       <c r="J407" t="n">
-        <v>0.7675999999999999</v>
+        <v>-0.1102</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>0.67</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.3132</v>
+        <v>-0.3352</v>
       </c>
       <c r="J408" t="n">
-        <v>-5.9508</v>
+        <v>-6.3688</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>0.58</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.3943</v>
+        <v>-0.413</v>
       </c>
       <c r="J409" t="n">
-        <v>-7.4917</v>
+        <v>-7.847</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.55</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.422</v>
+        <v>-0.4391</v>
       </c>
       <c r="J410" t="n">
-        <v>-8.018000000000001</v>
+        <v>-8.3429</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.34</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6208</v>
+        <v>-0.6238</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.7952</v>
+        <v>-11.8522</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.73</v>
       </c>
       <c r="I412" t="n">
-        <v>1.3568</v>
+        <v>1.346</v>
       </c>
       <c r="J412" t="n">
-        <v>25.7792</v>
+        <v>25.574</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.55</v>
       </c>
       <c r="I413" t="n">
-        <v>1.1502</v>
+        <v>1.1243</v>
       </c>
       <c r="J413" t="n">
-        <v>21.8538</v>
+        <v>21.3617</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.55</v>
       </c>
       <c r="I414" t="n">
-        <v>1.1502</v>
+        <v>1.1243</v>
       </c>
       <c r="J414" t="n">
-        <v>21.8538</v>
+        <v>21.3617</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>1.52</v>
       </c>
       <c r="I415" t="n">
-        <v>1.1159</v>
+        <v>1.087</v>
       </c>
       <c r="J415" t="n">
-        <v>21.2021</v>
+        <v>20.653</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>1.23</v>
       </c>
       <c r="I416" t="n">
-        <v>0.5692</v>
+        <v>0.5662</v>
       </c>
       <c r="J416" t="n">
-        <v>10.8148</v>
+        <v>10.7578</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>0.77</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.1913</v>
+        <v>-0.2216</v>
       </c>
       <c r="J417" t="n">
-        <v>-3.6347</v>
+        <v>-4.2104</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>0.68</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.2888</v>
+        <v>-0.3145</v>
       </c>
       <c r="J418" t="n">
-        <v>-5.4872</v>
+        <v>-5.9755</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.62</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.349</v>
+        <v>-0.3715</v>
       </c>
       <c r="J419" t="n">
-        <v>-6.631</v>
+        <v>-7.0585</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.46</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.4956</v>
+        <v>-0.5097</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.416399999999999</v>
+        <v>-9.6843</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.29</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.6601</v>
+        <v>-0.6609</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.5419</v>
+        <v>-12.5571</v>
       </c>
     </row>
     <row r="422">
@@ -21069,10 +21069,10 @@
         <v>1.19</v>
       </c>
       <c r="I422" t="n">
-        <v>0.571</v>
+        <v>0.5475</v>
       </c>
       <c r="J422" t="n">
-        <v>14.846</v>
+        <v>14.235</v>
       </c>
     </row>
     <row r="423">
@@ -21109,10 +21109,10 @@
         <v>1.15</v>
       </c>
       <c r="I423" t="n">
-        <v>0.4668</v>
+        <v>0.4539</v>
       </c>
       <c r="J423" t="n">
-        <v>12.1368</v>
+        <v>11.8014</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>1.13</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4133</v>
+        <v>0.4053</v>
       </c>
       <c r="J424" t="n">
-        <v>10.7458</v>
+        <v>10.5378</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>0.93</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.2766</v>
+        <v>-0.271</v>
       </c>
       <c r="J425" t="n">
-        <v>-7.1916</v>
+        <v>-7.046</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>0.9</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3661</v>
+        <v>-0.3539</v>
       </c>
       <c r="J426" t="n">
-        <v>-9.518599999999999</v>
+        <v>-9.2014</v>
       </c>
     </row>
     <row r="427">
@@ -21269,10 +21269,10 @@
         <v>1.61</v>
       </c>
       <c r="I427" t="n">
-        <v>1.0506</v>
+        <v>1.0132</v>
       </c>
       <c r="J427" t="n">
-        <v>27.3156</v>
+        <v>26.3432</v>
       </c>
     </row>
     <row r="428">
@@ -21309,10 +21309,10 @@
         <v>1.14</v>
       </c>
       <c r="I428" t="n">
-        <v>0.3053</v>
+        <v>0.3133</v>
       </c>
       <c r="J428" t="n">
-        <v>7.9378</v>
+        <v>8.145799999999999</v>
       </c>
     </row>
     <row r="429">
@@ -21349,10 +21349,10 @@
         <v>1.07</v>
       </c>
       <c r="I429" t="n">
-        <v>0.1699</v>
+        <v>0.1819</v>
       </c>
       <c r="J429" t="n">
-        <v>4.4174</v>
+        <v>4.7294</v>
       </c>
     </row>
     <row r="430">
@@ -21389,10 +21389,10 @@
         <v>0.88</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.1659</v>
+        <v>-0.1769</v>
       </c>
       <c r="J430" t="n">
-        <v>-4.3134</v>
+        <v>-4.5994</v>
       </c>
     </row>
     <row r="431">
@@ -21429,10 +21429,10 @@
         <v>0.74</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.3075</v>
+        <v>-0.3179</v>
       </c>
       <c r="J431" t="n">
-        <v>-7.995</v>
+        <v>-8.2654</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2325/event_2325_evp_summary.xlsx
+++ b/database/event/2325/event_2325_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7349</v>
+        <v>5.6593</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6086</v>
+        <v>2.5742</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9864</v>
+        <v>1.9723</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7349</v>
+        <v>5.6593</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8741</v>
+        <v>1.8587</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8608</v>
+        <v>3.8006</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8741</v>
+        <v>1.8587</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8741</v>
+        <v>1.8587</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8608</v>
+        <v>3.8006</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>183</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7349</v>
+        <v>5.6593</v>
       </c>
       <c r="N2" t="n">
         <v>230</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3208</v>
+        <v>5.1837</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4202</v>
+        <v>2.3579</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7979</v>
+        <v>1.7556</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3208</v>
+        <v>5.1837</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4124</v>
+        <v>1.3598</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9084</v>
+        <v>3.8239</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4124</v>
+        <v>1.3598</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4124</v>
+        <v>1.3598</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9084</v>
+        <v>3.8239</v>
       </c>
       <c r="K3" t="n">
         <v>47</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3208</v>
+        <v>5.1837</v>
       </c>
       <c r="N3" t="n">
         <v>230</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4803</v>
+        <v>4.5341</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0379</v>
+        <v>2.0624</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4153</v>
+        <v>1.4597</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4803</v>
+        <v>4.5341</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1136</v>
+        <v>2.1466</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3667</v>
+        <v>2.3875</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1136</v>
+        <v>2.1466</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1136</v>
+        <v>2.1466</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3667</v>
+        <v>2.3875</v>
       </c>
       <c r="K4" t="n">
         <v>45</v>
@@ -621,7 +621,7 @@
         <v>179</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4803</v>
+        <v>4.5341</v>
       </c>
       <c r="N4" t="n">
         <v>224</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0371</v>
+        <v>3.9373</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8363</v>
+        <v>1.7909</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2136</v>
+        <v>1.1878</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0371</v>
+        <v>3.9373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.837</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2001</v>
+        <v>3.1727</v>
       </c>
       <c r="H5" t="n">
-        <v>0.837</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.837</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2001</v>
+        <v>3.1727</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>183</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0371</v>
+        <v>3.9373</v>
       </c>
       <c r="N5" t="n">
         <v>230</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.901</v>
+        <v>3.8721</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7744</v>
+        <v>1.7613</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1516</v>
+        <v>1.1581</v>
       </c>
       <c r="E6" t="n">
-        <v>3.901</v>
+        <v>3.8721</v>
       </c>
       <c r="F6" t="n">
-        <v>0.358</v>
+        <v>0.3796</v>
       </c>
       <c r="G6" t="n">
-        <v>3.543</v>
+        <v>3.4925</v>
       </c>
       <c r="H6" t="n">
-        <v>0.358</v>
+        <v>0.3796</v>
       </c>
       <c r="I6" t="n">
-        <v>0.358</v>
+        <v>0.3796</v>
       </c>
       <c r="J6" t="n">
-        <v>3.543</v>
+        <v>3.4925</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>3.901</v>
+        <v>3.8721</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7155</v>
+        <v>3.6466</v>
       </c>
       <c r="C7" t="n">
-        <v>1.69</v>
+        <v>1.6587</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0672</v>
+        <v>1.0554</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7155</v>
+        <v>3.6466</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4696</v>
+        <v>2.3656</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2459</v>
+        <v>1.281</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6803</v>
+        <v>2.4712</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6803</v>
+        <v>2.4712</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2459</v>
+        <v>1.281</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9262</v>
+        <v>3.7522</v>
       </c>
       <c r="N7" t="n">
-        <v>224</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6966</v>
+        <v>3.6079</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6815</v>
+        <v>1.6411</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0586</v>
+        <v>1.0378</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6966</v>
+        <v>3.6079</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3642</v>
+        <v>2.4804</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3324</v>
+        <v>1.1275</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4496</v>
+        <v>2.7342</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4496</v>
+        <v>2.7342</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3324</v>
+        <v>1.1275</v>
       </c>
       <c r="K8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L8" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="M8" t="n">
-        <v>3.782</v>
+        <v>3.8617</v>
       </c>
       <c r="N8" t="n">
-        <v>161</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.277</v>
+        <v>3.2684</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4906</v>
+        <v>1.4867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8676</v>
+        <v>0.8831</v>
       </c>
       <c r="E9" t="n">
-        <v>3.277</v>
+        <v>3.2684</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7035</v>
+        <v>1.7567</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5735</v>
+        <v>1.5117</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7035</v>
+        <v>1.7567</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7474</v>
+        <v>1.8036</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5735</v>
+        <v>1.5117</v>
       </c>
       <c r="K9" t="n">
         <v>95</v>
@@ -851,7 +851,7 @@
         <v>140</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3209</v>
+        <v>3.3153</v>
       </c>
       <c r="N9" t="n">
         <v>235</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2535</v>
+        <v>3.1884</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4799</v>
+        <v>1.4503</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8569</v>
+        <v>0.8467</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2535</v>
+        <v>3.1884</v>
       </c>
       <c r="F10" t="n">
-        <v>2.333</v>
+        <v>2.328</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9205</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3812</v>
+        <v>2.3849</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4426</v>
+        <v>2.4486</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9205</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>141</v>
@@ -897,7 +897,7 @@
         <v>72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3631</v>
+        <v>3.309</v>
       </c>
       <c r="N10" t="n">
         <v>213</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.155</v>
+        <v>3.1418</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4351</v>
+        <v>1.4291</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8255</v>
       </c>
       <c r="E11" t="n">
-        <v>3.155</v>
+        <v>3.1418</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9658</v>
+        <v>2.298</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1892</v>
+        <v>0.8438</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9658</v>
+        <v>2.3162</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9907</v>
+        <v>2.3781</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1892</v>
+        <v>0.8438</v>
       </c>
       <c r="K11" t="n">
         <v>95</v>
@@ -943,7 +943,7 @@
         <v>140</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1799</v>
+        <v>3.2219</v>
       </c>
       <c r="N11" t="n">
         <v>235</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1539</v>
+        <v>3.0233</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4346</v>
+        <v>1.3752</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8115</v>
+        <v>0.7715</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1539</v>
+        <v>3.0233</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3065</v>
+        <v>0.8969</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8474</v>
+        <v>2.1263</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3233</v>
+        <v>0.8969</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3832</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8474</v>
+        <v>2.1263</v>
       </c>
       <c r="K12" t="n">
         <v>95</v>
@@ -989,7 +989,7 @@
         <v>140</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2306</v>
+        <v>3.0472</v>
       </c>
       <c r="N12" t="n">
         <v>235</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1097</v>
+        <v>2.979</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4145</v>
+        <v>1.355</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7914</v>
+        <v>0.7513</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1097</v>
+        <v>2.979</v>
       </c>
       <c r="F13" t="n">
-        <v>1.982</v>
+        <v>1.972</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1277</v>
+        <v>1.007</v>
       </c>
       <c r="H13" t="n">
-        <v>1.982</v>
+        <v>1.972</v>
       </c>
       <c r="I13" t="n">
-        <v>1.982</v>
+        <v>1.972</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1277</v>
+        <v>1.007</v>
       </c>
       <c r="K13" t="n">
         <v>58</v>
@@ -1035,7 +1035,7 @@
         <v>83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1097</v>
+        <v>2.979</v>
       </c>
       <c r="N13" t="n">
         <v>141</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7063</v>
+        <v>2.6027</v>
       </c>
       <c r="C14" t="n">
-        <v>1.231</v>
+        <v>1.1839</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6078</v>
+        <v>0.5799</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7063</v>
+        <v>2.6027</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3065</v>
+        <v>2.5065</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3998</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3065</v>
+        <v>2.7939</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3402</v>
+        <v>2.7939</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3998</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.74</v>
+        <v>2.8901</v>
       </c>
       <c r="N14" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6455</v>
+        <v>2.5649</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2033</v>
+        <v>1.1667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5626</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6455</v>
+        <v>2.5649</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4974</v>
+        <v>1.2565</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1481</v>
+        <v>1.3084</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7411</v>
+        <v>1.2565</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7411</v>
+        <v>1.2901</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1481</v>
+        <v>1.3084</v>
       </c>
       <c r="K15" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="L15" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8892</v>
+        <v>2.5985</v>
       </c>
       <c r="N15" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2855</v>
+        <v>2.2756</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0396</v>
+        <v>1.0351</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4162</v>
+        <v>0.4309</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2855</v>
+        <v>2.2756</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3109</v>
+        <v>1.2952</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9746</v>
+        <v>0.9804</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3109</v>
+        <v>1.2952</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3109</v>
+        <v>1.2952</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9746</v>
+        <v>0.9804</v>
       </c>
       <c r="K16" t="n">
         <v>44</v>
@@ -1173,7 +1173,7 @@
         <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2855</v>
+        <v>2.2756</v>
       </c>
       <c r="N16" t="n">
         <v>161</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2535</v>
+        <v>2.2333</v>
       </c>
       <c r="C17" t="n">
-        <v>1.025</v>
+        <v>1.0158</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4016</v>
+        <v>0.4116</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2535</v>
+        <v>2.2333</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4996</v>
+        <v>2.4517</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2461</v>
+        <v>-0.2184</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7459</v>
+        <v>2.6684</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8167</v>
+        <v>2.7397</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2461</v>
+        <v>-0.2184</v>
       </c>
       <c r="K17" t="n">
         <v>97</v>
@@ -1219,7 +1219,7 @@
         <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5706</v>
+        <v>2.5213</v>
       </c>
       <c r="N17" t="n">
         <v>156</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2456</v>
+        <v>2.1299</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0214</v>
+        <v>0.9688</v>
       </c>
       <c r="D18" t="n">
-        <v>0.398</v>
+        <v>0.3645</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2456</v>
+        <v>2.1299</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2456</v>
+        <v>2.1299</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2456</v>
+        <v>2.1299</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2456</v>
+        <v>2.1299</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2456</v>
+        <v>2.1299</v>
       </c>
       <c r="N18" t="n">
         <v>122</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0455</v>
+        <v>2.0701</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9304</v>
+        <v>0.9416</v>
       </c>
       <c r="D19" t="n">
-        <v>0.307</v>
+        <v>0.3372</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0455</v>
+        <v>2.0701</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3983</v>
+        <v>2.3849</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3528</v>
+        <v>-0.3148</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5242</v>
+        <v>2.5154</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5892</v>
+        <v>2.5826</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3528</v>
+        <v>-0.3148</v>
       </c>
       <c r="K19" t="n">
         <v>97</v>
@@ -1311,7 +1311,7 @@
         <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2364</v>
+        <v>2.2678</v>
       </c>
       <c r="N19" t="n">
         <v>156</v>
@@ -1320,277 +1320,277 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0131</v>
+        <v>1.9274</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9157</v>
+        <v>0.8767</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2922</v>
+        <v>0.2722</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0131</v>
+        <v>1.9274</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7431</v>
+        <v>1.8254</v>
       </c>
       <c r="G20" t="n">
-        <v>0.27</v>
+        <v>0.102</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7431</v>
+        <v>1.8254</v>
       </c>
       <c r="I20" t="n">
-        <v>1.788</v>
+        <v>1.8254</v>
       </c>
       <c r="J20" t="n">
-        <v>0.27</v>
+        <v>0.102</v>
       </c>
       <c r="K20" t="n">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="L20" t="n">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="M20" t="n">
-        <v>2.058</v>
+        <v>1.9274</v>
       </c>
       <c r="N20" t="n">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9221</v>
+        <v>1.9061</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8743</v>
+        <v>0.867</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2508</v>
+        <v>0.2625</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9221</v>
+        <v>1.9061</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8453</v>
+        <v>1.6846</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.2216</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8453</v>
+        <v>1.6846</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8453</v>
+        <v>1.7296</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.2216</v>
       </c>
       <c r="K21" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="L21" t="n">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9221</v>
+        <v>1.9512</v>
       </c>
       <c r="N21" t="n">
-        <v>161</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8385</v>
+        <v>1.7547</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8363</v>
+        <v>0.7982</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2127</v>
+        <v>0.1936</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8385</v>
+        <v>1.7547</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9544</v>
+        <v>1.7547</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1159</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9544</v>
+        <v>1.7547</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0048</v>
+        <v>1.7547</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1159</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="L22" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8889</v>
+        <v>1.7547</v>
       </c>
       <c r="N22" t="n">
-        <v>213</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.796</v>
+        <v>1.7527</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8169</v>
+        <v>0.7972</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1934</v>
+        <v>0.1927</v>
       </c>
       <c r="E23" t="n">
-        <v>1.796</v>
+        <v>1.7527</v>
       </c>
       <c r="F23" t="n">
-        <v>1.796</v>
+        <v>1.8885</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.1358</v>
       </c>
       <c r="H23" t="n">
-        <v>1.796</v>
+        <v>1.8885</v>
       </c>
       <c r="I23" t="n">
-        <v>1.796</v>
+        <v>1.939</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.1358</v>
       </c>
       <c r="K23" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>1.796</v>
+        <v>1.8032</v>
       </c>
       <c r="N23" t="n">
-        <v>132</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7053</v>
+        <v>1.6826</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7654</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1521</v>
+        <v>0.1607</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7053</v>
+        <v>1.6826</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7053</v>
+        <v>1.6826</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7053</v>
+        <v>1.6826</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7053</v>
+        <v>1.6826</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7053</v>
+        <v>1.6826</v>
       </c>
       <c r="N24" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.687</v>
+        <v>1.6356</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7674</v>
+        <v>0.744</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1438</v>
+        <v>0.1393</v>
       </c>
       <c r="E25" t="n">
-        <v>1.687</v>
+        <v>1.6356</v>
       </c>
       <c r="F25" t="n">
-        <v>1.687</v>
+        <v>1.6409</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.0053</v>
       </c>
       <c r="H25" t="n">
-        <v>1.687</v>
+        <v>1.6409</v>
       </c>
       <c r="I25" t="n">
-        <v>1.687</v>
+        <v>1.6847</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.0053</v>
       </c>
       <c r="K25" t="n">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M25" t="n">
-        <v>1.687</v>
+        <v>1.6794</v>
       </c>
       <c r="N25" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6486</v>
+        <v>1.5675</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7499</v>
+        <v>0.713</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1263</v>
+        <v>0.1083</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6486</v>
+        <v>1.5675</v>
       </c>
       <c r="F26" t="n">
-        <v>1.167</v>
+        <v>1.1073</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4816</v>
+        <v>0.4602</v>
       </c>
       <c r="H26" t="n">
-        <v>1.167</v>
+        <v>1.1073</v>
       </c>
       <c r="I26" t="n">
-        <v>1.167</v>
+        <v>1.1073</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4816</v>
+        <v>0.4602</v>
       </c>
       <c r="K26" t="n">
         <v>44</v>
@@ -1633,7 +1633,7 @@
         <v>117</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6486</v>
+        <v>1.5675</v>
       </c>
       <c r="N26" t="n">
         <v>161</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5865</v>
+        <v>1.4935</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7216</v>
+        <v>0.6793</v>
       </c>
       <c r="D27" t="n">
-        <v>0.098</v>
+        <v>0.0746</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5865</v>
+        <v>1.4935</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5849</v>
+        <v>1.4935</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0016</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5849</v>
+        <v>1.4935</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6257</v>
+        <v>1.4935</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0016</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6273</v>
+        <v>1.4935</v>
       </c>
       <c r="N27" t="n">
-        <v>156</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5116</v>
+        <v>1.4879</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6876</v>
+        <v>0.6768</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0639</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5116</v>
+        <v>1.4879</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5116</v>
+        <v>1.4879</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5116</v>
+        <v>1.4879</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5116</v>
+        <v>1.4879</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5116</v>
+        <v>1.4879</v>
       </c>
       <c r="N28" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4992</v>
+        <v>1.4646</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6819</v>
+        <v>0.6662</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0583</v>
+        <v>0.0614</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4992</v>
+        <v>1.4646</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0042</v>
+        <v>0.0047</v>
       </c>
       <c r="G29" t="n">
-        <v>1.5034</v>
+        <v>1.4599</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0042</v>
+        <v>0.0047</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0042</v>
+        <v>0.0047</v>
       </c>
       <c r="J29" t="n">
-        <v>1.5034</v>
+        <v>1.4599</v>
       </c>
       <c r="K29" t="n">
         <v>44</v>
@@ -1771,7 +1771,7 @@
         <v>117</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4992</v>
+        <v>1.4646</v>
       </c>
       <c r="N29" t="n">
         <v>161</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4254</v>
+        <v>1.3767</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6484</v>
+        <v>0.6262</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0247</v>
+        <v>0.0214</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4254</v>
+        <v>1.3767</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4419</v>
+        <v>1.3767</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0165</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4419</v>
+        <v>1.3767</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4791</v>
+        <v>1.3767</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0165</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="L30" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4626</v>
+        <v>1.3767</v>
       </c>
       <c r="N30" t="n">
-        <v>190</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.389</v>
+        <v>1.3542</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6318</v>
+        <v>0.616</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0081</v>
+        <v>0.0111</v>
       </c>
       <c r="E31" t="n">
-        <v>1.389</v>
+        <v>1.3542</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2667</v>
+        <v>1.3901</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1223</v>
+        <v>-0.0359</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2667</v>
+        <v>1.3901</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2993</v>
+        <v>1.4272</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1223</v>
+        <v>-0.0359</v>
       </c>
       <c r="K31" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="L31" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4216</v>
+        <v>1.3913</v>
       </c>
       <c r="N31" t="n">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3477</v>
+        <v>1.2851</v>
       </c>
       <c r="C32" t="n">
-        <v>0.613</v>
+        <v>0.5845</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0107</v>
+        <v>-0.0204</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3477</v>
+        <v>1.2851</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0959</v>
+        <v>1.0611</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2518</v>
+        <v>0.224</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0959</v>
+        <v>1.0611</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0959</v>
+        <v>1.0611</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2518</v>
+        <v>0.224</v>
       </c>
       <c r="K32" t="n">
         <v>58</v>
@@ -1909,7 +1909,7 @@
         <v>83</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3477</v>
+        <v>1.2851</v>
       </c>
       <c r="N32" t="n">
         <v>141</v>
@@ -1918,323 +1918,323 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3106</v>
+        <v>1.2759</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5961</v>
+        <v>0.5804</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0276</v>
+        <v>-0.0246</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3106</v>
+        <v>1.2759</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3381</v>
+        <v>1.2759</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9725</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3381</v>
+        <v>1.2759</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3381</v>
+        <v>1.2759</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9725</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L33" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3106</v>
+        <v>1.2759</v>
       </c>
       <c r="N33" t="n">
-        <v>230</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2975</v>
+        <v>1.2363</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5623</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0336</v>
+        <v>-0.0426</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2975</v>
+        <v>1.2363</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2975</v>
+        <v>0.3524</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.8839</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2975</v>
+        <v>0.3524</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2975</v>
+        <v>0.3524</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.8839</v>
       </c>
       <c r="K34" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2975</v>
+        <v>1.2363</v>
       </c>
       <c r="N34" t="n">
-        <v>132</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2791</v>
+        <v>1.2329</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5818</v>
+        <v>0.5608</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0419</v>
+        <v>-0.0441</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2791</v>
+        <v>1.2329</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2791</v>
+        <v>1.1345</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0983</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2791</v>
+        <v>1.1345</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2791</v>
+        <v>1.1649</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.0983</v>
       </c>
       <c r="K35" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2791</v>
+        <v>1.2632</v>
       </c>
       <c r="N35" t="n">
-        <v>92</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.2197</v>
+        <v>1.2188</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5548</v>
+        <v>0.5544</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0506</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2197</v>
+        <v>1.2188</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2197</v>
+        <v>1.2188</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.2197</v>
+        <v>1.2188</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2197</v>
+        <v>1.2188</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.2197</v>
+        <v>1.2188</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.2141</v>
+        <v>1.1628</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5523</v>
+        <v>0.5289</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0761</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2141</v>
+        <v>1.1628</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2141</v>
+        <v>1.1628</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2141</v>
+        <v>1.1628</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2141</v>
+        <v>1.1628</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2141</v>
+        <v>1.1628</v>
       </c>
       <c r="N37" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.212</v>
+        <v>1.1483</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5513</v>
+        <v>0.5223</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0725</v>
+        <v>-0.0827</v>
       </c>
       <c r="E38" t="n">
-        <v>1.212</v>
+        <v>1.1483</v>
       </c>
       <c r="F38" t="n">
-        <v>1.212</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.0584</v>
       </c>
       <c r="H38" t="n">
-        <v>1.212</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>1.212</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1.0584</v>
       </c>
       <c r="K38" t="n">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M38" t="n">
-        <v>1.212</v>
+        <v>1.1483</v>
       </c>
       <c r="N38" t="n">
-        <v>122</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2061</v>
+        <v>1.0625</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5486</v>
+        <v>0.4833</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0752</v>
+        <v>-0.1218</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2061</v>
+        <v>1.0625</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07829999999999999</v>
+        <v>1.0625</v>
       </c>
       <c r="G39" t="n">
-        <v>1.1278</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07829999999999999</v>
+        <v>1.0625</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07829999999999999</v>
+        <v>1.0625</v>
       </c>
       <c r="J39" t="n">
-        <v>1.1278</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L39" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.2061</v>
+        <v>1.0625</v>
       </c>
       <c r="N39" t="n">
-        <v>224</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9452</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4234</v>
+        <v>0.4299</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2004</v>
+        <v>-0.1752</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9452</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9452</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9452</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9452</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9452</v>
       </c>
       <c r="N40" t="n">
         <v>52</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7119</v>
+        <v>0.6915</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3238</v>
+        <v>0.3145</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3001</v>
+        <v>-0.2908</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7119</v>
+        <v>0.6915</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7119</v>
+        <v>0.6915</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7119</v>
+        <v>0.6915</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7119</v>
+        <v>0.6915</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7119</v>
+        <v>0.6915</v>
       </c>
       <c r="N41" t="n">
         <v>52</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6582</v>
+        <v>0.623</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2994</v>
+        <v>0.2834</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3246</v>
+        <v>-0.322</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6582</v>
+        <v>0.623</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6582</v>
+        <v>0.623</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6582</v>
+        <v>0.623</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6582</v>
+        <v>0.623</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6582</v>
+        <v>0.623</v>
       </c>
       <c r="N42" t="n">
         <v>61</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6162</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2854</v>
+        <v>0.2803</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3386</v>
+        <v>-0.3251</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6162</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6274999999999999</v>
+        <v>1.0171</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.4009</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6274999999999999</v>
+        <v>1.0171</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6274999999999999</v>
+        <v>1.0443</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.4009</v>
       </c>
       <c r="K43" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6434</v>
       </c>
       <c r="N43" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.597</v>
+        <v>0.5746</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2716</v>
+        <v>0.2614</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3524</v>
+        <v>-0.344</v>
       </c>
       <c r="E44" t="n">
-        <v>0.597</v>
+        <v>0.5746</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9674</v>
+        <v>0.5746</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9674</v>
+        <v>0.5746</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9923</v>
+        <v>0.5746</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="L44" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6218999999999999</v>
+        <v>0.5746</v>
       </c>
       <c r="N44" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.4951</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2598</v>
+        <v>0.2252</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3642</v>
+        <v>-0.3802</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.4951</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6744</v>
+        <v>0.6061</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1033</v>
+        <v>-0.111</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6744</v>
+        <v>0.6061</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6744</v>
+        <v>0.6061</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.1033</v>
+        <v>-0.111</v>
       </c>
       <c r="K45" t="n">
         <v>45</v>
@@ -2507,7 +2507,7 @@
         <v>179</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5710999999999999</v>
+        <v>0.4951</v>
       </c>
       <c r="N45" t="n">
         <v>224</v>
@@ -2516,185 +2516,185 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4864</v>
+        <v>0.3964</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2212</v>
+        <v>0.1803</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4028</v>
+        <v>-0.4252</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4864</v>
+        <v>0.3964</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2714</v>
+        <v>0.6008</v>
       </c>
       <c r="G46" t="n">
-        <v>0.215</v>
+        <v>-0.2044</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2714</v>
+        <v>0.6008</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2784</v>
+        <v>0.6169</v>
       </c>
       <c r="J46" t="n">
-        <v>0.215</v>
+        <v>-0.2044</v>
       </c>
       <c r="K46" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="L46" t="n">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4933999999999999</v>
+        <v>0.4125</v>
       </c>
       <c r="N46" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>LOVEYY</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4575</v>
+        <v>0.3875</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2081</v>
+        <v>0.1763</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4159</v>
+        <v>-0.4293</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4575</v>
+        <v>0.3875</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4575</v>
+        <v>0.3875</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4575</v>
+        <v>0.3875</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4575</v>
+        <v>0.3875</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4575</v>
+        <v>0.3875</v>
       </c>
       <c r="N47" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LOVEYY</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4464</v>
+        <v>0.3378</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2031</v>
+        <v>0.1537</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.421</v>
+        <v>-0.4519</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4464</v>
+        <v>0.3378</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4464</v>
+        <v>0.3378</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4464</v>
+        <v>0.3378</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4464</v>
+        <v>0.3378</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4464</v>
+        <v>0.3378</v>
       </c>
       <c r="N48" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4065</v>
+        <v>0.3365</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1849</v>
+        <v>0.1531</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4392</v>
+        <v>-0.4525</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4065</v>
+        <v>0.3365</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6001</v>
+        <v>0.2102</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.1936</v>
+        <v>0.1263</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6001</v>
+        <v>0.2102</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6156</v>
+        <v>0.2158</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.1936</v>
+        <v>0.1263</v>
       </c>
       <c r="K49" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="L49" t="n">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="M49" t="n">
-        <v>0.422</v>
+        <v>0.3421</v>
       </c>
       <c r="N49" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3339</v>
+        <v>0.2882</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1519</v>
+        <v>0.1311</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4722</v>
+        <v>-0.4745</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3339</v>
+        <v>0.2882</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3339</v>
+        <v>0.2882</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3339</v>
+        <v>0.2882</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3339</v>
+        <v>0.2882</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3339</v>
+        <v>0.2882</v>
       </c>
       <c r="N50" t="n">
         <v>47</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1736</v>
+        <v>0.1928</v>
       </c>
       <c r="C51" t="n">
-        <v>0.079</v>
+        <v>0.0877</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5452</v>
+        <v>-0.518</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1736</v>
+        <v>0.1928</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1736</v>
+        <v>0.1928</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1736</v>
+        <v>0.1928</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1736</v>
+        <v>0.1928</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1736</v>
+        <v>0.1928</v>
       </c>
       <c r="N51" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.1545</v>
+        <v>0.1295</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0703</v>
+        <v>0.0589</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5468</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1545</v>
+        <v>0.1295</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1545</v>
+        <v>0.1295</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1545</v>
+        <v>0.1295</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1545</v>
+        <v>0.1295</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1545</v>
+        <v>0.1295</v>
       </c>
       <c r="N52" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0658</v>
+        <v>0.077</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0299</v>
+        <v>0.035</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5942</v>
+        <v>-0.5707</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0658</v>
+        <v>0.077</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0658</v>
+        <v>0.077</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0658</v>
+        <v>0.077</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0658</v>
+        <v>0.077</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0658</v>
+        <v>0.077</v>
       </c>
       <c r="N53" t="n">
         <v>90</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0181</v>
+        <v>0.0746</v>
       </c>
       <c r="C54" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0339</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.616</v>
+        <v>-0.5718</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0181</v>
+        <v>0.0746</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0181</v>
+        <v>0.0746</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0181</v>
+        <v>0.0746</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0181</v>
+        <v>0.0746</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0181</v>
+        <v>0.0746</v>
       </c>
       <c r="N54" t="n">
         <v>90</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0271</v>
+        <v>-0.0731</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0123</v>
+        <v>-0.0333</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6365</v>
+        <v>-0.6391</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0271</v>
+        <v>-0.0731</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0271</v>
+        <v>-0.0731</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0271</v>
+        <v>-0.0731</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0271</v>
+        <v>-0.0731</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0271</v>
+        <v>-0.0731</v>
       </c>
       <c r="N55" t="n">
         <v>44</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0437</v>
+        <v>-0.0805</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0199</v>
+        <v>-0.0366</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6441</v>
+        <v>-0.6425</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0437</v>
+        <v>-0.0805</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0437</v>
+        <v>-0.0805</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0437</v>
+        <v>-0.0805</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0437</v>
+        <v>-0.0805</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0437</v>
+        <v>-0.0805</v>
       </c>
       <c r="N56" t="n">
         <v>52</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.127</v>
+        <v>-0.1135</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0578</v>
+        <v>-0.0516</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6575</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.127</v>
+        <v>-0.1135</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.127</v>
+        <v>-0.1135</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.127</v>
+        <v>-0.1135</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.127</v>
+        <v>-0.1135</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.127</v>
+        <v>-0.1135</v>
       </c>
       <c r="N57" t="n">
         <v>61</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1588</v>
+        <v>-0.1355</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0722</v>
+        <v>-0.0616</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6965</v>
+        <v>-0.6675</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1588</v>
+        <v>-0.1355</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1588</v>
+        <v>-0.1355</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1588</v>
+        <v>-0.1355</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1588</v>
+        <v>-0.1355</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1588</v>
+        <v>-0.1355</v>
       </c>
       <c r="N58" t="n">
         <v>47</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1933</v>
+        <v>-0.2169</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0987</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7046</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1933</v>
+        <v>-0.2169</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1933</v>
+        <v>-0.2169</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1933</v>
+        <v>-0.2169</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1933</v>
+        <v>-0.2169</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1933</v>
+        <v>-0.2169</v>
       </c>
       <c r="N59" t="n">
         <v>52</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3115</v>
+        <v>-0.2626</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1417</v>
+        <v>-0.1194</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.766</v>
+        <v>-0.7254</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3115</v>
+        <v>-0.2626</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3115</v>
+        <v>-0.2626</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3115</v>
+        <v>-0.2626</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3115</v>
+        <v>-0.2626</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3115</v>
+        <v>-0.2626</v>
       </c>
       <c r="N60" t="n">
         <v>44</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3344</v>
+        <v>-0.3102</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1521</v>
+        <v>-0.1411</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7764</v>
+        <v>-0.7471</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3344</v>
+        <v>-0.3102</v>
       </c>
       <c r="F61" t="n">
-        <v>1.0103</v>
+        <v>0.9799</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.3447</v>
+        <v>-1.2901</v>
       </c>
       <c r="H61" t="n">
-        <v>1.0103</v>
+        <v>0.9799</v>
       </c>
       <c r="I61" t="n">
-        <v>1.0103</v>
+        <v>0.9799</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.3447</v>
+        <v>-1.2901</v>
       </c>
       <c r="K61" t="n">
         <v>45</v>
@@ -3243,7 +3243,7 @@
         <v>179</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3344</v>
+        <v>-0.3102</v>
       </c>
       <c r="N61" t="n">
         <v>224</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.406</v>
+        <v>-0.3676</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1847</v>
+        <v>-0.1672</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.7732</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.406</v>
+        <v>-0.3676</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.406</v>
+        <v>-0.3676</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.406</v>
+        <v>-0.3676</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.406</v>
+        <v>-0.3676</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.406</v>
+        <v>-0.3676</v>
       </c>
       <c r="N62" t="n">
         <v>61</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4096</v>
+        <v>-0.464</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1863</v>
+        <v>-0.2111</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8107</v>
+        <v>-0.8172</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4096</v>
+        <v>-0.464</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4096</v>
+        <v>-0.464</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4096</v>
+        <v>-0.464</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4096</v>
+        <v>-0.464</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4096</v>
+        <v>-0.464</v>
       </c>
       <c r="N63" t="n">
         <v>92</v>
@@ -3344,231 +3344,231 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4449</v>
+        <v>-0.4891</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2024</v>
+        <v>-0.2225</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8267</v>
+        <v>-0.8286</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4449</v>
+        <v>-0.4891</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4449</v>
+        <v>-0.4891</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4449</v>
+        <v>-0.4891</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4449</v>
+        <v>-0.4891</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4449</v>
+        <v>-0.4891</v>
       </c>
       <c r="N64" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4463</v>
+        <v>-0.4979</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.203</v>
+        <v>-0.2265</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8274</v>
+        <v>-0.8326</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.4463</v>
+        <v>-0.4979</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1153</v>
+        <v>-0.4979</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.331</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1153</v>
+        <v>-0.4979</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1183</v>
+        <v>-0.4979</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.331</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="L65" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.4493</v>
+        <v>-0.4979</v>
       </c>
       <c r="N65" t="n">
-        <v>190</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.521</v>
+        <v>-0.499</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.237</v>
+        <v>-0.227</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.8331</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.521</v>
+        <v>-0.499</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.521</v>
+        <v>-0.499</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.521</v>
+        <v>-0.499</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.521</v>
+        <v>-0.499</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.521</v>
+        <v>-0.499</v>
       </c>
       <c r="N66" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5295</v>
+        <v>-0.5123</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2409</v>
+        <v>-0.233</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8652</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5295</v>
+        <v>-0.5123</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5295</v>
+        <v>-0.5123</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5295</v>
+        <v>-0.5123</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5295</v>
+        <v>-0.5123</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5295</v>
+        <v>-0.5123</v>
       </c>
       <c r="N67" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5389</v>
+        <v>-0.518</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2451</v>
+        <v>-0.2356</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8418</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5389</v>
+        <v>-0.518</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5389</v>
+        <v>0.0134</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>-0.5314</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5389</v>
+        <v>0.0134</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5389</v>
+        <v>0.0138</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>-0.5314</v>
       </c>
       <c r="K68" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5389</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>47</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5612</v>
+        <v>-0.5254</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2553</v>
+        <v>-0.239</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8797</v>
+        <v>-0.8451</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5612</v>
+        <v>-0.5254</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5612</v>
+        <v>-0.5254</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5612</v>
+        <v>-0.5254</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5612</v>
+        <v>-0.5254</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5612</v>
+        <v>-0.5254</v>
       </c>
       <c r="N69" t="n">
         <v>52</v>
@@ -3620,47 +3620,47 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6514</v>
+        <v>-0.5402</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2963</v>
+        <v>-0.2457</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9207</v>
+        <v>-0.8519</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6514</v>
+        <v>-0.5402</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1997</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.5649</v>
+        <v>-0.3405</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1997</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0887</v>
+        <v>-0.205</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5649</v>
+        <v>-0.3405</v>
       </c>
       <c r="K70" t="n">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="L70" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6536</v>
+        <v>-0.5455</v>
       </c>
       <c r="N70" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71">
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6728</v>
+        <v>-0.6348</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.306</v>
+        <v>-0.2887</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9305</v>
+        <v>-0.895</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6728</v>
+        <v>-0.6348</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6728</v>
+        <v>-0.6348</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6728</v>
+        <v>-0.6348</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6728</v>
+        <v>-0.6348</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6728</v>
+        <v>-0.6348</v>
       </c>
       <c r="N71" t="n">
         <v>92</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6872</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3126</v>
+        <v>-0.301</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9073</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6872</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6872</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6872</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6872</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6872</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="N72" t="n">
         <v>44</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7204</v>
+        <v>-0.7167</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3277</v>
+        <v>-0.326</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-0.9323</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7204</v>
+        <v>-0.7167</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7204</v>
+        <v>-0.7167</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7204</v>
+        <v>-0.7167</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7204</v>
+        <v>-0.7167</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7204</v>
+        <v>-0.7167</v>
       </c>
       <c r="N73" t="n">
         <v>47</v>
@@ -3808,31 +3808,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7963</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.3622</v>
+        <v>-0.3377</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9867</v>
+        <v>-0.944</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7963</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.9443</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>0.148</v>
+        <v>0.1543</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.9443</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.9686</v>
+        <v>-0.9207</v>
       </c>
       <c r="J74" t="n">
-        <v>0.148</v>
+        <v>0.1543</v>
       </c>
       <c r="K74" t="n">
         <v>95</v>
@@ -3841,7 +3841,7 @@
         <v>140</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.8206</v>
+        <v>-0.7664</v>
       </c>
       <c r="N74" t="n">
         <v>235</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.364</v>
+        <v>-0.3543</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9885</v>
+        <v>-0.9606</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="N75" t="n">
         <v>44</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8845</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4009</v>
+        <v>-0.4023</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0254</v>
+        <v>-1.0087</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8845</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8845</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8845</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8845</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8845</v>
       </c>
       <c r="N76" t="n">
         <v>92</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.0293</v>
+        <v>-0.9574</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.4682</v>
+        <v>-0.4355</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0928</v>
+        <v>-1.0419</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.0293</v>
+        <v>-0.9574</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.0293</v>
+        <v>-0.9574</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.0293</v>
+        <v>-0.9574</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.0293</v>
+        <v>-0.9574</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.0293</v>
+        <v>-0.9574</v>
       </c>
       <c r="N77" t="n">
         <v>132</v>
@@ -3992,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.038</v>
+        <v>-1.0114</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.4721</v>
+        <v>-0.4601</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0967</v>
+        <v>-1.0665</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.038</v>
+        <v>-1.0114</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.615</v>
+        <v>-0.5471</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.423</v>
+        <v>-0.4643</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.615</v>
+        <v>-0.5471</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.6308</v>
+        <v>-0.5617</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.423</v>
+        <v>-0.4643</v>
       </c>
       <c r="K78" t="n">
         <v>141</v>
@@ -4025,7 +4025,7 @@
         <v>72</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.0538</v>
+        <v>-1.026</v>
       </c>
       <c r="N78" t="n">
         <v>213</v>
@@ -4034,93 +4034,93 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.4282</v>
+        <v>-1.4226</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6496</v>
+        <v>-0.6471</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2743</v>
+        <v>-1.2539</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.4282</v>
+        <v>-1.4226</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.1847</v>
+        <v>-1.3404</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.2435</v>
+        <v>-0.0822</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.1847</v>
+        <v>-1.3404</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2152</v>
+        <v>-1.3404</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.2435</v>
+        <v>-0.0822</v>
       </c>
       <c r="K79" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="L79" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.4587</v>
+        <v>-1.4226</v>
       </c>
       <c r="N79" t="n">
-        <v>190</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.4518</v>
+        <v>-1.4734</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.6604</v>
+        <v>-0.6702</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2851</v>
+        <v>-1.277</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.4518</v>
+        <v>-1.4734</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.3974</v>
+        <v>-1.2016</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.0544</v>
+        <v>-0.2718</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.3974</v>
+        <v>-1.2016</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.3974</v>
+        <v>-1.2337</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.0544</v>
+        <v>-0.2718</v>
       </c>
       <c r="K80" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="L80" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.4518</v>
+        <v>-1.5055</v>
       </c>
       <c r="N80" t="n">
-        <v>141</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81">
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.0015</v>
+        <v>-1.9531</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9104</v>
+        <v>-0.8884</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5353</v>
+        <v>-1.4955</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.0015</v>
+        <v>-1.9531</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.2545</v>
+        <v>-1.2359</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.747</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.2545</v>
+        <v>-1.2359</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.2545</v>
+        <v>-1.2359</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.747</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="K81" t="n">
         <v>58</v>
@@ -4163,7 +4163,7 @@
         <v>83</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.0015</v>
+        <v>-1.9531</v>
       </c>
       <c r="N81" t="n">
         <v>141</v>
@@ -4269,10 +4269,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1253</v>
+        <v>1.1332</v>
       </c>
       <c r="J2" t="n">
-        <v>25.8819</v>
+        <v>26.0636</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1253</v>
+        <v>1.1332</v>
       </c>
       <c r="J3" t="n">
-        <v>25.8819</v>
+        <v>26.0636</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.43</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9798</v>
+        <v>0.974</v>
       </c>
       <c r="J4" t="n">
-        <v>22.5354</v>
+        <v>22.402</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.483</v>
+        <v>0.4525</v>
       </c>
       <c r="J5" t="n">
-        <v>11.109</v>
+        <v>10.4075</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>1.03</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0608</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8883</v>
+        <v>1.3984</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1921</v>
+        <v>0.1554</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4183</v>
+        <v>3.5742</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1861</v>
+        <v>-0.1691</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.2803</v>
+        <v>-3.8893</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2064</v>
+        <v>-0.189</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.7472</v>
+        <v>-4.347</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2162</v>
+        <v>-0.1986</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.9726</v>
+        <v>-4.5678</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.52</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4897</v>
+        <v>-0.4877</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.2631</v>
+        <v>-11.2171</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.41</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9802</v>
+        <v>0.9698</v>
       </c>
       <c r="J12" t="n">
-        <v>39.208</v>
+        <v>38.792</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6148</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>24.592</v>
+        <v>23.204</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.18</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5058</v>
+        <v>0.4691</v>
       </c>
       <c r="J14" t="n">
-        <v>20.232</v>
+        <v>18.764</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1111</v>
+        <v>0.0902</v>
       </c>
       <c r="J15" t="n">
-        <v>4.444</v>
+        <v>3.608</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.95</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2301</v>
+        <v>-0.1931</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.204000000000001</v>
+        <v>-7.724</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4054</v>
+        <v>0.349</v>
       </c>
       <c r="J17" t="n">
-        <v>16.216</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.152</v>
+        <v>0.1168</v>
       </c>
       <c r="J18" t="n">
-        <v>6.08</v>
+        <v>4.672</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.98</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0415</v>
+        <v>-0.0319</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.66</v>
+        <v>-1.276</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2198</v>
+        <v>-0.1993</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.792</v>
+        <v>-7.972</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2198</v>
+        <v>-0.1993</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.792</v>
+        <v>-7.972</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0391</v>
+        <v>1.029</v>
       </c>
       <c r="J22" t="n">
-        <v>30.1339</v>
+        <v>29.841</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.23</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>16.5619</v>
+        <v>16.269</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1475</v>
+        <v>0.1229</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2775</v>
+        <v>3.5641</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1139</v>
+        <v>0.0927</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3031</v>
+        <v>2.6883</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4477</v>
+        <v>-0.4058</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.9833</v>
+        <v>-11.7682</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3704</v>
+        <v>0.3155</v>
       </c>
       <c r="J27" t="n">
-        <v>10.7416</v>
+        <v>9.1495</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1523</v>
+        <v>0.1171</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4167</v>
+        <v>3.3959</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0707</v>
+        <v>-0.0571</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.0503</v>
+        <v>-1.6559</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1331</v>
+        <v>-0.1144</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.8599</v>
+        <v>-3.3176</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2695</v>
+        <v>-0.2501</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.8155</v>
+        <v>-7.2529</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6612</v>
       </c>
       <c r="J32" t="n">
-        <v>18.9252</v>
+        <v>18.5136</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.2</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5445</v>
+        <v>0.5327</v>
       </c>
       <c r="J33" t="n">
-        <v>15.246</v>
+        <v>14.9156</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.01</v>
       </c>
       <c r="I34" t="n">
-        <v>0.057</v>
+        <v>0.0421</v>
       </c>
       <c r="J34" t="n">
-        <v>1.596</v>
+        <v>1.1788</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5446</v>
+        <v>-0.5036</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.2488</v>
+        <v>-14.1008</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.78</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6369</v>
+        <v>-0.6001</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.8332</v>
+        <v>-16.8028</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6521</v>
+        <v>0.6202</v>
       </c>
       <c r="J37" t="n">
-        <v>18.2588</v>
+        <v>17.3656</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6303</v>
+        <v>0.5997</v>
       </c>
       <c r="J38" t="n">
-        <v>17.6484</v>
+        <v>16.7916</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0789</v>
+        <v>-0.0634</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.2092</v>
+        <v>-1.7752</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1764</v>
+        <v>-0.1559</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.9392</v>
+        <v>-4.3652</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2694</v>
+        <v>-0.2506</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.5432</v>
+        <v>-7.0168</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.04</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1535</v>
+        <v>0.1192</v>
       </c>
       <c r="J42" t="n">
-        <v>3.8375</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0241</v>
+        <v>0.0185</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6025</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0241</v>
+        <v>0.0185</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6025</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3433</v>
+        <v>-0.3276</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.5825</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.57</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4508</v>
+        <v>-0.4446</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.27</v>
+        <v>-11.115</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2014</v>
+        <v>1.1987</v>
       </c>
       <c r="J47" t="n">
-        <v>30.035</v>
+        <v>29.9675</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7682</v>
+        <v>0.7537</v>
       </c>
       <c r="J48" t="n">
-        <v>19.205</v>
+        <v>18.8425</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6217</v>
+        <v>0.612</v>
       </c>
       <c r="J49" t="n">
-        <v>15.5425</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1316</v>
+        <v>0.1081</v>
       </c>
       <c r="J50" t="n">
-        <v>3.29</v>
+        <v>2.7025</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6082</v>
+        <v>-0.5744</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.205</v>
+        <v>-14.36</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3116</v>
+        <v>0.2633</v>
       </c>
       <c r="J52" t="n">
-        <v>7.1668</v>
+        <v>6.0559</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1115</v>
+        <v>-0.0968</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.5645</v>
+        <v>-2.2264</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2084</v>
+        <v>-0.1899</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.7932</v>
+        <v>-4.3677</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2953</v>
+        <v>-0.2774</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.7919</v>
+        <v>-6.3802</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3962</v>
+        <v>-0.3844</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.1126</v>
+        <v>-8.841200000000001</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.69</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1773</v>
+        <v>1.1723</v>
       </c>
       <c r="J57" t="n">
-        <v>27.0779</v>
+        <v>26.9629</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.55</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="J58" t="n">
-        <v>22.9379</v>
+        <v>22.6734</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.3</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6574</v>
+        <v>0.6499</v>
       </c>
       <c r="J59" t="n">
-        <v>15.1202</v>
+        <v>14.9477</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1.3</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6574</v>
+        <v>0.6499</v>
       </c>
       <c r="J60" t="n">
-        <v>15.1202</v>
+        <v>14.9477</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4555</v>
+        <v>-0.4191</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.4765</v>
+        <v>-9.6393</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.14</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3408</v>
+        <v>0.2876</v>
       </c>
       <c r="J62" t="n">
-        <v>9.201599999999999</v>
+        <v>7.7652</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2438</v>
+        <v>0.1977</v>
       </c>
       <c r="J63" t="n">
-        <v>6.5826</v>
+        <v>5.3379</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1073</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.8971</v>
+        <v>-2.4543</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1423</v>
+        <v>-0.1236</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.8421</v>
+        <v>-3.3372</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.379</v>
+        <v>-0.3663</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.233</v>
+        <v>-9.8901</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7904</v>
+        <v>0.7743</v>
       </c>
       <c r="J67" t="n">
-        <v>21.3408</v>
+        <v>20.9061</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.32</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7156</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
-        <v>19.3212</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5593</v>
+        <v>0.549</v>
       </c>
       <c r="J69" t="n">
-        <v>15.1011</v>
+        <v>14.823</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4674</v>
+        <v>-0.4255</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.6198</v>
+        <v>-11.4885</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5874</v>
+        <v>-0.5495</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.8598</v>
+        <v>-14.8365</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.464</v>
+        <v>0.4062</v>
       </c>
       <c r="J72" t="n">
-        <v>12.992</v>
+        <v>11.3736</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4171</v>
+        <v>0.354</v>
       </c>
       <c r="J73" t="n">
-        <v>11.6788</v>
+        <v>9.912000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1594</v>
+        <v>0.1242</v>
       </c>
       <c r="J74" t="n">
-        <v>4.4632</v>
+        <v>3.4776</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0969</v>
+        <v>0.0723</v>
       </c>
       <c r="J75" t="n">
-        <v>2.7132</v>
+        <v>2.0244</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0112</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.3136</v>
+        <v>-0.2464</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.203</v>
+        <v>0.1861</v>
       </c>
       <c r="J77" t="n">
-        <v>5.684</v>
+        <v>5.2108</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.09</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1873</v>
+        <v>0.1701</v>
       </c>
       <c r="J78" t="n">
-        <v>5.2444</v>
+        <v>4.7628</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1378</v>
+        <v>0.1208</v>
       </c>
       <c r="J79" t="n">
-        <v>3.8584</v>
+        <v>3.3824</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.3484</v>
+        <v>-3.7996</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3538</v>
+        <v>-0.3392</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.9064</v>
+        <v>-9.4976</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.34</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6022</v>
       </c>
       <c r="J82" t="n">
-        <v>17.57</v>
+        <v>16.8616</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1049</v>
+        <v>-0.0897</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.9372</v>
+        <v>-2.5116</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1926</v>
+        <v>-0.1731</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.3928</v>
+        <v>-4.8468</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3292</v>
+        <v>-0.3126</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.217599999999999</v>
+        <v>-8.752800000000001</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.68</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3568</v>
+        <v>-0.3421</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.990399999999999</v>
+        <v>-9.578799999999999</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8386</v>
+        <v>0.8236</v>
       </c>
       <c r="J87" t="n">
-        <v>23.4808</v>
+        <v>23.0608</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7393</v>
       </c>
       <c r="J88" t="n">
-        <v>21.098</v>
+        <v>20.7004</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.21</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5304</v>
+        <v>0.524</v>
       </c>
       <c r="J89" t="n">
-        <v>14.8512</v>
+        <v>14.672</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>1.12</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3551</v>
+        <v>0.3223</v>
       </c>
       <c r="J90" t="n">
-        <v>9.9428</v>
+        <v>9.0244</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2503</v>
+        <v>0.2199</v>
       </c>
       <c r="J91" t="n">
-        <v>7.0084</v>
+        <v>6.1572</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5092</v>
+        <v>0.4942</v>
       </c>
       <c r="J92" t="n">
-        <v>15.276</v>
+        <v>14.826</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4757</v>
+        <v>0.45</v>
       </c>
       <c r="J93" t="n">
-        <v>14.271</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4757</v>
+        <v>0.45</v>
       </c>
       <c r="J94" t="n">
-        <v>14.271</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.296</v>
+        <v>0.2612</v>
       </c>
       <c r="J95" t="n">
-        <v>8.880000000000001</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0794</v>
+        <v>-0.0588</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.382</v>
+        <v>-1.764</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4588</v>
+        <v>0.4081</v>
       </c>
       <c r="J97" t="n">
-        <v>13.764</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I98" t="n">
-        <v>0.073</v>
+        <v>0.0522</v>
       </c>
       <c r="J98" t="n">
-        <v>2.19</v>
+        <v>1.566</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0254</v>
+        <v>-0.0182</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.762</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1118</v>
+        <v>-0.094</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.354</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.86</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1913</v>
+        <v>-0.1706</v>
       </c>
       <c r="J101" t="n">
-        <v>-5.739</v>
+        <v>-5.118</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.84</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4272</v>
+        <v>1.4497</v>
       </c>
       <c r="J102" t="n">
-        <v>41.3888</v>
+        <v>42.0413</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2111</v>
+        <v>0.1814</v>
       </c>
       <c r="J103" t="n">
-        <v>6.1219</v>
+        <v>5.2606</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.116</v>
+        <v>0.0946</v>
       </c>
       <c r="J104" t="n">
-        <v>3.364</v>
+        <v>2.7434</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3942</v>
+        <v>-0.3518</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.4318</v>
+        <v>-10.2022</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5193</v>
+        <v>-0.479</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.0597</v>
+        <v>-13.891</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.65</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9094</v>
       </c>
       <c r="J107" t="n">
-        <v>27.289</v>
+        <v>26.3726</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.96</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0575</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.0706</v>
+        <v>-1.6675</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2207</v>
+        <v>-0.2002</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.4003</v>
+        <v>-5.8058</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.241</v>
+        <v>-0.2208</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.989</v>
+        <v>-6.4032</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3736</v>
+        <v>-0.3608</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.8344</v>
+        <v>-10.4632</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3898</v>
+        <v>0.4036</v>
       </c>
       <c r="J112" t="n">
-        <v>8.5756</v>
+        <v>8.879200000000001</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.86</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1644</v>
+        <v>-0.1488</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.6168</v>
+        <v>-3.2736</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2758</v>
+        <v>-0.2605</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.0676</v>
+        <v>-5.731</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.47</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5243</v>
+        <v>-0.526</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.5346</v>
+        <v>-11.572</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.41</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.5855</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.6742</v>
+        <v>-12.881</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>2.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9656</v>
+        <v>0.9081</v>
       </c>
       <c r="J117" t="n">
-        <v>21.2432</v>
+        <v>19.9782</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.47</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5383</v>
+        <v>0.5027</v>
       </c>
       <c r="J118" t="n">
-        <v>11.8426</v>
+        <v>11.0594</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.23</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3216</v>
+        <v>0.2701</v>
       </c>
       <c r="J119" t="n">
-        <v>7.0752</v>
+        <v>5.9422</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>1.15</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2229</v>
+        <v>0.1808</v>
       </c>
       <c r="J120" t="n">
-        <v>4.9038</v>
+        <v>3.9776</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1275</v>
+        <v>-0.1114</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.805</v>
+        <v>-2.4508</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6268</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>17.5504</v>
+        <v>17.2312</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5651</v>
+        <v>0.5569</v>
       </c>
       <c r="J123" t="n">
-        <v>15.8228</v>
+        <v>15.5932</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5651</v>
+        <v>0.5569</v>
       </c>
       <c r="J124" t="n">
-        <v>15.8228</v>
+        <v>15.5932</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.13</v>
       </c>
       <c r="I125" t="n">
-        <v>0.387</v>
+        <v>0.3525</v>
       </c>
       <c r="J125" t="n">
-        <v>10.836</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>1.1</v>
       </c>
       <c r="I126" t="n">
-        <v>0.3115</v>
+        <v>0.2785</v>
       </c>
       <c r="J126" t="n">
-        <v>8.722</v>
+        <v>7.798</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>0.86</v>
+        <v>0.8321</v>
       </c>
       <c r="J127" t="n">
-        <v>24.08</v>
+        <v>23.2988</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.251</v>
+        <v>0.2045</v>
       </c>
       <c r="J128" t="n">
-        <v>7.028</v>
+        <v>5.726</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.73</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3117</v>
+        <v>-0.2942</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.727600000000001</v>
+        <v>-8.2376</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.321</v>
+        <v>-0.304</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.988</v>
+        <v>-8.512</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.48</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5332</v>
+        <v>-0.5385</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.9296</v>
+        <v>-15.078</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.5</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9378</v>
+        <v>0.9244</v>
       </c>
       <c r="J132" t="n">
-        <v>20.6316</v>
+        <v>20.3368</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8837</v>
+        <v>0.87</v>
       </c>
       <c r="J133" t="n">
-        <v>19.4414</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.24</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5713</v>
+        <v>0.5666</v>
       </c>
       <c r="J134" t="n">
-        <v>12.5686</v>
+        <v>12.4652</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>1.18</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4747</v>
+        <v>0.4566</v>
       </c>
       <c r="J135" t="n">
-        <v>10.4434</v>
+        <v>10.0452</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3697</v>
+        <v>0.3376</v>
       </c>
       <c r="J136" t="n">
-        <v>8.1334</v>
+        <v>7.4272</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0012</v>
+        <v>0.0059</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.0264</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>0.91</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1165</v>
+        <v>-0.1019</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.563</v>
+        <v>-2.2418</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1624</v>
+        <v>-0.1465</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.5728</v>
+        <v>-3.223</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1624</v>
+        <v>-0.1465</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.5728</v>
+        <v>-3.223</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.33</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6496</v>
+        <v>-0.6728</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.2912</v>
+        <v>-14.8016</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9832</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>23.5968</v>
+        <v>23.2872</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8193</v>
+        <v>0.8051</v>
       </c>
       <c r="J143" t="n">
-        <v>19.6632</v>
+        <v>19.3224</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I144" t="n">
-        <v>0.511</v>
+        <v>0.5031</v>
       </c>
       <c r="J144" t="n">
-        <v>12.264</v>
+        <v>12.0744</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.13</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3745</v>
+        <v>0.342</v>
       </c>
       <c r="J145" t="n">
-        <v>8.988</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>1.09</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2719</v>
+        <v>0.2409</v>
       </c>
       <c r="J146" t="n">
-        <v>6.5256</v>
+        <v>5.7816</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1843</v>
+        <v>0.147</v>
       </c>
       <c r="J147" t="n">
-        <v>4.4232</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1981</v>
+        <v>-0.1801</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.7544</v>
+        <v>-4.3224</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.82</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2176</v>
+        <v>-0.1992</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.2224</v>
+        <v>-4.7808</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2371</v>
+        <v>-0.2185</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.6904</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.68</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3501</v>
+        <v>-0.3349</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.4024</v>
+        <v>-8.037599999999999</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0521</v>
+        <v>0.056</v>
       </c>
       <c r="J152" t="n">
-        <v>1.2504</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.68</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3382</v>
+        <v>-0.3238</v>
       </c>
       <c r="J153" t="n">
-        <v>-8.1168</v>
+        <v>-7.7712</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3382</v>
+        <v>-0.3238</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.1168</v>
+        <v>-7.7712</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3472</v>
+        <v>-0.3331</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.332800000000001</v>
+        <v>-7.9944</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.63</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3831</v>
+        <v>-0.3707</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.1944</v>
+        <v>-8.896800000000001</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.64</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="J157" t="n">
-        <v>15.9552</v>
+        <v>14.928</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4422</v>
+        <v>0.3838</v>
       </c>
       <c r="J158" t="n">
-        <v>10.6128</v>
+        <v>9.2112</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3491</v>
+        <v>0.2945</v>
       </c>
       <c r="J159" t="n">
-        <v>8.378399999999999</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.25</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3491</v>
+        <v>0.2945</v>
       </c>
       <c r="J160" t="n">
-        <v>8.378399999999999</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.13</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2011</v>
+        <v>0.1614</v>
       </c>
       <c r="J161" t="n">
-        <v>4.8264</v>
+        <v>3.8736</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0633</v>
+        <v>1.0548</v>
       </c>
       <c r="J162" t="n">
-        <v>22.3293</v>
+        <v>22.1508</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9246</v>
       </c>
       <c r="J163" t="n">
-        <v>19.635</v>
+        <v>19.4166</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8174</v>
+        <v>0.8079</v>
       </c>
       <c r="J164" t="n">
-        <v>17.1654</v>
+        <v>16.9659</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.3</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6501</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>13.6521</v>
+        <v>13.5387</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>1.26</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5899</v>
+        <v>0.5867</v>
       </c>
       <c r="J166" t="n">
-        <v>12.3879</v>
+        <v>12.3207</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.71</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.295</v>
+        <v>-0.2834</v>
       </c>
       <c r="J167" t="n">
-        <v>-6.195</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.63</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3694</v>
+        <v>-0.3605</v>
       </c>
       <c r="J168" t="n">
-        <v>-7.7574</v>
+        <v>-7.5705</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.6</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3945</v>
+        <v>-0.3862</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.2845</v>
+        <v>-8.110200000000001</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.58</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4115</v>
+        <v>-0.4036</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.641500000000001</v>
+        <v>-8.4756</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.52</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4637</v>
+        <v>-0.4587</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.7377</v>
+        <v>-9.6327</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.31</v>
       </c>
       <c r="I172" t="n">
-        <v>0.788</v>
+        <v>0.761</v>
       </c>
       <c r="J172" t="n">
-        <v>23.64</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.705</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>21.15</v>
+        <v>20.187</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>0.705</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>21.15</v>
+        <v>20.187</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.91</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3412</v>
+        <v>-0.2994</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.236</v>
+        <v>-8.981999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3412</v>
+        <v>-0.2994</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.236</v>
+        <v>-8.981999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.2</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4366</v>
+        <v>0.379</v>
       </c>
       <c r="J177" t="n">
-        <v>13.098</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4366</v>
+        <v>0.379</v>
       </c>
       <c r="J178" t="n">
-        <v>13.098</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>0.96</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0717</v>
+        <v>-0.0577</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.151</v>
+        <v>-1.731</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.89</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1572</v>
+        <v>-0.1373</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.716</v>
+        <v>-4.119</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3558</v>
+        <v>-0.3415</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.674</v>
+        <v>-10.245</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1828</v>
+        <v>1.1997</v>
       </c>
       <c r="J182" t="n">
-        <v>22.4732</v>
+        <v>22.7943</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.57</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1574</v>
+        <v>1.1738</v>
       </c>
       <c r="J183" t="n">
-        <v>21.9906</v>
+        <v>22.3022</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.44</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9806</v>
+        <v>0.9832</v>
       </c>
       <c r="J184" t="n">
-        <v>18.6314</v>
+        <v>18.6808</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.31</v>
       </c>
       <c r="I185" t="n">
-        <v>0.742</v>
+        <v>0.7251</v>
       </c>
       <c r="J185" t="n">
-        <v>14.098</v>
+        <v>13.7769</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>1.28</v>
       </c>
       <c r="I186" t="n">
-        <v>0.6818</v>
+        <v>0.6613</v>
       </c>
       <c r="J186" t="n">
-        <v>12.9542</v>
+        <v>12.5647</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>0.76</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2637</v>
+        <v>-0.2492</v>
       </c>
       <c r="J187" t="n">
-        <v>-5.0103</v>
+        <v>-4.7348</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2733</v>
+        <v>-0.2588</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.1927</v>
+        <v>-4.9172</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.75</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2733</v>
+        <v>-0.2588</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.1927</v>
+        <v>-4.9172</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.67</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3447</v>
+        <v>-0.3311</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.5493</v>
+        <v>-6.2909</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.62</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3893</v>
+        <v>-0.3776</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.3967</v>
+        <v>-7.1744</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3151</v>
+        <v>0.2672</v>
       </c>
       <c r="J192" t="n">
-        <v>7.2473</v>
+        <v>6.1456</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.96</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0577</v>
+        <v>-0.0469</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.3271</v>
+        <v>-1.0787</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3036</v>
+        <v>-0.2862</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.9828</v>
+        <v>-6.5826</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.313</v>
+        <v>-0.2959</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.199</v>
+        <v>-6.8057</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.66</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3681</v>
+        <v>-0.3541</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.4663</v>
+        <v>-8.144299999999999</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.4</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9493</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>21.8339</v>
+        <v>21.574</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.36</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8729</v>
+        <v>0.8536</v>
       </c>
       <c r="J198" t="n">
-        <v>20.0767</v>
+        <v>19.6328</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4339</v>
+        <v>0.3992</v>
       </c>
       <c r="J199" t="n">
-        <v>9.979699999999999</v>
+        <v>9.1816</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3106</v>
+        <v>0.2777</v>
       </c>
       <c r="J200" t="n">
-        <v>7.1438</v>
+        <v>6.3871</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.98</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1345</v>
+        <v>-0.1073</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.0935</v>
+        <v>-2.4679</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5262</v>
+        <v>0.4569</v>
       </c>
       <c r="J202" t="n">
-        <v>13.6812</v>
+        <v>11.8794</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5047</v>
+        <v>0.4363</v>
       </c>
       <c r="J203" t="n">
-        <v>13.1222</v>
+        <v>11.3438</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2144</v>
+        <v>0.1714</v>
       </c>
       <c r="J204" t="n">
-        <v>5.5744</v>
+        <v>4.4564</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.02</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0404</v>
+        <v>0.0276</v>
       </c>
       <c r="J205" t="n">
-        <v>1.0504</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1607</v>
+        <v>-0.141</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.1782</v>
+        <v>-3.666</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4019</v>
+        <v>0.3989</v>
       </c>
       <c r="J207" t="n">
-        <v>10.4494</v>
+        <v>10.3714</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1314</v>
+        <v>0.1155</v>
       </c>
       <c r="J208" t="n">
-        <v>3.4164</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.0182</v>
+        <v>-0.0078</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1128</v>
+        <v>-0.0948</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.9328</v>
+        <v>-2.4648</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.84</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2133</v>
+        <v>-0.1927</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.5458</v>
+        <v>-5.0102</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3196</v>
+        <v>0.2676</v>
       </c>
       <c r="J212" t="n">
-        <v>8.9488</v>
+        <v>7.4928</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0226</v>
+        <v>-0.0167</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.6328</v>
+        <v>-0.4676</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0402</v>
+        <v>-0.0312</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.1256</v>
+        <v>-0.8736</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.6796</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.73</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3156</v>
+        <v>-0.2983</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.8368</v>
+        <v>-8.352399999999999</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.6</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2271</v>
+        <v>1.243</v>
       </c>
       <c r="J217" t="n">
-        <v>34.3588</v>
+        <v>34.804</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.23</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6032</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>16.8896</v>
+        <v>16.0468</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5515</v>
       </c>
       <c r="J219" t="n">
-        <v>16.3016</v>
+        <v>15.442</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>1.14</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4016</v>
+        <v>0.3688</v>
       </c>
       <c r="J220" t="n">
-        <v>11.2448</v>
+        <v>10.3264</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>1.08</v>
       </c>
       <c r="I221" t="n">
-        <v>0.2477</v>
+        <v>0.2174</v>
       </c>
       <c r="J221" t="n">
-        <v>6.9356</v>
+        <v>6.0872</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1934</v>
+        <v>-0.1765</v>
       </c>
       <c r="J222" t="n">
-        <v>-3.868</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.72</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2869</v>
+        <v>-0.2748</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.738</v>
+        <v>-5.496</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.64</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3617</v>
+        <v>-0.3522</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.234</v>
+        <v>-7.044</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4211</v>
+        <v>-0.4133</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.422000000000001</v>
+        <v>-8.266</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.34</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6233</v>
+        <v>-0.6388</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.466</v>
+        <v>-12.776</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.71</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7937</v>
+        <v>0.7227</v>
       </c>
       <c r="J227" t="n">
-        <v>15.874</v>
+        <v>14.454</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.51</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6067</v>
+        <v>0.5389</v>
       </c>
       <c r="J228" t="n">
-        <v>12.134</v>
+        <v>10.778</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.51</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6067</v>
+        <v>0.5389</v>
       </c>
       <c r="J229" t="n">
-        <v>12.134</v>
+        <v>10.778</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.38</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4802</v>
+        <v>0.4187</v>
       </c>
       <c r="J230" t="n">
-        <v>9.603999999999999</v>
+        <v>8.374000000000001</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1905</v>
+        <v>0.1518</v>
       </c>
       <c r="J231" t="n">
-        <v>3.81</v>
+        <v>3.036</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.4</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9761</v>
+        <v>0.9689</v>
       </c>
       <c r="J232" t="n">
-        <v>27.3308</v>
+        <v>27.1292</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.11</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3494</v>
+        <v>0.3113</v>
       </c>
       <c r="J233" t="n">
-        <v>9.783200000000001</v>
+        <v>8.7164</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.245</v>
+        <v>0.2119</v>
       </c>
       <c r="J234" t="n">
-        <v>6.86</v>
+        <v>5.9332</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>1.03</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1218</v>
+        <v>0.0993</v>
       </c>
       <c r="J235" t="n">
-        <v>3.4104</v>
+        <v>2.7804</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4136</v>
+        <v>-0.3708</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.5808</v>
+        <v>-10.3824</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.06</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1748</v>
+        <v>0.1365</v>
       </c>
       <c r="J237" t="n">
-        <v>4.8944</v>
+        <v>3.822</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.03</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1039</v>
+        <v>0.0765</v>
       </c>
       <c r="J238" t="n">
-        <v>2.9092</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J239" t="n">
-        <v>1.3048</v>
+        <v>0.8736</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0027</v>
+        <v>0.0013</v>
       </c>
       <c r="J240" t="n">
-        <v>0.0756</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.76</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2888</v>
+        <v>-0.2702</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.086399999999999</v>
+        <v>-7.5656</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.32</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8171</v>
+        <v>0.7919</v>
       </c>
       <c r="J242" t="n">
-        <v>24.513</v>
+        <v>23.757</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.19</v>
       </c>
       <c r="I243" t="n">
-        <v>0.538</v>
+        <v>0.4989</v>
       </c>
       <c r="J243" t="n">
-        <v>16.14</v>
+        <v>14.967</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.05</v>
       </c>
       <c r="I244" t="n">
-        <v>0.186</v>
+        <v>0.1573</v>
       </c>
       <c r="J244" t="n">
-        <v>5.58</v>
+        <v>4.719</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1546</v>
+        <v>0.1287</v>
       </c>
       <c r="J245" t="n">
-        <v>4.638</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.91</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3351</v>
+        <v>-0.2931</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.053</v>
+        <v>-8.792999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.58</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9992</v>
+        <v>0.9686</v>
       </c>
       <c r="J247" t="n">
-        <v>29.976</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1889</v>
+        <v>0.1497</v>
       </c>
       <c r="J248" t="n">
-        <v>5.667</v>
+        <v>4.491</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1485</v>
+        <v>-0.1287</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.455</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.82</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.234</v>
+        <v>-0.2137</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.02</v>
+        <v>-6.411</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.72</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3308</v>
+        <v>-0.3149</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.923999999999999</v>
+        <v>-9.446999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.66</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2874</v>
+        <v>1.3061</v>
       </c>
       <c r="J252" t="n">
-        <v>27.0354</v>
+        <v>27.4281</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.47</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0374</v>
+        <v>1.0437</v>
       </c>
       <c r="J253" t="n">
-        <v>21.7854</v>
+        <v>21.9177</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.24</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6128</v>
+        <v>0.5865</v>
       </c>
       <c r="J254" t="n">
-        <v>12.8688</v>
+        <v>12.3165</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5485</v>
+        <v>0.52</v>
       </c>
       <c r="J255" t="n">
-        <v>11.5185</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>1.12</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3388</v>
+        <v>0.3069</v>
       </c>
       <c r="J256" t="n">
-        <v>7.1148</v>
+        <v>6.4449</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>0.78</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2445</v>
+        <v>-0.2297</v>
       </c>
       <c r="J257" t="n">
-        <v>-5.1345</v>
+        <v>-4.8237</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>0.76</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.264</v>
+        <v>-0.2494</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.544</v>
+        <v>-5.2374</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.71</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3096</v>
+        <v>-0.2954</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.5016</v>
+        <v>-6.2034</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.67</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3449</v>
+        <v>-0.3313</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.2429</v>
+        <v>-6.9573</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3717</v>
+        <v>-0.3591</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.8057</v>
+        <v>-7.5411</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5349</v>
+        <v>1.5809</v>
       </c>
       <c r="J262" t="n">
-        <v>44.5121</v>
+        <v>45.8461</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1549</v>
+        <v>0.1289</v>
       </c>
       <c r="J263" t="n">
-        <v>4.4921</v>
+        <v>3.7381</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0552</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.1866</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.98</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1168</v>
+        <v>-0.09</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.3872</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8495</v>
+        <v>-0.8312</v>
       </c>
       <c r="J266" t="n">
-        <v>-24.6355</v>
+        <v>-24.1048</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.39</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6542</v>
       </c>
       <c r="J267" t="n">
-        <v>20.6538</v>
+        <v>18.9718</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.16</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3489</v>
+        <v>0.2965</v>
       </c>
       <c r="J268" t="n">
-        <v>10.1181</v>
+        <v>8.5985</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2959</v>
+        <v>0.2476</v>
       </c>
       <c r="J269" t="n">
-        <v>8.581099999999999</v>
+        <v>7.1804</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0646</v>
+        <v>-0.0507</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.8734</v>
+        <v>-1.4703</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.77</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.289</v>
+        <v>-0.2711</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.381</v>
+        <v>-7.8619</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.83</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4828</v>
+        <v>1.513</v>
       </c>
       <c r="J272" t="n">
-        <v>29.656</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.51</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0822</v>
+        <v>1.0962</v>
       </c>
       <c r="J273" t="n">
-        <v>21.644</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.4</v>
       </c>
       <c r="I274" t="n">
-        <v>0.915</v>
+        <v>0.9089</v>
       </c>
       <c r="J274" t="n">
-        <v>18.3</v>
+        <v>18.178</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1.22</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5584</v>
+        <v>0.5316</v>
       </c>
       <c r="J275" t="n">
-        <v>11.168</v>
+        <v>10.632</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>1.14</v>
       </c>
       <c r="I276" t="n">
-        <v>0.3759</v>
+        <v>0.3438</v>
       </c>
       <c r="J276" t="n">
-        <v>7.518</v>
+        <v>6.876</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>0.93</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0447</v>
       </c>
       <c r="J277" t="n">
-        <v>-1.254</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.76</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2562</v>
+        <v>-0.2424</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.124</v>
+        <v>-4.848</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3228</v>
+        <v>-0.3107</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.456</v>
+        <v>-6.214</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.47</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5154</v>
+        <v>-0.5153</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.308</v>
+        <v>-10.306</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5241</v>
+        <v>-0.5251</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.482</v>
+        <v>-10.502</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.68</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3309</v>
+        <v>1.3523</v>
       </c>
       <c r="J282" t="n">
-        <v>31.9416</v>
+        <v>32.4552</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.38</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8995</v>
+        <v>0.8842</v>
       </c>
       <c r="J283" t="n">
-        <v>21.588</v>
+        <v>21.2208</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7831</v>
+        <v>0.7601</v>
       </c>
       <c r="J284" t="n">
-        <v>18.7944</v>
+        <v>18.2424</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.03</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0946</v>
+        <v>0.0741</v>
       </c>
       <c r="J285" t="n">
-        <v>2.2704</v>
+        <v>1.7784</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4671</v>
+        <v>-0.4283</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.2104</v>
+        <v>-10.2792</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.23</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5038</v>
+        <v>0.4466</v>
       </c>
       <c r="J287" t="n">
-        <v>12.0912</v>
+        <v>10.7184</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.18</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4172</v>
+        <v>0.3612</v>
       </c>
       <c r="J288" t="n">
-        <v>10.0128</v>
+        <v>8.668799999999999</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>0.92</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1183</v>
+        <v>-0.1014</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.8392</v>
+        <v>-2.4336</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.89</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1523</v>
+        <v>-0.1334</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.6552</v>
+        <v>-3.2016</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.43</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5765</v>
+        <v>-0.5887</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.836</v>
+        <v>-14.1288</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>0.99</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.1495</v>
+        <v>-0.0483</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0833</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.9159</v>
+        <v>-1.6215</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.89</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1439</v>
+        <v>-0.128</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.3097</v>
+        <v>-2.944</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.7</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3302</v>
+        <v>-0.314</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.5946</v>
+        <v>-7.222</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.6</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4206</v>
+        <v>-0.4109</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.6738</v>
+        <v>-9.450699999999999</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.96</v>
       </c>
       <c r="I297" t="n">
-        <v>1.6772</v>
+        <v>1.7283</v>
       </c>
       <c r="J297" t="n">
-        <v>38.5756</v>
+        <v>39.7509</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.29</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7219</v>
+        <v>0.6968</v>
       </c>
       <c r="J298" t="n">
-        <v>16.6037</v>
+        <v>16.0264</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.09</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2719</v>
+        <v>0.2409</v>
       </c>
       <c r="J299" t="n">
-        <v>6.2537</v>
+        <v>5.5407</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0139</v>
+        <v>0.0037</v>
       </c>
       <c r="J300" t="n">
-        <v>0.3197</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I301" t="n">
-        <v>0.0139</v>
+        <v>0.0037</v>
       </c>
       <c r="J301" t="n">
-        <v>0.3197</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.43</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8159</v>
+        <v>0.769</v>
       </c>
       <c r="J302" t="n">
-        <v>28.5565</v>
+        <v>26.915</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.9</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1424</v>
+        <v>-0.1237</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.984</v>
+        <v>-4.3295</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1536</v>
+        <v>-0.1344</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.376</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2172</v>
+        <v>-0.1969</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.602</v>
+        <v>-6.8915</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3611</v>
+        <v>-0.3469</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.6385</v>
+        <v>-12.1415</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.4</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9631</v>
       </c>
       <c r="J307" t="n">
-        <v>33.9955</v>
+        <v>33.7085</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.28</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7308</v>
+        <v>0.6997</v>
       </c>
       <c r="J308" t="n">
-        <v>25.578</v>
+        <v>24.4895</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.2</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5198</v>
       </c>
       <c r="J309" t="n">
-        <v>19.53</v>
+        <v>18.193</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.89</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3908</v>
+        <v>-0.3481</v>
       </c>
       <c r="J310" t="n">
-        <v>-13.678</v>
+        <v>-12.1835</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6102</v>
+        <v>-0.5734</v>
       </c>
       <c r="J311" t="n">
-        <v>-21.357</v>
+        <v>-20.069</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.79</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4904</v>
+        <v>1.5261</v>
       </c>
       <c r="J312" t="n">
-        <v>38.7504</v>
+        <v>39.6786</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.15</v>
       </c>
       <c r="I313" t="n">
-        <v>0.435</v>
+        <v>0.3999</v>
       </c>
       <c r="J313" t="n">
-        <v>11.31</v>
+        <v>10.3974</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.08</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2583</v>
+        <v>0.2272</v>
       </c>
       <c r="J314" t="n">
-        <v>6.7158</v>
+        <v>5.9072</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1395</v>
+        <v>0.1158</v>
       </c>
       <c r="J315" t="n">
-        <v>3.627</v>
+        <v>3.0108</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.89</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4047</v>
+        <v>-0.3635</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.5222</v>
+        <v>-9.451000000000001</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.36</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7512</v>
+        <v>0.7096</v>
       </c>
       <c r="J317" t="n">
-        <v>19.5312</v>
+        <v>18.4496</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4633</v>
+        <v>0.4109</v>
       </c>
       <c r="J318" t="n">
-        <v>12.0458</v>
+        <v>10.6834</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.83</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2084</v>
+        <v>-0.1899</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.4184</v>
+        <v>-4.9374</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.43</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5698</v>
+        <v>-0.5798</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.8148</v>
+        <v>-15.0748</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.42</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5782</v>
+        <v>-0.5896</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.0332</v>
+        <v>-15.3296</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.15</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3859</v>
+        <v>0.3339</v>
       </c>
       <c r="J322" t="n">
-        <v>9.647500000000001</v>
+        <v>8.3475</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.05</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1789</v>
+        <v>0.1414</v>
       </c>
       <c r="J323" t="n">
-        <v>4.4725</v>
+        <v>3.535</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.73</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.3057</v>
+        <v>-0.2882</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.6425</v>
+        <v>-7.205</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.68</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.352</v>
+        <v>-0.3369</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.422499999999999</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3611</v>
+        <v>-0.3467</v>
       </c>
       <c r="J326" t="n">
-        <v>-9.0275</v>
+        <v>-8.6675</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.61</v>
       </c>
       <c r="I327" t="n">
-        <v>1.2447</v>
+        <v>1.2616</v>
       </c>
       <c r="J327" t="n">
-        <v>31.1175</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8262</v>
+        <v>0.8048</v>
       </c>
       <c r="J328" t="n">
-        <v>20.655</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.13</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3805</v>
+        <v>0.3473</v>
       </c>
       <c r="J329" t="n">
-        <v>9.512499999999999</v>
+        <v>8.682499999999999</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>1.05</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1637</v>
+        <v>0.1378</v>
       </c>
       <c r="J330" t="n">
-        <v>4.0925</v>
+        <v>3.445</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>1.04</v>
       </c>
       <c r="I331" t="n">
-        <v>0.132</v>
+        <v>0.1084</v>
       </c>
       <c r="J331" t="n">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.77</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4202</v>
+        <v>1.4463</v>
       </c>
       <c r="J332" t="n">
-        <v>29.8242</v>
+        <v>30.3723</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.37</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8649</v>
+        <v>0.8525</v>
       </c>
       <c r="J333" t="n">
-        <v>18.1629</v>
+        <v>17.9025</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.29</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7119</v>
+        <v>0.6909</v>
       </c>
       <c r="J334" t="n">
-        <v>14.9499</v>
+        <v>14.5089</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>1.24</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6091</v>
+        <v>0.5834</v>
       </c>
       <c r="J335" t="n">
-        <v>12.7911</v>
+        <v>12.2514</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>1.16</v>
       </c>
       <c r="I336" t="n">
-        <v>0.4317</v>
+        <v>0.4005</v>
       </c>
       <c r="J336" t="n">
-        <v>9.0657</v>
+        <v>8.410500000000001</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>0.99</v>
       </c>
       <c r="I337" t="n">
-        <v>0.02</v>
+        <v>0.0301</v>
       </c>
       <c r="J337" t="n">
-        <v>0.42</v>
+        <v>0.6321</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>0.97</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0236</v>
+        <v>-0.0125</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.4956</v>
+        <v>-0.2625</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.9</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1182</v>
+        <v>-0.103</v>
       </c>
       <c r="J339" t="n">
-        <v>-2.4822</v>
+        <v>-2.163</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4455</v>
+        <v>-0.4381</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.355499999999999</v>
+        <v>-9.200100000000001</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.25</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7121</v>
+        <v>-0.7473</v>
       </c>
       <c r="J341" t="n">
-        <v>-14.9541</v>
+        <v>-15.6933</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.64</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1078</v>
+        <v>1.1093</v>
       </c>
       <c r="J342" t="n">
-        <v>28.8028</v>
+        <v>28.8418</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>0.8</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.2433</v>
+        <v>-0.2236</v>
       </c>
       <c r="J343" t="n">
-        <v>-6.3258</v>
+        <v>-5.8136</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.74</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.3013</v>
+        <v>-0.2832</v>
       </c>
       <c r="J344" t="n">
-        <v>-7.8338</v>
+        <v>-7.3632</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.68</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.357</v>
+        <v>-0.3423</v>
       </c>
       <c r="J345" t="n">
-        <v>-9.282</v>
+        <v>-8.899800000000001</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3752</v>
+        <v>-0.3619</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.7552</v>
+        <v>-9.4094</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.53</v>
       </c>
       <c r="I347" t="n">
-        <v>1.1413</v>
+        <v>1.1541</v>
       </c>
       <c r="J347" t="n">
-        <v>29.6738</v>
+        <v>30.0066</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.36</v>
       </c>
       <c r="I348" t="n">
-        <v>0.8685</v>
+        <v>0.8495</v>
       </c>
       <c r="J348" t="n">
-        <v>22.581</v>
+        <v>22.087</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.33</v>
       </c>
       <c r="I349" t="n">
-        <v>0.8095</v>
+        <v>0.7864</v>
       </c>
       <c r="J349" t="n">
-        <v>21.047</v>
+        <v>20.4464</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>1.02</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0645</v>
+        <v>0.0484</v>
       </c>
       <c r="J350" t="n">
-        <v>1.677</v>
+        <v>1.2584</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5103</v>
+        <v>-0.4716</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.2678</v>
+        <v>-12.2616</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.05</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1712</v>
+        <v>0.1338</v>
       </c>
       <c r="J352" t="n">
-        <v>4.1088</v>
+        <v>3.2112</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>0.92</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.1154</v>
+        <v>-0.0998</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.7696</v>
+        <v>-2.3952</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>0.84</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.2014</v>
+        <v>-0.182</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.8336</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.83</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2115</v>
+        <v>-0.192</v>
       </c>
       <c r="J355" t="n">
-        <v>-5.076</v>
+        <v>-4.608</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.78</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.261</v>
+        <v>-0.2417</v>
       </c>
       <c r="J356" t="n">
-        <v>-6.264</v>
+        <v>-5.8008</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.41</v>
       </c>
       <c r="I357" t="n">
-        <v>0.9668</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="J357" t="n">
-        <v>23.2032</v>
+        <v>22.9968</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.39</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9303</v>
+        <v>0.9165</v>
       </c>
       <c r="J358" t="n">
-        <v>22.3272</v>
+        <v>21.996</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>1.23</v>
       </c>
       <c r="I359" t="n">
-        <v>0.6086</v>
+        <v>0.5757</v>
       </c>
       <c r="J359" t="n">
-        <v>14.6064</v>
+        <v>13.8168</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>1.07</v>
       </c>
       <c r="I360" t="n">
-        <v>0.2287</v>
+        <v>0.199</v>
       </c>
       <c r="J360" t="n">
-        <v>5.4888</v>
+        <v>4.776</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.9</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3801</v>
+        <v>-0.3391</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.122400000000001</v>
+        <v>-8.138400000000001</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.31</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6044</v>
+        <v>0.545</v>
       </c>
       <c r="J362" t="n">
-        <v>17.5276</v>
+        <v>15.805</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.01</v>
       </c>
       <c r="I363" t="n">
-        <v>0.0407</v>
+        <v>0.0282</v>
       </c>
       <c r="J363" t="n">
-        <v>1.1803</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>0.97</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.0605</v>
+        <v>-0.0473</v>
       </c>
       <c r="J364" t="n">
-        <v>-1.7545</v>
+        <v>-1.3717</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.1016</v>
+        <v>-0.0843</v>
       </c>
       <c r="J365" t="n">
-        <v>-2.9464</v>
+        <v>-2.4447</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.93</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.1141</v>
+        <v>-0.0959</v>
       </c>
       <c r="J366" t="n">
-        <v>-3.3089</v>
+        <v>-2.7811</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.64</v>
       </c>
       <c r="I367" t="n">
-        <v>1.2991</v>
+        <v>1.3201</v>
       </c>
       <c r="J367" t="n">
-        <v>37.6739</v>
+        <v>38.2829</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.54</v>
       </c>
       <c r="I368" t="n">
-        <v>1.1645</v>
+        <v>1.1784</v>
       </c>
       <c r="J368" t="n">
-        <v>33.7705</v>
+        <v>34.1736</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.4</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9546</v>
+        <v>0.9437</v>
       </c>
       <c r="J369" t="n">
-        <v>27.6834</v>
+        <v>27.3673</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.72</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.7985</v>
+        <v>-0.7774</v>
       </c>
       <c r="J370" t="n">
-        <v>-23.1565</v>
+        <v>-22.5446</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.58</v>
       </c>
       <c r="I371" t="n">
-        <v>-1.0865</v>
+        <v>-1.0994</v>
       </c>
       <c r="J371" t="n">
-        <v>-31.5085</v>
+        <v>-31.8826</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.648</v>
+        <v>0.5926</v>
       </c>
       <c r="J372" t="n">
-        <v>18.792</v>
+        <v>17.1854</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.01</v>
       </c>
       <c r="I373" t="n">
-        <v>0.0516</v>
+        <v>0.0347</v>
       </c>
       <c r="J373" t="n">
-        <v>1.4964</v>
+        <v>1.0063</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.87</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1749</v>
+        <v>-0.155</v>
       </c>
       <c r="J374" t="n">
-        <v>-5.0721</v>
+        <v>-4.495</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.87</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1749</v>
+        <v>-0.155</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.0721</v>
+        <v>-4.495</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.63</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4055</v>
+        <v>-0.3953</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.7595</v>
+        <v>-11.4637</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.75</v>
       </c>
       <c r="I377" t="n">
-        <v>1.442</v>
+        <v>1.4738</v>
       </c>
       <c r="J377" t="n">
-        <v>41.818</v>
+        <v>42.7402</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.33</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8175</v>
+        <v>0.7936</v>
       </c>
       <c r="J378" t="n">
-        <v>23.7075</v>
+        <v>23.0144</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.04</v>
       </c>
       <c r="I379" t="n">
-        <v>0.1413</v>
+        <v>0.1174</v>
       </c>
       <c r="J379" t="n">
-        <v>4.0977</v>
+        <v>3.4046</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.97</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.168</v>
+        <v>-0.1365</v>
       </c>
       <c r="J380" t="n">
-        <v>-4.872</v>
+        <v>-3.9585</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5989</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J381" t="n">
-        <v>-17.3681</v>
+        <v>-16.327</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1</v>
       </c>
       <c r="I382" t="n">
-        <v>0.0266</v>
+        <v>0.021</v>
       </c>
       <c r="J382" t="n">
-        <v>0.6916</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>0.88</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.1577</v>
+        <v>-0.1407</v>
       </c>
       <c r="J383" t="n">
-        <v>-4.1002</v>
+        <v>-3.6582</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.87</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1684</v>
+        <v>-0.151</v>
       </c>
       <c r="J384" t="n">
-        <v>-4.3784</v>
+        <v>-3.926</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.85</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1888</v>
+        <v>-0.1707</v>
       </c>
       <c r="J385" t="n">
-        <v>-4.9088</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.65</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3786</v>
+        <v>-0.3654</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.8436</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.46</v>
       </c>
       <c r="I387" t="n">
-        <v>1.0478</v>
+        <v>1.0529</v>
       </c>
       <c r="J387" t="n">
-        <v>27.2428</v>
+        <v>27.3754</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.43</v>
       </c>
       <c r="I388" t="n">
-        <v>1.001</v>
+        <v>0.9981</v>
       </c>
       <c r="J388" t="n">
-        <v>26.026</v>
+        <v>25.9506</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.31</v>
       </c>
       <c r="I389" t="n">
-        <v>0.7731</v>
+        <v>0.7471</v>
       </c>
       <c r="J389" t="n">
-        <v>20.1006</v>
+        <v>19.4246</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.92</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3255</v>
+        <v>-0.2853</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.462999999999999</v>
+        <v>-7.4178</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.88</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4323</v>
+        <v>-0.3915</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.2398</v>
+        <v>-10.179</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>2.15</v>
       </c>
       <c r="I392" t="n">
-        <v>1.8298</v>
+        <v>1.89</v>
       </c>
       <c r="J392" t="n">
-        <v>32.9364</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.74</v>
       </c>
       <c r="I393" t="n">
-        <v>1.3539</v>
+        <v>1.3786</v>
       </c>
       <c r="J393" t="n">
-        <v>24.3702</v>
+        <v>24.8148</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.59</v>
       </c>
       <c r="I394" t="n">
-        <v>1.1713</v>
+        <v>1.1914</v>
       </c>
       <c r="J394" t="n">
-        <v>21.0834</v>
+        <v>21.4452</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>1.15</v>
       </c>
       <c r="I395" t="n">
-        <v>0.3816</v>
+        <v>0.3482</v>
       </c>
       <c r="J395" t="n">
-        <v>6.8688</v>
+        <v>6.2676</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>1.11</v>
       </c>
       <c r="I396" t="n">
-        <v>0.2831</v>
+        <v>0.2482</v>
       </c>
       <c r="J396" t="n">
-        <v>5.0958</v>
+        <v>4.4676</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>0.83</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.1519</v>
+        <v>-0.1286</v>
       </c>
       <c r="J397" t="n">
-        <v>-2.7342</v>
+        <v>-2.3148</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>0.64</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.3517</v>
+        <v>-0.3437</v>
       </c>
       <c r="J398" t="n">
-        <v>-6.3306</v>
+        <v>-6.1866</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.51</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.4649</v>
+        <v>-0.4612</v>
       </c>
       <c r="J399" t="n">
-        <v>-8.3682</v>
+        <v>-8.301600000000001</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.46</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.5087</v>
+        <v>-0.5082</v>
       </c>
       <c r="J400" t="n">
-        <v>-9.156599999999999</v>
+        <v>-9.147600000000001</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.35</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.6065</v>
+        <v>-0.6183</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.917</v>
+        <v>-11.1294</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>2.16</v>
       </c>
       <c r="I402" t="n">
-        <v>1.8553</v>
+        <v>1.9194</v>
       </c>
       <c r="J402" t="n">
-        <v>35.2507</v>
+        <v>36.4686</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.6</v>
       </c>
       <c r="I403" t="n">
-        <v>1.1899</v>
+        <v>1.2081</v>
       </c>
       <c r="J403" t="n">
-        <v>22.6081</v>
+        <v>22.9539</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.38</v>
       </c>
       <c r="I404" t="n">
-        <v>0.8708</v>
+        <v>0.8641</v>
       </c>
       <c r="J404" t="n">
-        <v>16.5452</v>
+        <v>16.4179</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>1.19</v>
       </c>
       <c r="I405" t="n">
-        <v>0.483</v>
+        <v>0.4534</v>
       </c>
       <c r="J405" t="n">
-        <v>9.177</v>
+        <v>8.614599999999999</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>1.09</v>
       </c>
       <c r="I406" t="n">
-        <v>0.2394</v>
+        <v>0.2062</v>
       </c>
       <c r="J406" t="n">
-        <v>4.5486</v>
+        <v>3.9178</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>0.96</v>
       </c>
       <c r="I407" t="n">
-        <v>-0.0058</v>
+        <v>0.0258</v>
       </c>
       <c r="J407" t="n">
-        <v>-0.1102</v>
+        <v>0.4902</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>0.67</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.3352</v>
+        <v>-0.3249</v>
       </c>
       <c r="J408" t="n">
-        <v>-6.3688</v>
+        <v>-6.1731</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>0.58</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.413</v>
+        <v>-0.4047</v>
       </c>
       <c r="J409" t="n">
-        <v>-7.847</v>
+        <v>-7.6893</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.55</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.4391</v>
+        <v>-0.4322</v>
       </c>
       <c r="J410" t="n">
-        <v>-8.3429</v>
+        <v>-8.2118</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.34</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6238</v>
+        <v>-0.6394</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.8522</v>
+        <v>-12.1486</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.73</v>
       </c>
       <c r="I412" t="n">
-        <v>1.346</v>
+        <v>1.3696</v>
       </c>
       <c r="J412" t="n">
-        <v>25.574</v>
+        <v>26.0224</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.55</v>
       </c>
       <c r="I413" t="n">
-        <v>1.1243</v>
+        <v>1.1429</v>
       </c>
       <c r="J413" t="n">
-        <v>21.3617</v>
+        <v>21.7151</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.55</v>
       </c>
       <c r="I414" t="n">
-        <v>1.1243</v>
+        <v>1.1429</v>
       </c>
       <c r="J414" t="n">
-        <v>21.3617</v>
+        <v>21.7151</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>1.52</v>
       </c>
       <c r="I415" t="n">
-        <v>1.087</v>
+        <v>1.1047</v>
       </c>
       <c r="J415" t="n">
-        <v>20.653</v>
+        <v>20.9893</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>1.23</v>
       </c>
       <c r="I416" t="n">
-        <v>0.5662</v>
+        <v>0.5403</v>
       </c>
       <c r="J416" t="n">
-        <v>10.7578</v>
+        <v>10.2657</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>0.77</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.2216</v>
+        <v>-0.2044</v>
       </c>
       <c r="J417" t="n">
-        <v>-4.2104</v>
+        <v>-3.8836</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>0.68</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.3145</v>
+        <v>-0.3042</v>
       </c>
       <c r="J418" t="n">
-        <v>-5.9755</v>
+        <v>-5.7798</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.62</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3715</v>
+        <v>-0.3644</v>
       </c>
       <c r="J419" t="n">
-        <v>-7.0585</v>
+        <v>-6.9236</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.46</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.5097</v>
+        <v>-0.5092</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.6843</v>
+        <v>-9.674799999999999</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.29</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.6609</v>
+        <v>-0.6824</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.5571</v>
+        <v>-12.9656</v>
       </c>
     </row>
     <row r="422">
@@ -21069,10 +21069,10 @@
         <v>1.19</v>
       </c>
       <c r="I422" t="n">
-        <v>0.5475</v>
+        <v>0.5073</v>
       </c>
       <c r="J422" t="n">
-        <v>14.235</v>
+        <v>13.1898</v>
       </c>
     </row>
     <row r="423">
@@ -21109,10 +21109,10 @@
         <v>1.15</v>
       </c>
       <c r="I423" t="n">
-        <v>0.4539</v>
+        <v>0.4124</v>
       </c>
       <c r="J423" t="n">
-        <v>11.8014</v>
+        <v>10.7224</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>1.13</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4053</v>
+        <v>0.3641</v>
       </c>
       <c r="J424" t="n">
-        <v>10.5378</v>
+        <v>9.4666</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>0.93</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.271</v>
+        <v>-0.231</v>
       </c>
       <c r="J425" t="n">
-        <v>-7.046</v>
+        <v>-6.006</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>0.9</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3539</v>
+        <v>-0.3113</v>
       </c>
       <c r="J426" t="n">
-        <v>-9.2014</v>
+        <v>-8.0938</v>
       </c>
     </row>
     <row r="427">
@@ -21269,10 +21269,10 @@
         <v>1.61</v>
       </c>
       <c r="I427" t="n">
-        <v>1.0132</v>
+        <v>0.9815</v>
       </c>
       <c r="J427" t="n">
-        <v>26.3432</v>
+        <v>25.519</v>
       </c>
     </row>
     <row r="428">
@@ -21309,10 +21309,10 @@
         <v>1.14</v>
       </c>
       <c r="I428" t="n">
-        <v>0.3133</v>
+        <v>0.2636</v>
       </c>
       <c r="J428" t="n">
-        <v>8.145799999999999</v>
+        <v>6.8536</v>
       </c>
     </row>
     <row r="429">
@@ -21349,10 +21349,10 @@
         <v>1.07</v>
       </c>
       <c r="I429" t="n">
-        <v>0.1819</v>
+        <v>0.146</v>
       </c>
       <c r="J429" t="n">
-        <v>4.7294</v>
+        <v>3.796</v>
       </c>
     </row>
     <row r="430">
@@ -21389,10 +21389,10 @@
         <v>0.88</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.1769</v>
+        <v>-0.1564</v>
       </c>
       <c r="J430" t="n">
-        <v>-4.5994</v>
+        <v>-4.0664</v>
       </c>
     </row>
     <row r="431">
@@ -21429,10 +21429,10 @@
         <v>0.74</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.3179</v>
+        <v>-0.3018</v>
       </c>
       <c r="J431" t="n">
-        <v>-8.2654</v>
+        <v>-7.8468</v>
       </c>
     </row>
   </sheetData>
